--- a/src/utils/sxsyzlzq/zzz_xingyuzhanli.xlsx
+++ b/src/utils/sxsyzlzq/zzz_xingyuzhanli.xlsx
@@ -16,7 +16,7 @@
     <sheet name="19星域异界币统计" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'19星域战力标'!$F$1:$F$25</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'19星域战力标'!$F$1:$F$24</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="366" uniqueCount="220">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="364" uniqueCount="222">
   <si>
     <t>区服</t>
   </si>
@@ -281,6 +281,9 @@
     <t>战力（2026.09.03）</t>
   </si>
   <si>
+    <t>战力（2026.09.09）</t>
+  </si>
+  <si>
     <t>首席（流派）</t>
   </si>
   <si>
@@ -308,6 +311,9 @@
     <t>累计提升</t>
   </si>
   <si>
+    <t>三周提升</t>
+  </si>
+  <si>
     <t>146区</t>
   </si>
   <si>
@@ -329,6 +335,9 @@
     <t>灰企鹅呆瓜</t>
   </si>
   <si>
+    <t>沙琪玛（快攻）</t>
+  </si>
+  <si>
     <t>丽娅（人海）</t>
   </si>
   <si>
@@ -401,18 +410,18 @@
     <t>迅（养神）</t>
   </si>
   <si>
+    <t>12345。</t>
+  </si>
+  <si>
+    <t>冰男（人海）</t>
+  </si>
+  <si>
     <t>小黑</t>
   </si>
   <si>
     <t>蒙多（回血）</t>
   </si>
   <si>
-    <t>12345。</t>
-  </si>
-  <si>
-    <t>冰男（人海）</t>
-  </si>
-  <si>
     <t>淘汰郎</t>
   </si>
   <si>
@@ -462,9 +471,6 @@
   </si>
   <si>
     <t>微氪</t>
-  </si>
-  <si>
-    <t>明</t>
   </si>
   <si>
     <t>momo</t>
@@ -1424,10 +1430,10 @@
     <xf numFmtId="176" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
+    <xf numFmtId="176" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1770,7 +1776,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:FO39"/>
+  <dimension ref="A1:FQ38"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="11.3666666666667" customWidth="1"/>
@@ -1814,19 +1820,20 @@
     <col min="90" max="90" width="17.9333333333333" hidden="1" customWidth="1"/>
     <col min="91" max="119" width="17.2833333333333" hidden="1" customWidth="1"/>
     <col min="120" max="120" width="18.8" hidden="1" customWidth="1"/>
-    <col min="121" max="149" width="17.2833333333333" hidden="1" customWidth="1"/>
-    <col min="150" max="153" width="17.2833333333333" customWidth="1"/>
-    <col min="154" max="154" width="14.5416666666667" customWidth="1"/>
-    <col min="155" max="155" width="15.1833333333333" hidden="1" customWidth="1"/>
-    <col min="156" max="156" width="13.2583333333333" hidden="1" customWidth="1"/>
-    <col min="157" max="157" width="11.625" hidden="1" customWidth="1"/>
-    <col min="158" max="158" width="12.6083333333333" hidden="1" customWidth="1"/>
-    <col min="159" max="159" width="15.0166666666667" hidden="1" customWidth="1"/>
-    <col min="160" max="160" width="12.625"/>
-    <col min="161" max="161" width="11.4083333333333" hidden="1" customWidth="1"/>
+    <col min="121" max="151" width="17.2833333333333" hidden="1" customWidth="1"/>
+    <col min="152" max="155" width="17.2833333333333" customWidth="1"/>
+    <col min="156" max="156" width="14.5416666666667" customWidth="1"/>
+    <col min="157" max="157" width="15.1833333333333" hidden="1" customWidth="1"/>
+    <col min="158" max="158" width="13.2583333333333" hidden="1" customWidth="1"/>
+    <col min="159" max="159" width="11.625" hidden="1" customWidth="1"/>
+    <col min="160" max="160" width="12.6083333333333" hidden="1" customWidth="1"/>
+    <col min="161" max="161" width="15.0166666666667" hidden="1" customWidth="1"/>
+    <col min="162" max="162" width="12.625"/>
+    <col min="163" max="163" width="11.4083333333333" hidden="1" customWidth="1"/>
+    <col min="164" max="164" width="10.425" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:171">
+    <row r="1" spans="1:173">
       <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
@@ -2283,43 +2290,52 @@
       <c r="EV1" s="5" t="s">
         <v>80</v>
       </c>
-      <c r="EW1" s="5" t="s">
+      <c r="EW1" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="EX1" s="9" t="s">
         <v>81</v>
       </c>
-      <c r="EX1" s="5" t="s">
+      <c r="EY1" s="5" t="s">
         <v>82</v>
       </c>
-      <c r="EY1" t="s">
+      <c r="EZ1" s="5" t="s">
         <v>83</v>
       </c>
-      <c r="EZ1" t="s">
+      <c r="FA1" t="s">
         <v>84</v>
       </c>
-      <c r="FA1" t="s">
+      <c r="FB1" t="s">
         <v>85</v>
       </c>
-      <c r="FB1" t="s">
+      <c r="FC1" t="s">
         <v>86</v>
       </c>
-      <c r="FC1" t="s">
+      <c r="FD1" t="s">
         <v>87</v>
       </c>
-      <c r="FD1" t="s">
+      <c r="FE1" t="s">
         <v>88</v>
       </c>
-      <c r="FE1" t="s">
+      <c r="FF1" t="s">
         <v>89</v>
       </c>
+      <c r="FG1" t="s">
+        <v>90</v>
+      </c>
+      <c r="FH1" t="s">
+        <v>91</v>
+      </c>
     </row>
-    <row r="2" s="8" customFormat="1" spans="1:171">
+    <row r="2" s="8" customFormat="1" spans="1:173">
       <c r="A2" s="5" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="D2" s="5">
         <v>4105.48</v>
@@ -2842,45 +2858,56 @@
       <c r="EV2" s="12">
         <v>11709.72</v>
       </c>
-      <c r="EW2" s="11" t="s">
-        <v>93</v>
-      </c>
-      <c r="EX2" s="9">
-        <v>2973.52</v>
-      </c>
-      <c r="EY2" s="9" t="s">
-        <v>94</v>
+      <c r="EW2" s="12">
+        <f>EX2-EV2</f>
+        <v>323.470000000001</v>
+      </c>
+      <c r="EX2" s="12">
+        <v>12033.19</v>
+      </c>
+      <c r="EY2" s="11" t="s">
+        <v>95</v>
       </c>
       <c r="EZ2" s="9">
+        <v>3051.02</v>
+      </c>
+      <c r="FA2" s="9" t="s">
+        <v>96</v>
+      </c>
+      <c r="FB2" s="9">
         <v>1267.77</v>
       </c>
-      <c r="FA2" s="5">
+      <c r="FC2" s="5">
         <v>400</v>
       </c>
-      <c r="FB2" s="5">
+      <c r="FD2" s="5">
         <v>1.2</v>
       </c>
-      <c r="FC2" s="5">
+      <c r="FE2" s="5">
         <v>186759</v>
       </c>
-      <c r="FD2" s="9">
-        <f>2.79/(EV2/EX2)</f>
-        <v>0.70848156915793</v>
-      </c>
-      <c r="FE2" s="9">
+      <c r="FF2" s="9">
+        <f>2.43/(EX2/EZ2)</f>
+        <v>0.616127444177313</v>
+      </c>
+      <c r="FG2" s="9">
         <f>BP2-D2</f>
         <v>2684.95</v>
       </c>
+      <c r="FH2" s="9">
+        <f>EX2-ER2</f>
+        <v>734.25</v>
+      </c>
     </row>
-    <row r="3" spans="1:171">
+    <row r="3" spans="1:173">
       <c r="A3" s="5" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="D3" s="5">
         <v>2533.85</v>
@@ -3403,45 +3430,56 @@
       <c r="EV3" s="12">
         <v>9465.91</v>
       </c>
-      <c r="EW3" s="11" t="s">
-        <v>97</v>
-      </c>
-      <c r="EX3" s="9">
-        <v>2242.07</v>
-      </c>
-      <c r="EY3" s="9" t="s">
-        <v>97</v>
+      <c r="EW3" s="12">
+        <f>EX3-EV3</f>
+        <v>50.3600000000006</v>
+      </c>
+      <c r="EX3" s="12">
+        <v>9516.27</v>
+      </c>
+      <c r="EY3" s="11" t="s">
+        <v>99</v>
       </c>
       <c r="EZ3" s="9">
+        <v>2259.4</v>
+      </c>
+      <c r="FA3" s="9" t="s">
+        <v>100</v>
+      </c>
+      <c r="FB3" s="9">
         <v>1010.07</v>
       </c>
-      <c r="FA3" s="5">
+      <c r="FC3" s="5">
         <v>200</v>
       </c>
-      <c r="FB3" s="5">
+      <c r="FD3" s="5">
         <v>1.6</v>
       </c>
-      <c r="FC3" s="5">
+      <c r="FE3" s="5">
         <v>172501</v>
       </c>
-      <c r="FD3" s="9">
-        <f>2.79/(EV3/EX3)</f>
-        <v>0.660831901000538</v>
-      </c>
-      <c r="FE3" s="9">
+      <c r="FF3" s="9">
+        <f>2.43/(EX3/EZ3)</f>
+        <v>0.576942646646218</v>
+      </c>
+      <c r="FG3" s="9">
         <f>BP3-D3</f>
         <v>2277.14</v>
       </c>
+      <c r="FH3" s="9">
+        <f>EX3-ER3</f>
+        <v>517.470000000001</v>
+      </c>
     </row>
-    <row r="4" spans="1:171">
+    <row r="4" spans="1:173">
       <c r="A4" s="5" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="D4" s="5">
         <v>2714.1</v>
@@ -3964,45 +4002,56 @@
       <c r="EV4" s="12">
         <v>9368.87</v>
       </c>
-      <c r="EW4" s="11" t="s">
-        <v>100</v>
-      </c>
-      <c r="EX4" s="9">
-        <v>2652.52</v>
-      </c>
-      <c r="EY4" s="9" t="s">
-        <v>101</v>
+      <c r="EW4" s="12">
+        <f>EX4-EV4</f>
+        <v>91.1899999999987</v>
+      </c>
+      <c r="EX4" s="12">
+        <v>9460.06</v>
+      </c>
+      <c r="EY4" s="11" t="s">
+        <v>103</v>
       </c>
       <c r="EZ4" s="9">
+        <v>2704.72</v>
+      </c>
+      <c r="FA4" s="9" t="s">
+        <v>104</v>
+      </c>
+      <c r="FB4" s="9">
         <v>1327.12</v>
       </c>
-      <c r="FA4" s="5">
+      <c r="FC4" s="5">
         <v>500</v>
       </c>
-      <c r="FB4" s="5">
+      <c r="FD4" s="5">
         <v>8.6</v>
       </c>
-      <c r="FC4" s="5">
+      <c r="FE4" s="5">
         <v>191519</v>
       </c>
-      <c r="FD4" s="9">
-        <f>2.79/(EV4/EX4)</f>
-        <v>0.789906445494494</v>
-      </c>
-      <c r="FE4" s="9">
+      <c r="FF4" s="9">
+        <f>2.43/(EX4/EZ4)</f>
+        <v>0.694759821819312</v>
+      </c>
+      <c r="FG4" s="9">
         <f>BP4-D4</f>
         <v>3022.78</v>
       </c>
+      <c r="FH4" s="9">
+        <f>EX4-ER4</f>
+        <v>197.59</v>
+      </c>
     </row>
-    <row r="5" spans="1:171">
+    <row r="5" spans="1:173">
       <c r="A5" s="5" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="D5" s="5">
         <v>1754.54</v>
@@ -4525,48 +4574,59 @@
       <c r="EV5" s="12">
         <v>7585.38</v>
       </c>
-      <c r="EW5" s="11" t="s">
-        <v>105</v>
-      </c>
-      <c r="EX5" s="9">
-        <v>1591.14</v>
-      </c>
-      <c r="EY5" s="9" t="s">
-        <v>106</v>
+      <c r="EW5" s="12">
+        <f>EX5-EV5</f>
+        <v>13.9300000000003</v>
+      </c>
+      <c r="EX5" s="12">
+        <v>7599.31</v>
+      </c>
+      <c r="EY5" s="11" t="s">
+        <v>108</v>
       </c>
       <c r="EZ5" s="9">
+        <v>1560.32</v>
+      </c>
+      <c r="FA5" s="9" t="s">
+        <v>109</v>
+      </c>
+      <c r="FB5" s="9">
         <v>686.88</v>
       </c>
-      <c r="FA5" s="5">
+      <c r="FC5" s="5">
         <v>300</v>
       </c>
-      <c r="FB5" s="5">
+      <c r="FD5" s="5">
         <v>2.2</v>
       </c>
-      <c r="FC5" s="5">
+      <c r="FE5" s="5">
         <v>132783</v>
       </c>
-      <c r="FD5" s="9">
-        <f>2.79/(EV5/EX5)</f>
-        <v>0.585241688616786</v>
-      </c>
-      <c r="FE5" s="9">
+      <c r="FF5" s="9">
+        <f>2.43/(EX5/EZ5)</f>
+        <v>0.498937087709279</v>
+      </c>
+      <c r="FG5" s="9">
         <f>BP5-D5</f>
         <v>2267.65</v>
       </c>
-      <c r="FO5">
+      <c r="FH5" s="9">
+        <f>EX5-ER5</f>
+        <v>391.580000000001</v>
+      </c>
+      <c r="FQ5">
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:171">
+    <row r="6" spans="1:173">
       <c r="A6" s="1" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="D6" s="1">
         <v>1735.94</v>
@@ -5089,45 +5149,56 @@
       <c r="EV6" s="16">
         <v>6521.7</v>
       </c>
-      <c r="EW6" s="15" t="s">
-        <v>93</v>
-      </c>
-      <c r="EX6" s="14">
-        <v>2125.02</v>
-      </c>
-      <c r="EY6" s="9" t="s">
-        <v>110</v>
-      </c>
-      <c r="EZ6" s="9">
+      <c r="EW6" s="16">
+        <f>EX6-EV6</f>
+        <v>27.4899999999998</v>
+      </c>
+      <c r="EX6" s="16">
+        <v>6549.19</v>
+      </c>
+      <c r="EY6" s="15" t="s">
+        <v>95</v>
+      </c>
+      <c r="EZ6" s="14">
+        <v>2129.62</v>
+      </c>
+      <c r="FA6" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="FB6" s="9">
         <v>824.67</v>
       </c>
-      <c r="FA6" s="5">
+      <c r="FC6" s="5">
         <v>80</v>
       </c>
-      <c r="FB6" s="5">
+      <c r="FD6" s="5">
         <v>7.2</v>
       </c>
-      <c r="FC6" s="5">
+      <c r="FE6" s="5">
         <v>150192</v>
       </c>
-      <c r="FD6" s="9">
-        <f>2.79/(EV6/EX6)</f>
-        <v>0.909089010534063</v>
-      </c>
-      <c r="FE6" s="9">
+      <c r="FF6" s="9">
+        <f>2.43/(EX6/EZ6)</f>
+        <v>0.790170479097415</v>
+      </c>
+      <c r="FG6" s="9">
         <f>BP6-D6</f>
         <v>1944.52</v>
       </c>
+      <c r="FH6" s="9">
+        <f>EX6-ER6</f>
+        <v>212.57</v>
+      </c>
     </row>
-    <row r="7" spans="1:171">
+    <row r="7" spans="1:173">
       <c r="A7" s="1" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="D7" s="1">
         <v>1350.52</v>
@@ -5650,45 +5721,56 @@
       <c r="EV7" s="16">
         <v>6330.97</v>
       </c>
-      <c r="EW7" s="15" t="s">
-        <v>97</v>
-      </c>
-      <c r="EX7" s="14">
-        <v>1944.37</v>
-      </c>
-      <c r="EY7" s="9" t="s">
-        <v>112</v>
-      </c>
-      <c r="EZ7" s="9">
+      <c r="EW7" s="16">
+        <f>EX7-EV7</f>
+        <v>57.6899999999996</v>
+      </c>
+      <c r="EX7" s="16">
+        <v>6388.66</v>
+      </c>
+      <c r="EY7" s="15" t="s">
+        <v>100</v>
+      </c>
+      <c r="EZ7" s="14">
+        <v>1966.57</v>
+      </c>
+      <c r="FA7" s="9" t="s">
+        <v>115</v>
+      </c>
+      <c r="FB7" s="9">
         <v>896.02</v>
       </c>
-      <c r="FA7" s="5">
+      <c r="FC7" s="5">
         <v>65</v>
       </c>
-      <c r="FB7" s="5">
+      <c r="FD7" s="5">
         <v>1.4</v>
       </c>
-      <c r="FC7" s="5">
+      <c r="FE7" s="5">
         <v>127603</v>
       </c>
-      <c r="FD7" s="9">
-        <f>2.79/(EV7/EX7)</f>
-        <v>0.856865898906487</v>
-      </c>
-      <c r="FE7" s="9">
+      <c r="FF7" s="9">
+        <f>2.43/(EX7/EZ7)</f>
+        <v>0.74800742252679</v>
+      </c>
+      <c r="FG7" s="9">
         <f>BP7-D7</f>
         <v>2104.56</v>
       </c>
+      <c r="FH7" s="9">
+        <f>EX7-ER7</f>
+        <v>258.11</v>
+      </c>
     </row>
-    <row r="8" spans="1:171">
+    <row r="8" spans="1:173">
       <c r="A8" s="1" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="D8" s="1">
         <v>2136.24</v>
@@ -6211,45 +6293,56 @@
       <c r="EV8" s="16">
         <v>6016.99</v>
       </c>
-      <c r="EW8" s="15" t="s">
-        <v>114</v>
-      </c>
-      <c r="EX8" s="14">
-        <v>2252.57</v>
-      </c>
-      <c r="EY8" s="9" t="s">
-        <v>115</v>
-      </c>
-      <c r="EZ8" s="9">
+      <c r="EW8" s="16">
+        <f>EX8-EV8</f>
+        <v>19.5300000000007</v>
+      </c>
+      <c r="EX8" s="16">
+        <v>6036.52</v>
+      </c>
+      <c r="EY8" s="15" t="s">
+        <v>117</v>
+      </c>
+      <c r="EZ8" s="14">
+        <v>2259.27</v>
+      </c>
+      <c r="FA8" s="9" t="s">
+        <v>118</v>
+      </c>
+      <c r="FB8" s="9">
         <v>1211.82</v>
       </c>
-      <c r="FA8" s="5">
+      <c r="FC8" s="5">
         <v>20</v>
       </c>
-      <c r="FB8" s="5">
+      <c r="FD8" s="5">
         <v>1.2</v>
       </c>
-      <c r="FC8" s="5">
+      <c r="FE8" s="5">
         <v>153852</v>
       </c>
-      <c r="FD8" s="9">
-        <f>2.79/(EV8/EX8)</f>
-        <v>1.04448740981787</v>
-      </c>
-      <c r="FE8" s="9">
+      <c r="FF8" s="9">
+        <f>2.43/(EX8/EZ8)</f>
+        <v>0.909468717075401</v>
+      </c>
+      <c r="FG8" s="9">
         <f>BP8-D8</f>
         <v>1584.75</v>
       </c>
+      <c r="FH8" s="9">
+        <f>EX8-ER8</f>
+        <v>121.76</v>
+      </c>
     </row>
-    <row r="9" spans="1:171">
+    <row r="9" spans="1:173">
       <c r="A9" s="1" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="D9" s="1">
         <v>1726.42</v>
@@ -6772,45 +6865,56 @@
       <c r="EV9" s="16">
         <v>5747.92</v>
       </c>
-      <c r="EW9" s="15" t="s">
-        <v>112</v>
-      </c>
-      <c r="EX9" s="14">
-        <v>1751.52</v>
-      </c>
-      <c r="EY9" s="9" t="s">
-        <v>112</v>
-      </c>
-      <c r="EZ9" s="9">
+      <c r="EW9" s="16">
+        <f>EX9-EV9</f>
+        <v>20.1599999999999</v>
+      </c>
+      <c r="EX9" s="16">
+        <v>5768.08</v>
+      </c>
+      <c r="EY9" s="15" t="s">
+        <v>115</v>
+      </c>
+      <c r="EZ9" s="14">
+        <v>1768.92</v>
+      </c>
+      <c r="FA9" s="9" t="s">
+        <v>115</v>
+      </c>
+      <c r="FB9" s="9">
         <v>754.67</v>
       </c>
-      <c r="FA9" s="5">
+      <c r="FC9" s="5">
         <v>50</v>
       </c>
-      <c r="FB9" s="5">
+      <c r="FD9" s="5">
         <v>1.3</v>
       </c>
-      <c r="FC9" s="5">
+      <c r="FE9" s="5">
         <v>124763</v>
       </c>
-      <c r="FD9" s="9">
-        <f>2.79/(EV9/EX9)</f>
-        <v>0.850175506965998</v>
-      </c>
-      <c r="FE9" s="9">
+      <c r="FF9" s="9">
+        <f>2.43/(EX9/EZ9)</f>
+        <v>0.745217750100553</v>
+      </c>
+      <c r="FG9" s="9">
         <f>BP9-D9</f>
         <v>1654.23</v>
       </c>
+      <c r="FH9" s="9">
+        <f>EX9-ER9</f>
+        <v>90.1899999999996</v>
+      </c>
     </row>
-    <row r="10" spans="1:171">
+    <row r="10" spans="1:173">
       <c r="A10" s="1" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="D10" s="1">
         <v>1446.65</v>
@@ -7333,45 +7437,56 @@
       <c r="EV10" s="16">
         <v>5356.72</v>
       </c>
-      <c r="EW10" s="15" t="s">
-        <v>97</v>
-      </c>
-      <c r="EX10" s="14">
-        <v>1918.37</v>
-      </c>
-      <c r="EY10" s="9" t="s">
-        <v>112</v>
-      </c>
-      <c r="EZ10" s="9">
+      <c r="EW10" s="16">
+        <f>EX10-EV10</f>
+        <v>11.2699999999995</v>
+      </c>
+      <c r="EX10" s="16">
+        <v>5367.99</v>
+      </c>
+      <c r="EY10" s="15" t="s">
+        <v>100</v>
+      </c>
+      <c r="EZ10" s="14">
+        <v>2207.42</v>
+      </c>
+      <c r="FA10" s="9" t="s">
+        <v>115</v>
+      </c>
+      <c r="FB10" s="9">
         <v>1048.57</v>
       </c>
-      <c r="FA10" s="5">
+      <c r="FC10" s="5">
         <v>65</v>
       </c>
-      <c r="FB10" s="5">
+      <c r="FD10" s="5">
         <v>1.4</v>
       </c>
-      <c r="FC10" s="5">
+      <c r="FE10" s="5">
         <v>109333</v>
       </c>
-      <c r="FD10" s="9">
-        <f>2.79/(EV10/EX10)</f>
-        <v>0.999165963500052</v>
-      </c>
-      <c r="FE10" s="9">
+      <c r="FF10" s="9">
+        <f>2.43/(EX10/EZ10)</f>
+        <v>0.999262405481381</v>
+      </c>
+      <c r="FG10" s="9">
         <f>BP10-D10</f>
         <v>1685.99</v>
       </c>
+      <c r="FH10" s="9">
+        <f>EX10-ER10</f>
+        <v>79.9499999999998</v>
+      </c>
     </row>
-    <row r="11" spans="1:171">
+    <row r="11" spans="1:173">
       <c r="A11" s="1" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="D11" s="1">
         <v>1425.22</v>
@@ -7894,1167 +8009,1200 @@
       <c r="EV11" s="16">
         <v>5025.19</v>
       </c>
-      <c r="EW11" s="15" t="s">
-        <v>120</v>
-      </c>
-      <c r="EX11" s="14">
-        <v>1327.27</v>
-      </c>
-      <c r="EY11" s="14" t="s">
-        <v>120</v>
+      <c r="EW11" s="16">
+        <f>EX11-EV11</f>
+        <v>14.0100000000002</v>
+      </c>
+      <c r="EX11" s="16">
+        <v>5039.2</v>
+      </c>
+      <c r="EY11" s="15" t="s">
+        <v>123</v>
       </c>
       <c r="EZ11" s="14">
+        <v>1335.47</v>
+      </c>
+      <c r="FA11" s="14" t="s">
+        <v>123</v>
+      </c>
+      <c r="FB11" s="14">
         <v>748.71</v>
       </c>
-      <c r="FA11" s="1">
+      <c r="FC11" s="1">
         <v>20</v>
       </c>
-      <c r="FB11" s="1">
+      <c r="FD11" s="1">
         <v>1.1</v>
       </c>
-      <c r="FC11" s="1">
+      <c r="FE11" s="1">
         <v>106867</v>
       </c>
-      <c r="FD11" s="9">
-        <f>2.79/(EV11/EX11)</f>
-        <v>0.736904136958006</v>
-      </c>
-      <c r="FE11" s="9">
+      <c r="FF11" s="9">
+        <f>2.43/(EX11/EZ11)</f>
+        <v>0.643989541990792</v>
+      </c>
+      <c r="FG11" s="9">
         <f>BP11-D11</f>
         <v>1715.51</v>
       </c>
+      <c r="FH11" s="9">
+        <f>EX11-ER11</f>
+        <v>55.8000000000002</v>
+      </c>
     </row>
-    <row r="12" spans="1:171">
+    <row r="12" spans="1:173">
       <c r="A12" s="2" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="D12" s="2">
-        <v>1349.35</v>
+        <v>1156.57</v>
       </c>
       <c r="E12" s="2">
         <f>F12-D12</f>
-        <v>49.6200000000001</v>
+        <v>40.4400000000001</v>
       </c>
       <c r="F12" s="2">
-        <v>1398.97</v>
+        <v>1197.01</v>
       </c>
       <c r="G12" s="2">
         <f>H12-F12</f>
-        <v>27.79</v>
+        <v>46.97</v>
       </c>
       <c r="H12" s="2">
-        <v>1426.76</v>
+        <v>1243.98</v>
       </c>
       <c r="I12" s="2">
         <f>J12-H12</f>
-        <v>29.02</v>
+        <v>58.49</v>
       </c>
       <c r="J12" s="2">
-        <v>1455.78</v>
+        <v>1302.47</v>
       </c>
       <c r="K12" s="2">
         <f>L12-J12</f>
-        <v>97.8800000000001</v>
+        <v>36.6399999999999</v>
       </c>
       <c r="L12" s="2">
-        <v>1553.66</v>
+        <v>1339.11</v>
       </c>
       <c r="M12" s="2">
         <f>N12-L12</f>
-        <v>42.3599999999999</v>
+        <v>33.99</v>
       </c>
       <c r="N12" s="2">
-        <v>1596.02</v>
+        <v>1373.1</v>
       </c>
       <c r="O12" s="2">
         <f>P12-N12</f>
-        <v>54.22</v>
+        <v>30.0600000000002</v>
       </c>
       <c r="P12" s="2">
-        <v>1650.24</v>
+        <v>1403.16</v>
       </c>
       <c r="Q12" s="2">
         <f>R12-P12</f>
-        <v>35.5899999999999</v>
+        <v>47.3</v>
       </c>
       <c r="R12" s="2">
-        <v>1685.83</v>
+        <v>1450.46</v>
       </c>
       <c r="S12" s="2">
         <f>T12-R12</f>
-        <v>68.1300000000001</v>
+        <v>46.8299999999999</v>
       </c>
       <c r="T12" s="2">
-        <v>1753.96</v>
+        <v>1497.29</v>
       </c>
       <c r="U12" s="2">
         <f>V12-T12</f>
-        <v>58.5599999999999</v>
+        <v>58.6500000000001</v>
       </c>
       <c r="V12" s="17">
-        <v>1812.52</v>
+        <v>1555.94</v>
       </c>
       <c r="W12" s="2">
         <f>X12-V12</f>
-        <v>67.21</v>
+        <v>70.3099999999999</v>
       </c>
       <c r="X12" s="17">
-        <v>1879.73</v>
+        <v>1626.25</v>
       </c>
       <c r="Y12" s="2">
         <f>Z12-X12</f>
-        <v>20.22</v>
+        <v>31.49</v>
       </c>
       <c r="Z12" s="2">
-        <v>1899.95</v>
+        <v>1657.74</v>
       </c>
       <c r="AA12" s="2">
         <f>AB12-Z12</f>
-        <v>35.0999999999999</v>
+        <v>59.21</v>
       </c>
       <c r="AB12" s="2">
-        <v>1935.05</v>
+        <v>1716.95</v>
       </c>
       <c r="AC12" s="2">
         <f>AD12-AB12</f>
-        <v>44.73</v>
+        <v>31.99</v>
       </c>
       <c r="AD12" s="2">
-        <v>1979.78</v>
+        <v>1748.94</v>
       </c>
       <c r="AE12" s="18">
         <f>AF12-AD12</f>
-        <v>31.1700000000001</v>
+        <v>52.0999999999999</v>
       </c>
       <c r="AF12" s="18">
-        <v>2010.95</v>
+        <v>1801.04</v>
       </c>
       <c r="AG12" s="18">
         <f>AH12-AF12</f>
-        <v>51.4100000000001</v>
+        <v>74.74</v>
       </c>
       <c r="AH12" s="18">
-        <v>2062.36</v>
+        <v>1875.78</v>
       </c>
       <c r="AI12" s="18">
         <f>AJ12-AH12</f>
-        <v>64.9899999999998</v>
+        <v>51.3700000000001</v>
       </c>
       <c r="AJ12" s="18">
-        <v>2127.35</v>
+        <v>1927.15</v>
       </c>
       <c r="AK12" s="18">
         <f>AL12-AJ12</f>
-        <v>21.6500000000001</v>
+        <v>58.48</v>
       </c>
       <c r="AL12" s="18">
-        <v>2149</v>
+        <v>1985.63</v>
       </c>
       <c r="AM12" s="18">
         <f>AN12-AL12</f>
-        <v>29.3899999999999</v>
+        <v>31.6599999999999</v>
       </c>
       <c r="AN12" s="18">
-        <v>2178.39</v>
+        <v>2017.29</v>
       </c>
       <c r="AO12" s="18">
         <f>AP12-AN12</f>
-        <v>28.6100000000001</v>
+        <v>53.0100000000002</v>
       </c>
       <c r="AP12" s="18">
-        <v>2207</v>
+        <v>2070.3</v>
       </c>
       <c r="AQ12" s="18">
         <f>AR12-AP12</f>
-        <v>17.4099999999999</v>
+        <v>52.5</v>
       </c>
       <c r="AR12" s="18">
-        <v>2224.41</v>
+        <v>2122.8</v>
       </c>
       <c r="AS12" s="18">
         <f>AT12-AR12</f>
-        <v>21.0700000000002</v>
+        <v>65.02</v>
       </c>
       <c r="AT12" s="18">
-        <v>2245.48</v>
+        <v>2187.82</v>
       </c>
       <c r="AU12" s="19">
         <f>AV12-AT12</f>
-        <v>94.73</v>
+        <v>39.3199999999997</v>
       </c>
       <c r="AV12" s="19">
-        <v>2340.21</v>
+        <v>2227.14</v>
       </c>
       <c r="AW12" s="20">
         <f>AX12-AV12</f>
-        <v>25.7199999999998</v>
+        <v>65.5799999999999</v>
       </c>
       <c r="AX12" s="20">
-        <v>2365.93</v>
+        <v>2292.72</v>
       </c>
       <c r="AY12" s="20">
         <f>AZ12-AX12</f>
-        <v>69.3800000000001</v>
+        <v>43.3800000000001</v>
       </c>
       <c r="AZ12" s="20">
-        <v>2435.31</v>
+        <v>2336.1</v>
       </c>
       <c r="BA12" s="20">
         <f>BB12-AZ12</f>
-        <v>48.79</v>
+        <v>56.0500000000002</v>
       </c>
       <c r="BB12" s="20">
-        <v>2484.1</v>
+        <v>2392.15</v>
       </c>
       <c r="BC12" s="20">
         <f>BD12-BB12</f>
-        <v>4.57999999999993</v>
+        <v>36.2999999999997</v>
       </c>
       <c r="BD12" s="20">
-        <v>2488.68</v>
+        <v>2428.45</v>
       </c>
       <c r="BE12" s="19">
         <f>BF12-BD12</f>
-        <v>42.2000000000003</v>
+        <v>49.8200000000002</v>
       </c>
       <c r="BF12" s="20">
-        <v>2530.88</v>
+        <v>2478.27</v>
       </c>
       <c r="BG12" s="20">
         <f>BH12-BF12</f>
-        <v>24.9400000000001</v>
+        <v>65.7800000000002</v>
       </c>
       <c r="BH12" s="20">
-        <v>2555.82</v>
+        <v>2544.05</v>
       </c>
       <c r="BI12" s="20">
         <f>BJ12-BH12</f>
-        <v>52.77</v>
+        <v>16.29</v>
       </c>
       <c r="BJ12" s="20">
-        <v>2608.59</v>
+        <v>2560.34</v>
       </c>
       <c r="BK12" s="20">
         <f>BL12-BJ12</f>
-        <v>55.8799999999997</v>
+        <v>84.4099999999999</v>
       </c>
       <c r="BL12" s="20">
-        <v>2664.47</v>
+        <v>2644.75</v>
       </c>
       <c r="BM12" s="20">
         <f>BN12-BL12</f>
-        <v>21.2000000000003</v>
+        <v>33.6599999999999</v>
       </c>
       <c r="BN12" s="20">
-        <v>2685.67</v>
+        <v>2678.41</v>
       </c>
       <c r="BO12" s="20">
         <f>BP12-BN12</f>
-        <v>32.02</v>
+        <v>51.1500000000001</v>
       </c>
       <c r="BP12" s="20">
-        <v>2717.69</v>
+        <v>2729.56</v>
       </c>
       <c r="BQ12" s="20">
         <f>BR12-BP12</f>
-        <v>24.5999999999999</v>
+        <v>50.8299999999999</v>
       </c>
       <c r="BR12" s="20">
-        <v>2742.29</v>
+        <v>2780.39</v>
       </c>
       <c r="BS12" s="20">
         <f>BT12-BR12</f>
-        <v>14.79</v>
+        <v>33.9300000000003</v>
       </c>
       <c r="BT12" s="20">
-        <v>2757.08</v>
+        <v>2814.32</v>
       </c>
       <c r="BU12" s="20">
         <f>BV12-BT12</f>
-        <v>70.6700000000001</v>
+        <v>43.9400000000001</v>
       </c>
       <c r="BV12" s="20">
-        <v>2827.75</v>
+        <v>2858.26</v>
       </c>
       <c r="BW12" s="20">
         <f>BX12-BV12</f>
-        <v>56.4400000000001</v>
+        <v>47.4199999999996</v>
       </c>
       <c r="BX12" s="20">
-        <v>2884.19</v>
+        <v>2905.68</v>
       </c>
       <c r="BY12" s="20">
         <f>BZ12-BX12</f>
-        <v>33.4200000000001</v>
+        <v>51.02</v>
       </c>
       <c r="BZ12" s="20">
-        <v>2917.61</v>
+        <v>2956.7</v>
       </c>
       <c r="CA12" s="20">
         <f>CB12-BZ12</f>
-        <v>57.9000000000001</v>
+        <v>67.3400000000001</v>
       </c>
       <c r="CB12" s="20">
-        <v>2975.51</v>
+        <v>3024.04</v>
       </c>
       <c r="CC12" s="20">
         <f>CD12-CB12</f>
-        <v>90.8599999999997</v>
+        <v>59.4200000000001</v>
       </c>
       <c r="CD12" s="20">
-        <v>3066.37</v>
+        <v>3083.46</v>
       </c>
       <c r="CE12" s="20">
         <f>CF12-CD12</f>
-        <v>161.05</v>
+        <v>49.1900000000001</v>
       </c>
       <c r="CF12" s="20">
-        <v>3227.42</v>
+        <v>3132.65</v>
       </c>
       <c r="CG12" s="20">
         <f>CH12-CF12</f>
-        <v>36.6700000000001</v>
+        <v>46.54</v>
       </c>
       <c r="CH12" s="20">
-        <v>3264.09</v>
+        <v>3179.19</v>
       </c>
       <c r="CI12" s="20">
         <f>CJ12-CH12</f>
-        <v>72.0899999999997</v>
+        <v>23.3600000000001</v>
       </c>
       <c r="CJ12" s="20">
-        <v>3336.18</v>
+        <v>3202.55</v>
       </c>
       <c r="CK12" s="20">
         <f>CL12-CJ12</f>
-        <v>32.7800000000002</v>
+        <v>39.1199999999999</v>
       </c>
       <c r="CL12" s="20">
-        <v>3368.96</v>
+        <v>3241.67</v>
       </c>
       <c r="CM12" s="20">
         <f>CN12-CL12</f>
-        <v>40.8299999999999</v>
+        <v>57.2199999999998</v>
       </c>
       <c r="CN12" s="20">
-        <v>3409.79</v>
+        <v>3298.89</v>
       </c>
       <c r="CO12" s="20">
         <f>CP12-CN12</f>
-        <v>23.02</v>
+        <v>48.46</v>
       </c>
       <c r="CP12" s="20">
-        <v>3432.81</v>
+        <v>3347.35</v>
       </c>
       <c r="CQ12" s="20">
         <f>CR12-CP12</f>
-        <v>43.9500000000003</v>
+        <v>37.0799999999999</v>
       </c>
       <c r="CR12" s="20">
-        <v>3476.76</v>
+        <v>3384.43</v>
       </c>
       <c r="CS12" s="20">
         <f>CT12-CR12</f>
-        <v>76</v>
+        <v>144.73</v>
       </c>
       <c r="CT12" s="20">
-        <v>3552.76</v>
+        <v>3529.16</v>
       </c>
       <c r="CU12" s="20">
         <f>CV12-CT12</f>
-        <v>40.6499999999996</v>
+        <v>38.7400000000002</v>
       </c>
       <c r="CV12" s="20">
-        <v>3593.41</v>
+        <v>3567.9</v>
       </c>
       <c r="CW12" s="19">
         <f>CX12-CV12</f>
-        <v>34.1300000000001</v>
+        <v>62.7399999999998</v>
       </c>
       <c r="CX12" s="20">
-        <v>3627.54</v>
+        <v>3630.64</v>
       </c>
       <c r="CY12" s="20">
         <f>CZ12-CX12</f>
-        <v>63.5599999999999</v>
+        <v>36.1200000000003</v>
       </c>
       <c r="CZ12" s="20">
-        <v>3691.1</v>
+        <v>3666.76</v>
       </c>
       <c r="DA12" s="20">
         <f>DB12-CZ12</f>
-        <v>43.3800000000001</v>
+        <v>36.7299999999996</v>
       </c>
       <c r="DB12" s="20">
-        <v>3734.48</v>
+        <v>3703.49</v>
       </c>
       <c r="DC12" s="20">
         <f>DD12-DB12</f>
-        <v>57.9699999999998</v>
+        <v>53.7700000000004</v>
       </c>
       <c r="DD12" s="20">
-        <v>3792.45</v>
+        <v>3757.26</v>
       </c>
       <c r="DE12" s="20">
         <f>DF12-DD12</f>
-        <v>53.6100000000001</v>
+        <v>59.2099999999996</v>
       </c>
       <c r="DF12" s="20">
-        <v>3846.06</v>
+        <v>3816.47</v>
       </c>
       <c r="DG12" s="20">
         <f>DH12-DF12</f>
-        <v>32.0900000000001</v>
+        <v>25.75</v>
       </c>
       <c r="DH12" s="20">
-        <v>3878.15</v>
+        <v>3842.22</v>
       </c>
       <c r="DI12" s="20">
         <f>DJ12-DH12</f>
-        <v>50.4299999999998</v>
+        <v>61.21</v>
       </c>
       <c r="DJ12" s="20">
-        <v>3928.58</v>
+        <v>3903.43</v>
       </c>
       <c r="DK12" s="20">
         <f>DL12-DJ12</f>
-        <v>22.9500000000003</v>
+        <v>46.3700000000003</v>
       </c>
       <c r="DL12" s="20">
-        <v>3951.53</v>
+        <v>3949.8</v>
       </c>
       <c r="DM12" s="20">
         <f>DN12-DL12</f>
-        <v>35.1299999999997</v>
+        <v>70.9199999999996</v>
       </c>
       <c r="DN12" s="20">
-        <v>3986.66</v>
+        <v>4020.72</v>
       </c>
       <c r="DO12" s="19">
         <f>DP12-DN12</f>
-        <v>56.3400000000001</v>
+        <v>72.2000000000003</v>
       </c>
       <c r="DP12" s="20">
-        <v>4043</v>
+        <v>4092.92</v>
       </c>
       <c r="DQ12" s="20">
         <f>DR12-DP12</f>
-        <v>18.9099999999999</v>
+        <v>55.2699999999995</v>
       </c>
       <c r="DR12" s="20">
-        <v>4061.91</v>
+        <v>4148.19</v>
       </c>
       <c r="DS12" s="20">
         <f>DT12-DR12</f>
-        <v>55.6999999999998</v>
+        <v>43.1300000000001</v>
       </c>
       <c r="DT12" s="20">
-        <v>4117.61</v>
+        <v>4191.32</v>
       </c>
       <c r="DU12" s="20">
         <f>DV12-DT12</f>
-        <v>64.9300000000003</v>
+        <v>35.4400000000005</v>
       </c>
       <c r="DV12" s="20">
-        <v>4182.54</v>
+        <v>4226.76</v>
       </c>
       <c r="DW12" s="20">
         <f>DX12-DV12</f>
-        <v>32.5500000000002</v>
+        <v>48.6499999999996</v>
       </c>
       <c r="DX12" s="20">
-        <v>4215.09</v>
+        <v>4275.41</v>
       </c>
       <c r="DY12" s="20">
         <f>DZ12-DX12</f>
-        <v>26.0100000000002</v>
+        <v>36.1500000000005</v>
       </c>
       <c r="DZ12" s="20">
-        <v>4241.1</v>
+        <v>4311.56</v>
       </c>
       <c r="EA12" s="20">
         <f>EB12-DZ12</f>
-        <v>190.809999999999</v>
+        <v>58.4499999999998</v>
       </c>
       <c r="EB12" s="20">
-        <v>4431.91</v>
+        <v>4370.01</v>
       </c>
       <c r="EC12" s="20">
         <f>ED12-EB12</f>
-        <v>108.85</v>
+        <v>21.0799999999999</v>
       </c>
       <c r="ED12" s="20">
-        <v>4540.76</v>
+        <v>4391.09</v>
       </c>
       <c r="EE12" s="20">
         <f>EF12-ED12</f>
-        <v>63.2600000000002</v>
+        <v>52.8099999999995</v>
       </c>
       <c r="EF12" s="20">
-        <v>4604.02</v>
+        <v>4443.9</v>
       </c>
       <c r="EG12" s="20">
         <f>EH12-EF12</f>
-        <v>24.4399999999996</v>
+        <v>57.9300000000003</v>
       </c>
       <c r="EH12" s="20">
-        <v>4628.46</v>
+        <v>4501.83</v>
       </c>
       <c r="EI12" s="20">
         <f>EJ12-EH12</f>
-        <v>58.5199999999995</v>
+        <v>16.6900000000005</v>
       </c>
       <c r="EJ12" s="20">
-        <v>4686.98</v>
+        <v>4518.52</v>
       </c>
       <c r="EK12" s="20">
         <f>EL12-EJ12</f>
-        <v>34.5</v>
+        <v>36.5799999999999</v>
       </c>
       <c r="EL12" s="20">
-        <v>4721.48</v>
+        <v>4555.1</v>
       </c>
       <c r="EM12" s="20">
         <f>EN12-EL12</f>
-        <v>-59.7599999999993</v>
+        <v>46.9299999999994</v>
       </c>
       <c r="EN12" s="20">
-        <v>4661.72</v>
+        <v>4602.03</v>
       </c>
       <c r="EO12" s="20">
         <f>EP12-EN12</f>
-        <v>109.99</v>
+        <v>64.5799999999999</v>
       </c>
       <c r="EP12" s="20">
-        <v>4771.71</v>
+        <v>4666.61</v>
       </c>
       <c r="EQ12" s="20">
         <f>ER12-EP12</f>
-        <v>20.2299999999996</v>
+        <v>66.8299999999999</v>
       </c>
       <c r="ER12" s="20">
-        <v>4791.94</v>
+        <v>4733.44</v>
       </c>
       <c r="ES12" s="20">
         <f>ET12-ER12</f>
-        <v>22.1000000000004</v>
+        <v>75.2400000000007</v>
       </c>
       <c r="ET12" s="20">
-        <v>4814.04</v>
+        <v>4808.68</v>
       </c>
       <c r="EU12" s="20">
         <f>EV12-ET12</f>
-        <v>25.8800000000001</v>
+        <v>29.2599999999993</v>
       </c>
       <c r="EV12" s="20">
-        <v>4839.92</v>
-      </c>
-      <c r="EW12" s="19" t="s">
-        <v>122</v>
-      </c>
-      <c r="EX12" s="18">
-        <v>1571.92</v>
-      </c>
-      <c r="EY12" s="14" t="s">
+        <v>4837.94</v>
+      </c>
+      <c r="EW12" s="20">
+        <f>EX12-EV12</f>
+        <v>36.4700000000003</v>
+      </c>
+      <c r="EX12" s="20">
+        <v>4874.41</v>
+      </c>
+      <c r="EY12" s="19" t="s">
+        <v>125</v>
+      </c>
+      <c r="EZ12" s="18">
+        <v>1520.9</v>
+      </c>
+      <c r="FA12" s="14" t="s">
+        <v>108</v>
+      </c>
+      <c r="FB12" s="14">
+        <v>614.12</v>
+      </c>
+      <c r="FC12" s="1">
+        <v>25</v>
+      </c>
+      <c r="FD12" s="1">
+        <v>3</v>
+      </c>
+      <c r="FE12" s="1">
+        <v>100457</v>
+      </c>
+      <c r="FF12" s="9">
+        <f>2.43/(EX12/EZ12)</f>
+        <v>0.758201915719031</v>
+      </c>
+      <c r="FG12" s="9">
+        <f>BP12-D12</f>
+        <v>1572.99</v>
+      </c>
+      <c r="FH12" s="9">
+        <f>EX12-ER12</f>
+        <v>140.97</v>
+      </c>
+    </row>
+    <row r="13" spans="1:173">
+      <c r="A13" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="C13" s="2" t="s">
         <v>120</v>
       </c>
-      <c r="EZ12" s="14">
-        <v>645.48</v>
-      </c>
-      <c r="FA12" s="1">
-        <v>20</v>
-      </c>
-      <c r="FB12" s="1">
-        <v>3.2</v>
-      </c>
-      <c r="FC12" s="1">
-        <v>109106</v>
-      </c>
-      <c r="FD12" s="9">
-        <f>2.79/(EV12/EX12)</f>
-        <v>0.906142415577117</v>
-      </c>
-      <c r="FE12" s="9">
-        <f>BP12-D12</f>
-        <v>1368.34</v>
-      </c>
-    </row>
-    <row r="13" spans="1:171">
-      <c r="A13" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="B13" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="C13" s="2" t="s">
-        <v>117</v>
-      </c>
       <c r="D13" s="2">
-        <v>1156.57</v>
+        <v>1349.35</v>
       </c>
       <c r="E13" s="2">
         <f>F13-D13</f>
-        <v>40.4400000000001</v>
+        <v>49.6200000000001</v>
       </c>
       <c r="F13" s="2">
-        <v>1197.01</v>
+        <v>1398.97</v>
       </c>
       <c r="G13" s="2">
         <f>H13-F13</f>
-        <v>46.97</v>
+        <v>27.79</v>
       </c>
       <c r="H13" s="2">
-        <v>1243.98</v>
+        <v>1426.76</v>
       </c>
       <c r="I13" s="2">
         <f>J13-H13</f>
-        <v>58.49</v>
+        <v>29.02</v>
       </c>
       <c r="J13" s="2">
-        <v>1302.47</v>
+        <v>1455.78</v>
       </c>
       <c r="K13" s="2">
         <f>L13-J13</f>
-        <v>36.6399999999999</v>
+        <v>97.8800000000001</v>
       </c>
       <c r="L13" s="2">
-        <v>1339.11</v>
+        <v>1553.66</v>
       </c>
       <c r="M13" s="2">
         <f>N13-L13</f>
-        <v>33.99</v>
+        <v>42.3599999999999</v>
       </c>
       <c r="N13" s="2">
-        <v>1373.1</v>
+        <v>1596.02</v>
       </c>
       <c r="O13" s="2">
         <f>P13-N13</f>
-        <v>30.0600000000002</v>
+        <v>54.22</v>
       </c>
       <c r="P13" s="2">
-        <v>1403.16</v>
+        <v>1650.24</v>
       </c>
       <c r="Q13" s="2">
         <f>R13-P13</f>
-        <v>47.3</v>
+        <v>35.5899999999999</v>
       </c>
       <c r="R13" s="2">
-        <v>1450.46</v>
+        <v>1685.83</v>
       </c>
       <c r="S13" s="2">
         <f>T13-R13</f>
-        <v>46.8299999999999</v>
+        <v>68.1300000000001</v>
       </c>
       <c r="T13" s="2">
-        <v>1497.29</v>
+        <v>1753.96</v>
       </c>
       <c r="U13" s="2">
         <f>V13-T13</f>
-        <v>58.6500000000001</v>
+        <v>58.5599999999999</v>
       </c>
       <c r="V13" s="17">
-        <v>1555.94</v>
+        <v>1812.52</v>
       </c>
       <c r="W13" s="2">
         <f>X13-V13</f>
-        <v>70.3099999999999</v>
+        <v>67.21</v>
       </c>
       <c r="X13" s="17">
-        <v>1626.25</v>
+        <v>1879.73</v>
       </c>
       <c r="Y13" s="2">
         <f>Z13-X13</f>
-        <v>31.49</v>
+        <v>20.22</v>
       </c>
       <c r="Z13" s="2">
-        <v>1657.74</v>
+        <v>1899.95</v>
       </c>
       <c r="AA13" s="2">
         <f>AB13-Z13</f>
-        <v>59.21</v>
+        <v>35.0999999999999</v>
       </c>
       <c r="AB13" s="2">
-        <v>1716.95</v>
+        <v>1935.05</v>
       </c>
       <c r="AC13" s="2">
         <f>AD13-AB13</f>
-        <v>31.99</v>
+        <v>44.73</v>
       </c>
       <c r="AD13" s="2">
-        <v>1748.94</v>
+        <v>1979.78</v>
       </c>
       <c r="AE13" s="18">
         <f>AF13-AD13</f>
-        <v>52.0999999999999</v>
+        <v>31.1700000000001</v>
       </c>
       <c r="AF13" s="18">
-        <v>1801.04</v>
+        <v>2010.95</v>
       </c>
       <c r="AG13" s="18">
         <f>AH13-AF13</f>
-        <v>74.74</v>
+        <v>51.4100000000001</v>
       </c>
       <c r="AH13" s="18">
-        <v>1875.78</v>
+        <v>2062.36</v>
       </c>
       <c r="AI13" s="18">
         <f>AJ13-AH13</f>
-        <v>51.3700000000001</v>
+        <v>64.9899999999998</v>
       </c>
       <c r="AJ13" s="18">
-        <v>1927.15</v>
+        <v>2127.35</v>
       </c>
       <c r="AK13" s="18">
         <f>AL13-AJ13</f>
-        <v>58.48</v>
+        <v>21.6500000000001</v>
       </c>
       <c r="AL13" s="18">
-        <v>1985.63</v>
+        <v>2149</v>
       </c>
       <c r="AM13" s="18">
         <f>AN13-AL13</f>
-        <v>31.6599999999999</v>
+        <v>29.3899999999999</v>
       </c>
       <c r="AN13" s="18">
-        <v>2017.29</v>
+        <v>2178.39</v>
       </c>
       <c r="AO13" s="18">
         <f>AP13-AN13</f>
-        <v>53.0100000000002</v>
+        <v>28.6100000000001</v>
       </c>
       <c r="AP13" s="18">
-        <v>2070.3</v>
+        <v>2207</v>
       </c>
       <c r="AQ13" s="18">
         <f>AR13-AP13</f>
-        <v>52.5</v>
+        <v>17.4099999999999</v>
       </c>
       <c r="AR13" s="18">
-        <v>2122.8</v>
+        <v>2224.41</v>
       </c>
       <c r="AS13" s="18">
         <f>AT13-AR13</f>
-        <v>65.02</v>
+        <v>21.0700000000002</v>
       </c>
       <c r="AT13" s="18">
-        <v>2187.82</v>
+        <v>2245.48</v>
       </c>
       <c r="AU13" s="19">
         <f>AV13-AT13</f>
-        <v>39.3199999999997</v>
+        <v>94.73</v>
       </c>
       <c r="AV13" s="19">
-        <v>2227.14</v>
+        <v>2340.21</v>
       </c>
       <c r="AW13" s="20">
         <f>AX13-AV13</f>
-        <v>65.5799999999999</v>
+        <v>25.7199999999998</v>
       </c>
       <c r="AX13" s="20">
-        <v>2292.72</v>
+        <v>2365.93</v>
       </c>
       <c r="AY13" s="20">
         <f>AZ13-AX13</f>
-        <v>43.3800000000001</v>
+        <v>69.3800000000001</v>
       </c>
       <c r="AZ13" s="20">
-        <v>2336.1</v>
+        <v>2435.31</v>
       </c>
       <c r="BA13" s="20">
         <f>BB13-AZ13</f>
-        <v>56.0500000000002</v>
+        <v>48.79</v>
       </c>
       <c r="BB13" s="20">
-        <v>2392.15</v>
+        <v>2484.1</v>
       </c>
       <c r="BC13" s="20">
         <f>BD13-BB13</f>
-        <v>36.2999999999997</v>
+        <v>4.57999999999993</v>
       </c>
       <c r="BD13" s="20">
-        <v>2428.45</v>
+        <v>2488.68</v>
       </c>
       <c r="BE13" s="19">
         <f>BF13-BD13</f>
-        <v>49.8200000000002</v>
+        <v>42.2000000000003</v>
       </c>
       <c r="BF13" s="20">
-        <v>2478.27</v>
+        <v>2530.88</v>
       </c>
       <c r="BG13" s="20">
         <f>BH13-BF13</f>
-        <v>65.7800000000002</v>
+        <v>24.9400000000001</v>
       </c>
       <c r="BH13" s="20">
-        <v>2544.05</v>
+        <v>2555.82</v>
       </c>
       <c r="BI13" s="20">
         <f>BJ13-BH13</f>
-        <v>16.29</v>
+        <v>52.77</v>
       </c>
       <c r="BJ13" s="20">
-        <v>2560.34</v>
+        <v>2608.59</v>
       </c>
       <c r="BK13" s="20">
         <f>BL13-BJ13</f>
-        <v>84.4099999999999</v>
+        <v>55.8799999999997</v>
       </c>
       <c r="BL13" s="20">
-        <v>2644.75</v>
+        <v>2664.47</v>
       </c>
       <c r="BM13" s="20">
         <f>BN13-BL13</f>
-        <v>33.6599999999999</v>
+        <v>21.2000000000003</v>
       </c>
       <c r="BN13" s="20">
-        <v>2678.41</v>
+        <v>2685.67</v>
       </c>
       <c r="BO13" s="20">
         <f>BP13-BN13</f>
-        <v>51.1500000000001</v>
+        <v>32.02</v>
       </c>
       <c r="BP13" s="20">
-        <v>2729.56</v>
+        <v>2717.69</v>
       </c>
       <c r="BQ13" s="20">
         <f>BR13-BP13</f>
-        <v>50.8299999999999</v>
+        <v>24.5999999999999</v>
       </c>
       <c r="BR13" s="20">
-        <v>2780.39</v>
+        <v>2742.29</v>
       </c>
       <c r="BS13" s="20">
         <f>BT13-BR13</f>
-        <v>33.9300000000003</v>
+        <v>14.79</v>
       </c>
       <c r="BT13" s="20">
-        <v>2814.32</v>
+        <v>2757.08</v>
       </c>
       <c r="BU13" s="20">
         <f>BV13-BT13</f>
-        <v>43.9400000000001</v>
+        <v>70.6700000000001</v>
       </c>
       <c r="BV13" s="20">
-        <v>2858.26</v>
+        <v>2827.75</v>
       </c>
       <c r="BW13" s="20">
         <f>BX13-BV13</f>
-        <v>47.4199999999996</v>
+        <v>56.4400000000001</v>
       </c>
       <c r="BX13" s="20">
-        <v>2905.68</v>
+        <v>2884.19</v>
       </c>
       <c r="BY13" s="20">
         <f>BZ13-BX13</f>
-        <v>51.02</v>
+        <v>33.4200000000001</v>
       </c>
       <c r="BZ13" s="20">
-        <v>2956.7</v>
+        <v>2917.61</v>
       </c>
       <c r="CA13" s="20">
         <f>CB13-BZ13</f>
-        <v>67.3400000000001</v>
+        <v>57.9000000000001</v>
       </c>
       <c r="CB13" s="20">
-        <v>3024.04</v>
+        <v>2975.51</v>
       </c>
       <c r="CC13" s="20">
         <f>CD13-CB13</f>
-        <v>59.4200000000001</v>
+        <v>90.8599999999997</v>
       </c>
       <c r="CD13" s="20">
-        <v>3083.46</v>
+        <v>3066.37</v>
       </c>
       <c r="CE13" s="20">
         <f>CF13-CD13</f>
-        <v>49.1900000000001</v>
+        <v>161.05</v>
       </c>
       <c r="CF13" s="20">
-        <v>3132.65</v>
+        <v>3227.42</v>
       </c>
       <c r="CG13" s="20">
         <f>CH13-CF13</f>
-        <v>46.54</v>
+        <v>36.6700000000001</v>
       </c>
       <c r="CH13" s="20">
-        <v>3179.19</v>
+        <v>3264.09</v>
       </c>
       <c r="CI13" s="20">
         <f>CJ13-CH13</f>
-        <v>23.3600000000001</v>
+        <v>72.0899999999997</v>
       </c>
       <c r="CJ13" s="20">
-        <v>3202.55</v>
+        <v>3336.18</v>
       </c>
       <c r="CK13" s="20">
         <f>CL13-CJ13</f>
-        <v>39.1199999999999</v>
+        <v>32.7800000000002</v>
       </c>
       <c r="CL13" s="20">
-        <v>3241.67</v>
+        <v>3368.96</v>
       </c>
       <c r="CM13" s="20">
         <f>CN13-CL13</f>
-        <v>57.2199999999998</v>
+        <v>40.8299999999999</v>
       </c>
       <c r="CN13" s="20">
-        <v>3298.89</v>
+        <v>3409.79</v>
       </c>
       <c r="CO13" s="20">
         <f>CP13-CN13</f>
-        <v>48.46</v>
+        <v>23.02</v>
       </c>
       <c r="CP13" s="20">
-        <v>3347.35</v>
+        <v>3432.81</v>
       </c>
       <c r="CQ13" s="20">
         <f>CR13-CP13</f>
-        <v>37.0799999999999</v>
+        <v>43.9500000000003</v>
       </c>
       <c r="CR13" s="20">
-        <v>3384.43</v>
+        <v>3476.76</v>
       </c>
       <c r="CS13" s="20">
         <f>CT13-CR13</f>
-        <v>144.73</v>
+        <v>76</v>
       </c>
       <c r="CT13" s="20">
-        <v>3529.16</v>
+        <v>3552.76</v>
       </c>
       <c r="CU13" s="20">
         <f>CV13-CT13</f>
-        <v>38.7400000000002</v>
+        <v>40.6499999999996</v>
       </c>
       <c r="CV13" s="20">
-        <v>3567.9</v>
+        <v>3593.41</v>
       </c>
       <c r="CW13" s="19">
         <f>CX13-CV13</f>
-        <v>62.7399999999998</v>
+        <v>34.1300000000001</v>
       </c>
       <c r="CX13" s="20">
-        <v>3630.64</v>
+        <v>3627.54</v>
       </c>
       <c r="CY13" s="20">
         <f>CZ13-CX13</f>
-        <v>36.1200000000003</v>
+        <v>63.5599999999999</v>
       </c>
       <c r="CZ13" s="20">
-        <v>3666.76</v>
+        <v>3691.1</v>
       </c>
       <c r="DA13" s="20">
         <f>DB13-CZ13</f>
-        <v>36.7299999999996</v>
+        <v>43.3800000000001</v>
       </c>
       <c r="DB13" s="20">
-        <v>3703.49</v>
+        <v>3734.48</v>
       </c>
       <c r="DC13" s="20">
         <f>DD13-DB13</f>
-        <v>53.7700000000004</v>
+        <v>57.9699999999998</v>
       </c>
       <c r="DD13" s="20">
-        <v>3757.26</v>
+        <v>3792.45</v>
       </c>
       <c r="DE13" s="20">
         <f>DF13-DD13</f>
-        <v>59.2099999999996</v>
+        <v>53.6100000000001</v>
       </c>
       <c r="DF13" s="20">
-        <v>3816.47</v>
+        <v>3846.06</v>
       </c>
       <c r="DG13" s="20">
         <f>DH13-DF13</f>
-        <v>25.75</v>
+        <v>32.0900000000001</v>
       </c>
       <c r="DH13" s="20">
-        <v>3842.22</v>
+        <v>3878.15</v>
       </c>
       <c r="DI13" s="20">
         <f>DJ13-DH13</f>
-        <v>61.21</v>
+        <v>50.4299999999998</v>
       </c>
       <c r="DJ13" s="20">
-        <v>3903.43</v>
+        <v>3928.58</v>
       </c>
       <c r="DK13" s="20">
         <f>DL13-DJ13</f>
-        <v>46.3700000000003</v>
+        <v>22.9500000000003</v>
       </c>
       <c r="DL13" s="20">
-        <v>3949.8</v>
+        <v>3951.53</v>
       </c>
       <c r="DM13" s="20">
         <f>DN13-DL13</f>
-        <v>70.9199999999996</v>
+        <v>35.1299999999997</v>
       </c>
       <c r="DN13" s="20">
-        <v>4020.72</v>
+        <v>3986.66</v>
       </c>
       <c r="DO13" s="19">
         <f>DP13-DN13</f>
-        <v>72.2000000000003</v>
+        <v>56.3400000000001</v>
       </c>
       <c r="DP13" s="20">
-        <v>4092.92</v>
+        <v>4043</v>
       </c>
       <c r="DQ13" s="20">
         <f>DR13-DP13</f>
-        <v>55.2699999999995</v>
+        <v>18.9099999999999</v>
       </c>
       <c r="DR13" s="20">
-        <v>4148.19</v>
+        <v>4061.91</v>
       </c>
       <c r="DS13" s="20">
         <f>DT13-DR13</f>
-        <v>43.1300000000001</v>
+        <v>55.6999999999998</v>
       </c>
       <c r="DT13" s="20">
-        <v>4191.32</v>
+        <v>4117.61</v>
       </c>
       <c r="DU13" s="20">
         <f>DV13-DT13</f>
-        <v>35.4400000000005</v>
+        <v>64.9300000000003</v>
       </c>
       <c r="DV13" s="20">
-        <v>4226.76</v>
+        <v>4182.54</v>
       </c>
       <c r="DW13" s="20">
         <f>DX13-DV13</f>
-        <v>48.6499999999996</v>
+        <v>32.5500000000002</v>
       </c>
       <c r="DX13" s="20">
-        <v>4275.41</v>
+        <v>4215.09</v>
       </c>
       <c r="DY13" s="20">
         <f>DZ13-DX13</f>
-        <v>36.1500000000005</v>
+        <v>26.0100000000002</v>
       </c>
       <c r="DZ13" s="20">
-        <v>4311.56</v>
+        <v>4241.1</v>
       </c>
       <c r="EA13" s="20">
         <f>EB13-DZ13</f>
-        <v>58.4499999999998</v>
+        <v>190.809999999999</v>
       </c>
       <c r="EB13" s="20">
-        <v>4370.01</v>
+        <v>4431.91</v>
       </c>
       <c r="EC13" s="20">
         <f>ED13-EB13</f>
-        <v>21.0799999999999</v>
+        <v>108.85</v>
       </c>
       <c r="ED13" s="20">
-        <v>4391.09</v>
+        <v>4540.76</v>
       </c>
       <c r="EE13" s="20">
         <f>EF13-ED13</f>
-        <v>52.8099999999995</v>
+        <v>63.2600000000002</v>
       </c>
       <c r="EF13" s="20">
-        <v>4443.9</v>
+        <v>4604.02</v>
       </c>
       <c r="EG13" s="20">
         <f>EH13-EF13</f>
-        <v>57.9300000000003</v>
+        <v>24.4399999999996</v>
       </c>
       <c r="EH13" s="20">
-        <v>4501.83</v>
+        <v>4628.46</v>
       </c>
       <c r="EI13" s="20">
         <f>EJ13-EH13</f>
-        <v>16.6900000000005</v>
+        <v>58.5199999999995</v>
       </c>
       <c r="EJ13" s="20">
-        <v>4518.52</v>
+        <v>4686.98</v>
       </c>
       <c r="EK13" s="20">
         <f>EL13-EJ13</f>
-        <v>36.5799999999999</v>
+        <v>34.5</v>
       </c>
       <c r="EL13" s="20">
-        <v>4555.1</v>
+        <v>4721.48</v>
       </c>
       <c r="EM13" s="20">
         <f>EN13-EL13</f>
-        <v>46.9299999999994</v>
+        <v>-59.7599999999993</v>
       </c>
       <c r="EN13" s="20">
-        <v>4602.03</v>
+        <v>4661.72</v>
       </c>
       <c r="EO13" s="20">
         <f>EP13-EN13</f>
-        <v>64.5799999999999</v>
+        <v>109.99</v>
       </c>
       <c r="EP13" s="20">
-        <v>4666.61</v>
+        <v>4771.71</v>
       </c>
       <c r="EQ13" s="20">
         <f>ER13-EP13</f>
-        <v>66.8299999999999</v>
+        <v>20.2299999999996</v>
       </c>
       <c r="ER13" s="20">
-        <v>4733.44</v>
+        <v>4791.94</v>
       </c>
       <c r="ES13" s="20">
         <f>ET13-ER13</f>
-        <v>75.2400000000007</v>
+        <v>22.1000000000004</v>
       </c>
       <c r="ET13" s="20">
-        <v>4808.68</v>
+        <v>4814.04</v>
       </c>
       <c r="EU13" s="20">
         <f>EV13-ET13</f>
-        <v>29.2599999999993</v>
+        <v>25.8800000000001</v>
       </c>
       <c r="EV13" s="20">
-        <v>4837.94</v>
-      </c>
-      <c r="EW13" s="19" t="s">
-        <v>124</v>
-      </c>
-      <c r="EX13" s="18">
-        <v>1518.55</v>
-      </c>
-      <c r="EY13" s="14" t="s">
-        <v>105</v>
-      </c>
-      <c r="EZ13" s="14">
-        <v>614.12</v>
-      </c>
-      <c r="FA13" s="1">
-        <v>25</v>
-      </c>
-      <c r="FB13" s="1">
-        <v>3</v>
+        <v>4839.92</v>
+      </c>
+      <c r="EW13" s="20">
+        <f>EX13-EV13</f>
+        <v>11.0100000000002</v>
+      </c>
+      <c r="EX13" s="20">
+        <v>4850.93</v>
+      </c>
+      <c r="EY13" s="19" t="s">
+        <v>127</v>
+      </c>
+      <c r="EZ13" s="18">
+        <v>1571.12</v>
+      </c>
+      <c r="FA13" s="14" t="s">
+        <v>123</v>
+      </c>
+      <c r="FB13" s="14">
+        <v>645.48</v>
       </c>
       <c r="FC13" s="1">
-        <v>100457</v>
-      </c>
-      <c r="FD13" s="9">
-        <f>2.79/(EV13/EX13)</f>
-        <v>0.875735230283964</v>
-      </c>
-      <c r="FE13" s="9">
+        <v>20</v>
+      </c>
+      <c r="FD13" s="1">
+        <v>3.2</v>
+      </c>
+      <c r="FE13" s="1">
+        <v>109106</v>
+      </c>
+      <c r="FF13" s="9">
+        <f>2.43/(EX13/EZ13)</f>
+        <v>0.787028796540045</v>
+      </c>
+      <c r="FG13" s="9">
         <f>BP13-D13</f>
-        <v>1572.99</v>
+        <v>1368.34</v>
+      </c>
+      <c r="FH13" s="9">
+        <f>EX13-ER13</f>
+        <v>58.9900000000007</v>
       </c>
     </row>
-    <row r="14" spans="1:171">
+    <row r="14" spans="1:173">
       <c r="A14" s="2" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="D14" s="2">
         <v>907.94</v>
@@ -9577,45 +9725,56 @@
       <c r="EV14" s="20">
         <v>4310.83</v>
       </c>
-      <c r="EW14" s="19" t="s">
-        <v>126</v>
-      </c>
-      <c r="EX14" s="18">
-        <v>1317.26</v>
-      </c>
-      <c r="EY14" s="18" t="s">
-        <v>127</v>
+      <c r="EW14" s="20">
+        <f>EX14-EV14</f>
+        <v>77.1300000000001</v>
+      </c>
+      <c r="EX14" s="20">
+        <v>4387.96</v>
+      </c>
+      <c r="EY14" s="19" t="s">
+        <v>129</v>
       </c>
       <c r="EZ14" s="18">
+        <v>1474.27</v>
+      </c>
+      <c r="FA14" s="18" t="s">
+        <v>130</v>
+      </c>
+      <c r="FB14" s="18">
         <v>628.67</v>
       </c>
-      <c r="FA14" s="2">
+      <c r="FC14" s="2">
         <v>35</v>
       </c>
-      <c r="FB14" s="2">
+      <c r="FD14" s="2">
         <v>8.2</v>
       </c>
-      <c r="FC14" s="2">
+      <c r="FE14" s="2">
         <v>65285</v>
       </c>
-      <c r="FD14" s="9">
-        <f>2.79/(EV14/EX14)</f>
-        <v>0.85254009088737</v>
-      </c>
-      <c r="FE14" s="9">
+      <c r="FF14" s="9">
+        <f>2.43/(EX14/EZ14)</f>
+        <v>0.816433171678867</v>
+      </c>
+      <c r="FG14" s="9">
         <f>BP14-D14</f>
         <v>1361.61</v>
       </c>
+      <c r="FH14" s="9">
+        <f>EX14-ER14</f>
+        <v>187.36</v>
+      </c>
     </row>
-    <row r="15" spans="1:171">
+    <row r="15" spans="1:173">
       <c r="A15" s="2" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="D15" s="2">
         <v>953.78</v>
@@ -10138,45 +10297,56 @@
       <c r="EV15" s="20">
         <v>4129.86</v>
       </c>
-      <c r="EW15" s="19" t="s">
-        <v>97</v>
-      </c>
-      <c r="EX15" s="18">
-        <v>1629.87</v>
-      </c>
-      <c r="EY15" s="18" t="s">
-        <v>112</v>
+      <c r="EW15" s="20">
+        <f>EX15-EV15</f>
+        <v>95.2600000000002</v>
+      </c>
+      <c r="EX15" s="20">
+        <v>4225.12</v>
+      </c>
+      <c r="EY15" s="19" t="s">
+        <v>100</v>
       </c>
       <c r="EZ15" s="18">
+        <v>1746.97</v>
+      </c>
+      <c r="FA15" s="18" t="s">
+        <v>115</v>
+      </c>
+      <c r="FB15" s="18">
         <v>758.25</v>
       </c>
-      <c r="FA15" s="2">
+      <c r="FC15" s="2">
         <v>30</v>
       </c>
-      <c r="FB15" s="2">
+      <c r="FD15" s="2">
         <v>1</v>
       </c>
-      <c r="FC15" s="2">
+      <c r="FE15" s="2">
         <v>105419</v>
       </c>
-      <c r="FD15" s="9">
-        <f>2.79/(EV15/EX15)</f>
-        <v>1.10108751870523</v>
-      </c>
-      <c r="FE15" s="9">
+      <c r="FF15" s="9">
+        <f>2.43/(EX15/EZ15)</f>
+        <v>1.00473764058772</v>
+      </c>
+      <c r="FG15" s="9">
         <f>BP15-D15</f>
         <v>1446.26</v>
       </c>
+      <c r="FH15" s="9">
+        <f>EX15-ER15</f>
+        <v>162.89</v>
+      </c>
     </row>
-    <row r="16" spans="1:171">
+    <row r="16" spans="1:173">
       <c r="A16" s="2" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="D16" s="2">
         <v>950.09</v>
@@ -10699,45 +10869,56 @@
       <c r="EV16" s="20">
         <v>3944.48</v>
       </c>
-      <c r="EW16" s="19" t="s">
-        <v>133</v>
-      </c>
-      <c r="EX16" s="18">
-        <v>1556.36</v>
-      </c>
-      <c r="EY16" s="18" t="s">
-        <v>134</v>
+      <c r="EW16" s="20">
+        <f>EX16-EV16</f>
+        <v>20.2399999999998</v>
+      </c>
+      <c r="EX16" s="20">
+        <v>3964.72</v>
+      </c>
+      <c r="EY16" s="19" t="s">
+        <v>136</v>
       </c>
       <c r="EZ16" s="18">
+        <v>1560.36</v>
+      </c>
+      <c r="FA16" s="18" t="s">
+        <v>137</v>
+      </c>
+      <c r="FB16" s="18">
         <v>704.28</v>
       </c>
-      <c r="FA16" s="2">
+      <c r="FC16" s="2">
         <v>10</v>
       </c>
-      <c r="FB16" s="2">
+      <c r="FD16" s="2">
         <v>2.2</v>
       </c>
-      <c r="FC16" s="2">
+      <c r="FE16" s="2">
         <v>86194</v>
       </c>
-      <c r="FD16" s="9">
-        <f>2.79/(EV16/EX16)</f>
-        <v>1.10084076988602</v>
-      </c>
-      <c r="FE16" s="9">
+      <c r="FF16" s="9">
+        <f>2.43/(EX16/EZ16)</f>
+        <v>0.956353739986682</v>
+      </c>
+      <c r="FG16" s="9">
         <f>BP16-D16</f>
         <v>1143.19</v>
       </c>
+      <c r="FH16" s="9">
+        <f>EX16-ER16</f>
+        <v>152.52</v>
+      </c>
     </row>
-    <row r="17" spans="1:161">
+    <row r="17" spans="1:164">
       <c r="A17" s="2" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="D17" s="2"/>
       <c r="E17" s="2"/>
@@ -11160,39 +11341,50 @@
       <c r="EV17" s="20">
         <v>3736.04</v>
       </c>
-      <c r="EW17" s="19" t="s">
-        <v>136</v>
-      </c>
-      <c r="EX17" s="18">
-        <v>1073.85</v>
-      </c>
-      <c r="EY17" s="18" t="s">
-        <v>134</v>
+      <c r="EW17" s="20">
+        <f>EX17-EV17</f>
+        <v>173.68</v>
+      </c>
+      <c r="EX17" s="20">
+        <v>3909.72</v>
+      </c>
+      <c r="EY17" s="19" t="s">
+        <v>139</v>
       </c>
       <c r="EZ17" s="18">
+        <v>1074.57</v>
+      </c>
+      <c r="FA17" s="18" t="s">
+        <v>137</v>
+      </c>
+      <c r="FB17" s="18">
         <v>304.12</v>
       </c>
-      <c r="FA17" s="2"/>
-      <c r="FB17" s="2"/>
       <c r="FC17" s="2"/>
-      <c r="FD17" s="9">
-        <f>2.79/(EV17/EX17)</f>
-        <v>0.801929717026584</v>
-      </c>
-      <c r="FE17" s="9">
+      <c r="FD17" s="2"/>
+      <c r="FE17" s="2"/>
+      <c r="FF17" s="9">
+        <f>2.43/(EX17/EZ17)</f>
+        <v>0.667875218685737</v>
+      </c>
+      <c r="FG17" s="9">
         <f>BP17-D17</f>
         <v>1776.78</v>
       </c>
+      <c r="FH17" s="9">
+        <f>EX17-ER17</f>
+        <v>474.88</v>
+      </c>
     </row>
-    <row r="18" spans="1:161">
+    <row r="18" spans="1:164">
       <c r="A18" s="2" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="D18" s="2"/>
       <c r="E18" s="2"/>
@@ -11615,39 +11807,50 @@
       <c r="EV18" s="20">
         <v>3691.31</v>
       </c>
-      <c r="EW18" s="19" t="s">
-        <v>139</v>
-      </c>
-      <c r="EX18" s="18">
-        <v>884.52</v>
-      </c>
-      <c r="EY18" s="18" t="s">
-        <v>120</v>
+      <c r="EW18" s="20">
+        <f>EX18-EV18</f>
+        <v>18.6199999999999</v>
+      </c>
+      <c r="EX18" s="20">
+        <v>3709.93</v>
+      </c>
+      <c r="EY18" s="19" t="s">
+        <v>142</v>
       </c>
       <c r="EZ18" s="18">
+        <v>880.72</v>
+      </c>
+      <c r="FA18" s="18" t="s">
+        <v>123</v>
+      </c>
+      <c r="FB18" s="18">
         <v>490.62</v>
       </c>
-      <c r="FA18" s="2"/>
-      <c r="FB18" s="2"/>
       <c r="FC18" s="2"/>
-      <c r="FD18" s="9">
-        <f>2.79/(EV18/EX18)</f>
-        <v>0.668546071719796</v>
-      </c>
-      <c r="FE18" s="9">
+      <c r="FD18" s="2"/>
+      <c r="FE18" s="2"/>
+      <c r="FF18" s="9">
+        <f>2.43/(EX18/EZ18)</f>
+        <v>0.576870614809444</v>
+      </c>
+      <c r="FG18" s="9">
         <f>BP18-D18</f>
         <v>2634.73</v>
       </c>
+      <c r="FH18" s="9">
+        <f>EX18-ER18</f>
+        <v>86.1999999999998</v>
+      </c>
     </row>
-    <row r="19" spans="1:161">
+    <row r="19" spans="1:164">
       <c r="A19" s="2" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="D19" s="2"/>
       <c r="E19" s="2"/>
@@ -12070,1889 +12273,1944 @@
       <c r="EV19" s="20">
         <v>3501.03</v>
       </c>
-      <c r="EW19" s="19" t="s">
-        <v>126</v>
-      </c>
-      <c r="EX19" s="18">
+      <c r="EW19" s="20">
+        <f>EX19-EV19</f>
+        <v>45.0899999999997</v>
+      </c>
+      <c r="EX19" s="20">
+        <v>3546.12</v>
+      </c>
+      <c r="EY19" s="19" t="s">
+        <v>129</v>
+      </c>
+      <c r="EZ19" s="18">
         <v>573.21</v>
       </c>
-      <c r="EY19" s="18" t="s">
-        <v>120</v>
-      </c>
-      <c r="EZ19" s="18">
+      <c r="FA19" s="18" t="s">
+        <v>123</v>
+      </c>
+      <c r="FB19" s="18">
         <v>303.44</v>
       </c>
-      <c r="FA19" s="2"/>
-      <c r="FB19" s="2"/>
       <c r="FC19" s="2"/>
-      <c r="FD19" s="9">
-        <f>2.79/(EV19/EX19)</f>
-        <v>0.456795828656138</v>
-      </c>
-      <c r="FE19" s="9">
+      <c r="FD19" s="2"/>
+      <c r="FE19" s="2"/>
+      <c r="FF19" s="9">
+        <f>2.43/(EX19/EZ19)</f>
+        <v>0.392795590673751</v>
+      </c>
+      <c r="FG19" s="9">
         <f>BP19-D19</f>
         <v>1817.1</v>
       </c>
+      <c r="FH19" s="9">
+        <f>EX19-ER19</f>
+        <v>163.48</v>
+      </c>
     </row>
-    <row r="20" spans="1:161">
-      <c r="A20" s="8" t="s">
-        <v>102</v>
-      </c>
-      <c r="B20" s="8" t="s">
-        <v>142</v>
-      </c>
-      <c r="C20" s="8" t="s">
-        <v>117</v>
-      </c>
-      <c r="D20" s="8"/>
-      <c r="E20" s="8"/>
-      <c r="F20" s="8"/>
-      <c r="G20" s="8"/>
-      <c r="H20" s="8"/>
-      <c r="I20" s="8"/>
-      <c r="J20" s="8"/>
-      <c r="K20" s="8"/>
-      <c r="L20" s="8"/>
-      <c r="M20" s="8"/>
-      <c r="N20" s="8"/>
-      <c r="O20" s="8"/>
-      <c r="P20" s="8"/>
-      <c r="Q20" s="8"/>
-      <c r="R20" s="8"/>
-      <c r="S20" s="8"/>
-      <c r="T20" s="8"/>
-      <c r="U20" s="8"/>
-      <c r="V20" s="21"/>
-      <c r="W20" s="8"/>
-      <c r="X20" s="21"/>
-      <c r="Y20" s="8"/>
-      <c r="Z20" s="8"/>
-      <c r="AA20" s="8"/>
-      <c r="AB20" s="8"/>
-      <c r="AC20" s="8"/>
-      <c r="AD20" s="8"/>
-      <c r="AE20" s="22"/>
-      <c r="AF20" s="22"/>
-      <c r="AG20" s="22"/>
-      <c r="AH20" s="22"/>
-      <c r="AI20" s="22"/>
-      <c r="AJ20" s="22"/>
-      <c r="AK20" s="22"/>
-      <c r="AL20" s="22"/>
-      <c r="AM20" s="22"/>
-      <c r="AN20" s="22"/>
-      <c r="AO20" s="22"/>
-      <c r="AP20" s="22"/>
-      <c r="AQ20" s="22"/>
-      <c r="AR20" s="22">
-        <v>1644.57</v>
-      </c>
-      <c r="AS20" s="22">
-        <f>AT20-AR20</f>
+    <row r="20" spans="1:164">
+      <c r="A20" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="D20" s="2"/>
+      <c r="E20" s="2"/>
+      <c r="F20" s="2"/>
+      <c r="G20" s="2"/>
+      <c r="H20" s="2"/>
+      <c r="I20" s="2"/>
+      <c r="J20" s="2"/>
+      <c r="K20" s="2"/>
+      <c r="L20" s="2"/>
+      <c r="M20" s="2"/>
+      <c r="N20" s="2"/>
+      <c r="O20" s="2"/>
+      <c r="P20" s="2"/>
+      <c r="Q20" s="2"/>
+      <c r="R20" s="2"/>
+      <c r="S20" s="2"/>
+      <c r="T20" s="2"/>
+      <c r="U20" s="2"/>
+      <c r="V20" s="17"/>
+      <c r="W20" s="2"/>
+      <c r="X20" s="17"/>
+      <c r="Y20" s="2"/>
+      <c r="Z20" s="2"/>
+      <c r="AA20" s="2"/>
+      <c r="AB20" s="2"/>
+      <c r="AC20" s="2"/>
+      <c r="AD20" s="2"/>
+      <c r="AE20" s="18"/>
+      <c r="AF20" s="18"/>
+      <c r="AG20" s="18"/>
+      <c r="AH20" s="18"/>
+      <c r="AI20" s="18"/>
+      <c r="AJ20" s="18"/>
+      <c r="AK20" s="18"/>
+      <c r="AL20" s="18"/>
+      <c r="AM20" s="18"/>
+      <c r="AN20" s="18"/>
+      <c r="AO20" s="18"/>
+      <c r="AP20" s="18"/>
+      <c r="AQ20" s="18"/>
+      <c r="AR20" s="18"/>
+      <c r="AS20" s="18"/>
+      <c r="AT20" s="18"/>
+      <c r="AU20" s="19"/>
+      <c r="AV20" s="19"/>
+      <c r="AW20" s="20"/>
+      <c r="AX20" s="20"/>
+      <c r="AY20" s="20"/>
+      <c r="AZ20" s="20"/>
+      <c r="BA20" s="20"/>
+      <c r="BB20" s="20"/>
+      <c r="BC20" s="20"/>
+      <c r="BD20" s="20"/>
+      <c r="BE20" s="19"/>
+      <c r="BF20" s="20"/>
+      <c r="BG20" s="20"/>
+      <c r="BH20" s="20"/>
+      <c r="BI20" s="20"/>
+      <c r="BJ20" s="20"/>
+      <c r="BK20" s="20"/>
+      <c r="BL20" s="20"/>
+      <c r="BM20" s="20"/>
+      <c r="BN20" s="20"/>
+      <c r="BO20" s="20"/>
+      <c r="BP20" s="20"/>
+      <c r="BQ20" s="20"/>
+      <c r="BR20" s="20"/>
+      <c r="BS20" s="20"/>
+      <c r="BT20" s="20"/>
+      <c r="BU20" s="20"/>
+      <c r="BV20" s="20"/>
+      <c r="BW20" s="20"/>
+      <c r="BX20" s="20"/>
+      <c r="BY20" s="20"/>
+      <c r="BZ20" s="20"/>
+      <c r="CA20" s="20"/>
+      <c r="CB20" s="20"/>
+      <c r="CC20" s="20"/>
+      <c r="CD20" s="20"/>
+      <c r="CE20" s="20"/>
+      <c r="CF20" s="20"/>
+      <c r="CG20" s="20"/>
+      <c r="CH20" s="20"/>
+      <c r="CI20" s="20"/>
+      <c r="CJ20" s="20"/>
+      <c r="CK20" s="20"/>
+      <c r="CL20" s="20"/>
+      <c r="CM20" s="20"/>
+      <c r="CN20" s="20"/>
+      <c r="CO20" s="20"/>
+      <c r="CP20" s="20"/>
+      <c r="CQ20" s="20"/>
+      <c r="CR20" s="20"/>
+      <c r="CS20" s="20"/>
+      <c r="CT20" s="20"/>
+      <c r="CU20" s="20"/>
+      <c r="CV20" s="20"/>
+      <c r="CW20" s="19"/>
+      <c r="CX20" s="20"/>
+      <c r="CY20" s="20"/>
+      <c r="CZ20" s="20"/>
+      <c r="DA20" s="20"/>
+      <c r="DB20" s="20"/>
+      <c r="DC20" s="20"/>
+      <c r="DD20" s="20"/>
+      <c r="DE20" s="20"/>
+      <c r="DF20" s="20"/>
+      <c r="DG20" s="20"/>
+      <c r="DH20" s="20"/>
+      <c r="DI20" s="20"/>
+      <c r="DJ20" s="20">
+        <v>2158.34</v>
+      </c>
+      <c r="DK20" s="20">
+        <f>DL20-DJ20</f>
         <v>0</v>
       </c>
-      <c r="AT20" s="22">
-        <v>1644.57</v>
-      </c>
-      <c r="AU20" s="23">
-        <f>AV20-AT20</f>
-        <v>31.0700000000002</v>
-      </c>
-      <c r="AV20" s="23">
-        <v>1675.64</v>
-      </c>
-      <c r="AW20" s="24">
-        <f>AX20-AV20</f>
-        <v>13.9599999999998</v>
-      </c>
-      <c r="AX20" s="24">
-        <v>1689.6</v>
-      </c>
-      <c r="AY20" s="24">
-        <f>AZ20-AX20</f>
-        <v>44.99</v>
-      </c>
-      <c r="AZ20" s="24">
-        <v>1734.59</v>
-      </c>
-      <c r="BA20" s="24">
-        <f>BB20-AZ20</f>
-        <v>31.1600000000001</v>
-      </c>
-      <c r="BB20" s="24">
-        <v>1765.75</v>
-      </c>
-      <c r="BC20" s="24">
-        <f>BD20-BB20</f>
-        <v>39.9200000000001</v>
-      </c>
-      <c r="BD20" s="24">
-        <v>1805.67</v>
-      </c>
-      <c r="BE20" s="23">
-        <f>BF20-BD20</f>
-        <v>42.21</v>
-      </c>
-      <c r="BF20" s="24">
-        <v>1847.88</v>
-      </c>
-      <c r="BG20" s="24">
-        <f>BH20-BF20</f>
-        <v>86</v>
-      </c>
-      <c r="BH20" s="24">
-        <v>1933.88</v>
-      </c>
-      <c r="BI20" s="24">
-        <f>BJ20-BH20</f>
-        <v>21.8499999999999</v>
-      </c>
-      <c r="BJ20" s="24">
-        <v>1955.73</v>
-      </c>
-      <c r="BK20" s="24">
-        <f>BL20-BJ20</f>
-        <v>26.3099999999999</v>
-      </c>
-      <c r="BL20" s="24">
-        <v>1982.04</v>
-      </c>
-      <c r="BM20" s="24">
-        <f>BN20-BL20</f>
-        <v>26.51</v>
-      </c>
-      <c r="BN20" s="24">
-        <v>2008.55</v>
-      </c>
-      <c r="BO20" s="24">
-        <f>BP20-BN20</f>
-        <v>20.71</v>
-      </c>
-      <c r="BP20" s="24">
-        <v>2029.26</v>
-      </c>
-      <c r="BQ20" s="24">
-        <f>BR20-BP20</f>
-        <v>63.0800000000002</v>
-      </c>
-      <c r="BR20" s="24">
-        <v>2092.34</v>
-      </c>
-      <c r="BS20" s="24">
-        <f>BT20-BR20</f>
-        <v>4.29999999999973</v>
-      </c>
-      <c r="BT20" s="24">
-        <v>2096.64</v>
-      </c>
-      <c r="BU20" s="24">
-        <f>BV20-BT20</f>
-        <v>0.720000000000255</v>
-      </c>
-      <c r="BV20" s="24">
-        <v>2097.36</v>
-      </c>
-      <c r="BW20" s="24">
-        <f>BX20-BV20</f>
+      <c r="DL20" s="20">
+        <v>2158.34</v>
+      </c>
+      <c r="DM20" s="20">
+        <f>DN20-DL20</f>
+        <v>55.6999999999998</v>
+      </c>
+      <c r="DN20" s="20">
+        <v>2214.04</v>
+      </c>
+      <c r="DO20" s="19">
+        <f>DP20-DN20</f>
+        <v>21.9099999999999</v>
+      </c>
+      <c r="DP20" s="20">
+        <v>2235.95</v>
+      </c>
+      <c r="DQ20" s="20">
+        <f>DR20-DP20</f>
+        <v>57.5800000000004</v>
+      </c>
+      <c r="DR20" s="20">
+        <v>2293.53</v>
+      </c>
+      <c r="DS20" s="20">
+        <f>DT20-DR20</f>
+        <v>52.4899999999998</v>
+      </c>
+      <c r="DT20" s="20">
+        <v>2346.02</v>
+      </c>
+      <c r="DU20" s="20">
+        <f>DV20-DT20</f>
+        <v>0.0399999999999636</v>
+      </c>
+      <c r="DV20" s="20">
+        <v>2346.06</v>
+      </c>
+      <c r="DW20" s="20">
+        <f>DX20-DV20</f>
         <v>0</v>
       </c>
-      <c r="BX20" s="24">
-        <v>2097.36</v>
-      </c>
-      <c r="BY20" s="24">
-        <f>BZ20-BX20</f>
-        <v>0.0199999999999818</v>
-      </c>
-      <c r="BZ20" s="24">
-        <v>2097.38</v>
-      </c>
-      <c r="CA20" s="24">
-        <f>CB20-BZ20</f>
-        <v>30.5899999999997</v>
-      </c>
-      <c r="CB20" s="24">
-        <v>2127.97</v>
-      </c>
-      <c r="CC20" s="24">
-        <f>CD20-CB20</f>
-        <v>62.5300000000002</v>
-      </c>
-      <c r="CD20" s="24">
-        <v>2190.5</v>
-      </c>
-      <c r="CE20" s="24">
-        <f>CF20-CD20</f>
-        <v>49.0500000000002</v>
-      </c>
-      <c r="CF20" s="24">
-        <v>2239.55</v>
-      </c>
-      <c r="CG20" s="24">
-        <f>CH20-CF20</f>
-        <v>52.2599999999998</v>
-      </c>
-      <c r="CH20" s="24">
-        <v>2291.81</v>
-      </c>
-      <c r="CI20" s="24">
-        <f>CJ20-CH20</f>
-        <v>48.0300000000002</v>
-      </c>
-      <c r="CJ20" s="24">
-        <v>2339.84</v>
-      </c>
-      <c r="CK20" s="24">
-        <f>CL20-CJ20</f>
-        <v>56.8499999999999</v>
-      </c>
-      <c r="CL20" s="24">
-        <v>2396.69</v>
-      </c>
-      <c r="CM20" s="24">
-        <f>CN20-CL20</f>
-        <v>35.73</v>
-      </c>
-      <c r="CN20" s="24">
-        <v>2432.42</v>
-      </c>
-      <c r="CO20" s="24">
-        <f>CP20-CN20</f>
-        <v>31.79</v>
-      </c>
-      <c r="CP20" s="24">
-        <v>2464.21</v>
-      </c>
-      <c r="CQ20" s="24">
-        <f>CR20-CP20</f>
-        <v>28.4200000000001</v>
-      </c>
-      <c r="CR20" s="24">
-        <v>2492.63</v>
-      </c>
-      <c r="CS20" s="24">
-        <f>CT20-CR20</f>
-        <v>84.6199999999999</v>
-      </c>
-      <c r="CT20" s="24">
-        <v>2577.25</v>
-      </c>
-      <c r="CU20" s="24">
-        <f>CV20-CT20</f>
-        <v>29.0999999999999</v>
-      </c>
-      <c r="CV20" s="24">
-        <v>2606.35</v>
-      </c>
-      <c r="CW20" s="23">
-        <f>CX20-CV20</f>
-        <v>33.1300000000001</v>
-      </c>
-      <c r="CX20" s="24">
-        <v>2639.48</v>
-      </c>
-      <c r="CY20" s="24">
-        <f>CZ20-CX20</f>
-        <v>26.6199999999999</v>
-      </c>
-      <c r="CZ20" s="24">
-        <v>2666.1</v>
-      </c>
-      <c r="DA20" s="24">
-        <f>DB20-CZ20</f>
-        <v>34.8000000000002</v>
-      </c>
-      <c r="DB20" s="24">
-        <v>2700.9</v>
-      </c>
-      <c r="DC20" s="24">
-        <f>DD20-DB20</f>
-        <v>51.6999999999998</v>
-      </c>
-      <c r="DD20" s="24">
-        <v>2752.6</v>
-      </c>
-      <c r="DE20" s="24">
-        <f>DF20-DD20</f>
-        <v>32.4000000000001</v>
-      </c>
-      <c r="DF20" s="24">
-        <v>2785</v>
-      </c>
-      <c r="DG20" s="24">
-        <f>DH20-DF20</f>
-        <v>12.6599999999999</v>
-      </c>
-      <c r="DH20" s="24">
-        <v>2797.66</v>
-      </c>
-      <c r="DI20" s="24">
-        <f>DJ20-DH20</f>
-        <v>61.23</v>
-      </c>
-      <c r="DJ20" s="24">
-        <v>2858.89</v>
-      </c>
-      <c r="DK20" s="24">
-        <f>DL20-DJ20</f>
-        <v>32.0700000000002</v>
-      </c>
-      <c r="DL20" s="24">
-        <v>2890.96</v>
-      </c>
-      <c r="DM20" s="24">
-        <f>DN20-DL20</f>
-        <v>56.8400000000001</v>
-      </c>
-      <c r="DN20" s="24">
-        <v>2947.8</v>
-      </c>
-      <c r="DO20" s="23">
-        <f>DP20-DN20</f>
-        <v>12.0599999999999</v>
-      </c>
-      <c r="DP20" s="24">
-        <v>2959.86</v>
-      </c>
-      <c r="DQ20" s="24">
-        <f>DR20-DP20</f>
-        <v>19.8199999999997</v>
-      </c>
-      <c r="DR20" s="24">
-        <v>2979.68</v>
-      </c>
-      <c r="DS20" s="24">
-        <f>DT20-DR20</f>
-        <v>24.1000000000004</v>
-      </c>
-      <c r="DT20" s="24">
-        <v>3003.78</v>
-      </c>
-      <c r="DU20" s="24">
-        <f>DV20-DT20</f>
-        <v>34.7599999999998</v>
-      </c>
-      <c r="DV20" s="24">
-        <v>3038.54</v>
-      </c>
-      <c r="DW20" s="24">
-        <f>DX20-DV20</f>
-        <v>33.0799999999999</v>
-      </c>
-      <c r="DX20" s="24">
-        <v>3071.62</v>
-      </c>
-      <c r="DY20" s="24">
+      <c r="DX20" s="20">
+        <v>2346.06</v>
+      </c>
+      <c r="DY20" s="20">
         <f>DZ20-DX20</f>
-        <v>23.4200000000001</v>
-      </c>
-      <c r="DZ20" s="24">
-        <v>3095.04</v>
-      </c>
-      <c r="EA20" s="24">
+        <v>38.7600000000002</v>
+      </c>
+      <c r="DZ20" s="20">
+        <v>2384.82</v>
+      </c>
+      <c r="EA20" s="20">
         <f>EB20-DZ20</f>
-        <v>43.3200000000002</v>
-      </c>
-      <c r="EB20" s="24">
-        <v>3138.36</v>
-      </c>
-      <c r="EC20" s="24">
+        <v>41.4099999999999</v>
+      </c>
+      <c r="EB20" s="20">
+        <v>2426.23</v>
+      </c>
+      <c r="EC20" s="20">
         <f>ED20-EB20</f>
-        <v>18.71</v>
-      </c>
-      <c r="ED20" s="24">
-        <v>3157.07</v>
-      </c>
-      <c r="EE20" s="24">
+        <v>149.86</v>
+      </c>
+      <c r="ED20" s="20">
+        <v>2576.09</v>
+      </c>
+      <c r="EE20" s="20">
         <f>EF20-ED20</f>
-        <v>16.0299999999997</v>
-      </c>
-      <c r="EF20" s="24">
-        <v>3173.1</v>
-      </c>
-      <c r="EG20" s="24">
+        <v>79.1099999999997</v>
+      </c>
+      <c r="EF20" s="20">
+        <v>2655.2</v>
+      </c>
+      <c r="EG20" s="20">
         <f>EH20-EF20</f>
-        <v>31.71</v>
-      </c>
-      <c r="EH20" s="24">
-        <v>3204.81</v>
-      </c>
-      <c r="EI20" s="24">
+        <v>43.48</v>
+      </c>
+      <c r="EH20" s="20">
+        <v>2698.68</v>
+      </c>
+      <c r="EI20" s="20">
         <f>EJ20-EH20</f>
-        <v>15.54</v>
-      </c>
-      <c r="EJ20" s="24">
-        <v>3220.35</v>
-      </c>
-      <c r="EK20" s="24">
+        <v>76.3099999999999</v>
+      </c>
+      <c r="EJ20" s="20">
+        <v>2774.99</v>
+      </c>
+      <c r="EK20" s="20">
         <f>EL20-EJ20</f>
-        <v>19.9100000000003</v>
-      </c>
-      <c r="EL20" s="24">
-        <v>3240.26</v>
-      </c>
-      <c r="EM20" s="24">
+        <v>65.2200000000003</v>
+      </c>
+      <c r="EL20" s="20">
+        <v>2840.21</v>
+      </c>
+      <c r="EM20" s="20">
         <f>EN20-EL20</f>
-        <v>0</v>
-      </c>
-      <c r="EN20" s="24">
-        <v>3240.26</v>
-      </c>
-      <c r="EO20" s="24">
+        <v>84.2199999999998</v>
+      </c>
+      <c r="EN20" s="20">
+        <v>2924.43</v>
+      </c>
+      <c r="EO20" s="20">
         <f>EP20-EN20</f>
-        <v>0</v>
-      </c>
-      <c r="EP20" s="24">
-        <v>3240.26</v>
-      </c>
-      <c r="EQ20" s="24">
+        <v>40.5300000000002</v>
+      </c>
+      <c r="EP20" s="20">
+        <v>2964.96</v>
+      </c>
+      <c r="EQ20" s="20">
         <f>ER20-EP20</f>
-        <v>0</v>
-      </c>
-      <c r="ER20" s="24">
-        <v>3240.26</v>
-      </c>
-      <c r="ES20" s="24">
+        <v>43.6199999999999</v>
+      </c>
+      <c r="ER20" s="20">
+        <v>3008.58</v>
+      </c>
+      <c r="ES20" s="20">
         <f>ET20-ER20</f>
-        <v>0</v>
-      </c>
-      <c r="ET20" s="24">
-        <v>3240.26</v>
-      </c>
-      <c r="EU20" s="24">
+        <v>27.79</v>
+      </c>
+      <c r="ET20" s="20">
+        <v>3036.37</v>
+      </c>
+      <c r="EU20" s="20">
         <f>EV20-ET20</f>
-        <v>0</v>
-      </c>
-      <c r="EV20" s="24">
-        <v>3240.26</v>
-      </c>
-      <c r="EW20" s="23" t="s">
-        <v>139</v>
-      </c>
-      <c r="EX20" s="22">
-        <v>668.48</v>
-      </c>
-      <c r="EY20" s="18" t="s">
-        <v>120</v>
+        <v>47.5500000000002</v>
+      </c>
+      <c r="EV20" s="20">
+        <v>3083.92</v>
+      </c>
+      <c r="EW20" s="20">
+        <f>EX20-EV20</f>
+        <v>76.8499999999999</v>
+      </c>
+      <c r="EX20" s="20">
+        <v>3160.77</v>
+      </c>
+      <c r="EY20" s="19" t="s">
+        <v>108</v>
       </c>
       <c r="EZ20" s="18">
-        <v>367.24</v>
-      </c>
-      <c r="FA20" s="2"/>
-      <c r="FB20" s="2"/>
-      <c r="FC20" s="2"/>
-      <c r="FD20" s="9">
-        <f>2.79/(EV20/EX20)</f>
-        <v>0.575589366285422</v>
-      </c>
-      <c r="FE20" s="9">
-        <f>BP20-D20</f>
-        <v>2029.26</v>
+        <v>600.58</v>
+      </c>
+      <c r="FA20" s="21"/>
+      <c r="FB20" s="21"/>
+      <c r="FC20" s="8"/>
+      <c r="FD20" s="8"/>
+      <c r="FE20" s="8"/>
+      <c r="FF20" s="9">
+        <f>2.43/(EX20/EZ20)</f>
+        <v>0.461725908560256</v>
+      </c>
+      <c r="FG20" s="9"/>
+      <c r="FH20" s="9">
+        <f>EX20-ER20</f>
+        <v>152.19</v>
       </c>
     </row>
-    <row r="21" spans="1:161">
+    <row r="21" spans="1:164">
       <c r="A21" s="8" t="s">
-        <v>98</v>
+        <v>105</v>
       </c>
       <c r="B21" s="8" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="C21" s="8" t="s">
-        <v>141</v>
-      </c>
-      <c r="D21" s="8"/>
-      <c r="E21" s="8"/>
-      <c r="F21" s="8"/>
-      <c r="G21" s="8"/>
-      <c r="H21" s="8"/>
-      <c r="I21" s="8"/>
-      <c r="J21" s="8"/>
-      <c r="K21" s="8"/>
-      <c r="L21" s="8"/>
-      <c r="M21" s="8"/>
-      <c r="N21" s="8"/>
-      <c r="O21" s="8"/>
-      <c r="P21" s="8"/>
-      <c r="Q21" s="8"/>
-      <c r="R21" s="8"/>
-      <c r="S21" s="8"/>
-      <c r="T21" s="8"/>
-      <c r="U21" s="8"/>
-      <c r="V21" s="21"/>
-      <c r="W21" s="8"/>
-      <c r="X21" s="21"/>
-      <c r="Y21" s="8"/>
-      <c r="Z21" s="8"/>
-      <c r="AA21" s="8"/>
-      <c r="AB21" s="8"/>
-      <c r="AC21" s="8"/>
-      <c r="AD21" s="8"/>
-      <c r="AE21" s="22"/>
-      <c r="AF21" s="22"/>
-      <c r="AG21" s="22"/>
-      <c r="AH21" s="22"/>
-      <c r="AI21" s="22"/>
-      <c r="AJ21" s="22"/>
-      <c r="AK21" s="22"/>
-      <c r="AL21" s="22"/>
-      <c r="AM21" s="22"/>
-      <c r="AN21" s="22"/>
-      <c r="AO21" s="22"/>
-      <c r="AP21" s="22"/>
-      <c r="AQ21" s="22"/>
-      <c r="AR21" s="22"/>
-      <c r="AS21" s="22"/>
-      <c r="AT21" s="22"/>
-      <c r="AU21" s="23"/>
-      <c r="AV21" s="23"/>
-      <c r="AW21" s="24"/>
-      <c r="AX21" s="24"/>
-      <c r="AY21" s="24"/>
-      <c r="AZ21" s="24"/>
-      <c r="BA21" s="24"/>
-      <c r="BB21" s="24"/>
-      <c r="BC21" s="24"/>
-      <c r="BD21" s="24"/>
-      <c r="BE21" s="23"/>
-      <c r="BF21" s="24"/>
-      <c r="BG21" s="24"/>
-      <c r="BH21" s="24"/>
-      <c r="BI21" s="24"/>
-      <c r="BJ21" s="24"/>
-      <c r="BK21" s="24"/>
-      <c r="BL21" s="24"/>
-      <c r="BM21" s="24"/>
-      <c r="BN21" s="24"/>
-      <c r="BO21" s="24"/>
-      <c r="BP21" s="24"/>
-      <c r="BQ21" s="24"/>
-      <c r="BR21" s="24"/>
-      <c r="BS21" s="24"/>
-      <c r="BT21" s="24"/>
-      <c r="BU21" s="24"/>
-      <c r="BV21" s="24"/>
-      <c r="BW21" s="24"/>
-      <c r="BX21" s="24"/>
-      <c r="BY21" s="24"/>
-      <c r="BZ21" s="24"/>
-      <c r="CA21" s="24"/>
-      <c r="CB21" s="24"/>
-      <c r="CC21" s="24"/>
-      <c r="CD21" s="24"/>
-      <c r="CE21" s="24"/>
-      <c r="CF21" s="24"/>
-      <c r="CG21" s="24"/>
-      <c r="CH21" s="24"/>
-      <c r="CI21" s="24"/>
-      <c r="CJ21" s="24"/>
-      <c r="CK21" s="24"/>
-      <c r="CL21" s="24"/>
-      <c r="CM21" s="24"/>
-      <c r="CN21" s="24"/>
-      <c r="CO21" s="24"/>
-      <c r="CP21" s="24"/>
-      <c r="CQ21" s="24"/>
-      <c r="CR21" s="24"/>
-      <c r="CS21" s="24"/>
-      <c r="CT21" s="24"/>
-      <c r="CU21" s="24"/>
-      <c r="CV21" s="24"/>
-      <c r="CW21" s="23"/>
-      <c r="CX21" s="24"/>
-      <c r="CY21" s="24"/>
-      <c r="CZ21" s="24"/>
-      <c r="DA21" s="24"/>
-      <c r="DB21" s="24"/>
-      <c r="DC21" s="24"/>
-      <c r="DD21" s="24"/>
-      <c r="DE21" s="24"/>
-      <c r="DF21" s="24"/>
-      <c r="DG21" s="24"/>
-      <c r="DH21" s="24"/>
-      <c r="DI21" s="24"/>
+        <v>135</v>
+      </c>
+      <c r="D21" s="8">
+        <v>848.93</v>
+      </c>
+      <c r="E21" s="8">
+        <f>F21-D21</f>
+        <v>34.5600000000001</v>
+      </c>
+      <c r="F21" s="8">
+        <v>883.49</v>
+      </c>
+      <c r="G21" s="8">
+        <f>H21-F21</f>
+        <v>46.08</v>
+      </c>
+      <c r="H21" s="8">
+        <v>929.57</v>
+      </c>
+      <c r="I21" s="8">
+        <f>J21-H21</f>
+        <v>27.7399999999999</v>
+      </c>
+      <c r="J21" s="8">
+        <v>957.31</v>
+      </c>
+      <c r="K21" s="8">
+        <f>L21-J21</f>
+        <v>47.36</v>
+      </c>
+      <c r="L21" s="8">
+        <v>1004.67</v>
+      </c>
+      <c r="M21" s="8">
+        <f>N21-L21</f>
+        <v>25.9399999999999</v>
+      </c>
+      <c r="N21" s="8">
+        <v>1030.61</v>
+      </c>
+      <c r="O21" s="8">
+        <f>P21-N21</f>
+        <v>37.71</v>
+      </c>
+      <c r="P21" s="8">
+        <v>1068.32</v>
+      </c>
+      <c r="Q21" s="8">
+        <f>R21-P21</f>
+        <v>18.3800000000001</v>
+      </c>
+      <c r="R21" s="8">
+        <v>1086.7</v>
+      </c>
+      <c r="S21" s="8">
+        <f>T21-R21</f>
+        <v>21.04</v>
+      </c>
+      <c r="T21" s="8">
+        <v>1107.74</v>
+      </c>
+      <c r="U21" s="8">
+        <f>V21-T21</f>
+        <v>32.7</v>
+      </c>
+      <c r="V21" s="22">
+        <v>1140.44</v>
+      </c>
+      <c r="W21" s="8">
+        <f>X21-V21</f>
+        <v>26.9299999999998</v>
+      </c>
+      <c r="X21" s="22">
+        <v>1167.37</v>
+      </c>
+      <c r="Y21" s="8">
+        <f>Z21-X21</f>
+        <v>37.0300000000002</v>
+      </c>
+      <c r="Z21" s="8">
+        <v>1204.4</v>
+      </c>
+      <c r="AA21" s="8">
+        <f>AB21-Z21</f>
+        <v>33.6199999999999</v>
+      </c>
+      <c r="AB21" s="8">
+        <v>1238.02</v>
+      </c>
+      <c r="AC21" s="8">
+        <f>AD21-AB21</f>
+        <v>53.73</v>
+      </c>
+      <c r="AD21" s="8">
+        <v>1291.75</v>
+      </c>
+      <c r="AE21" s="21">
+        <f>AF21-AD21</f>
+        <v>23.99</v>
+      </c>
+      <c r="AF21" s="21">
+        <v>1315.74</v>
+      </c>
+      <c r="AG21" s="21">
+        <f>AH21-AF21</f>
+        <v>29.53</v>
+      </c>
+      <c r="AH21" s="21">
+        <v>1345.27</v>
+      </c>
+      <c r="AI21" s="21">
+        <f>AJ21-AH21</f>
+        <v>26.6100000000001</v>
+      </c>
+      <c r="AJ21" s="21">
+        <v>1371.88</v>
+      </c>
+      <c r="AK21" s="21">
+        <f>AL21-AJ21</f>
+        <v>40.3999999999999</v>
+      </c>
+      <c r="AL21" s="21">
+        <v>1412.28</v>
+      </c>
+      <c r="AM21" s="21">
+        <f>AN21-AL21</f>
+        <v>19.74</v>
+      </c>
+      <c r="AN21" s="21">
+        <v>1432.02</v>
+      </c>
+      <c r="AO21" s="21">
+        <f>AP21-AN21</f>
+        <v>53.23</v>
+      </c>
+      <c r="AP21" s="21">
+        <v>1485.25</v>
+      </c>
+      <c r="AQ21" s="21">
+        <f>AR21-AP21</f>
+        <v>21.1800000000001</v>
+      </c>
+      <c r="AR21" s="21">
+        <v>1506.43</v>
+      </c>
+      <c r="AS21" s="21">
+        <f>AT21-AR21</f>
+        <v>17.1199999999999</v>
+      </c>
+      <c r="AT21" s="21">
+        <v>1523.55</v>
+      </c>
+      <c r="AU21" s="23">
+        <f>AV21-AT21</f>
+        <v>52.4000000000001</v>
+      </c>
+      <c r="AV21" s="23">
+        <v>1575.95</v>
+      </c>
+      <c r="AW21" s="24">
+        <f>AX21-AV21</f>
+        <v>22.8</v>
+      </c>
+      <c r="AX21" s="24">
+        <v>1598.75</v>
+      </c>
+      <c r="AY21" s="24">
+        <f>AZ21-AX21</f>
+        <v>41.49</v>
+      </c>
+      <c r="AZ21" s="24">
+        <v>1640.24</v>
+      </c>
+      <c r="BA21" s="24">
+        <f>BB21-AZ21</f>
+        <v>17.73</v>
+      </c>
+      <c r="BB21" s="24">
+        <v>1657.97</v>
+      </c>
+      <c r="BC21" s="24">
+        <f>BD21-BB21</f>
+        <v>17.8899999999999</v>
+      </c>
+      <c r="BD21" s="24">
+        <v>1675.86</v>
+      </c>
+      <c r="BE21" s="23">
+        <f>BF21-BD21</f>
+        <v>36.3500000000001</v>
+      </c>
+      <c r="BF21" s="24">
+        <v>1712.21</v>
+      </c>
+      <c r="BG21" s="24">
+        <f>BH21-BF21</f>
+        <v>39.54</v>
+      </c>
+      <c r="BH21" s="24">
+        <v>1751.75</v>
+      </c>
+      <c r="BI21" s="24">
+        <f>BJ21-BH21</f>
+        <v>13.1800000000001</v>
+      </c>
+      <c r="BJ21" s="24">
+        <v>1764.93</v>
+      </c>
+      <c r="BK21" s="24">
+        <f>BL21-BJ21</f>
+        <v>13.76</v>
+      </c>
+      <c r="BL21" s="24">
+        <v>1778.69</v>
+      </c>
+      <c r="BM21" s="24">
+        <f>BN21-BL21</f>
+        <v>13.1299999999999</v>
+      </c>
+      <c r="BN21" s="24">
+        <v>1791.82</v>
+      </c>
+      <c r="BO21" s="24">
+        <f>BP21-BN21</f>
+        <v>24.24</v>
+      </c>
+      <c r="BP21" s="24">
+        <v>1816.06</v>
+      </c>
+      <c r="BQ21" s="24">
+        <f>BR21-BP21</f>
+        <v>16.3</v>
+      </c>
+      <c r="BR21" s="24">
+        <v>1832.36</v>
+      </c>
+      <c r="BS21" s="24">
+        <f>BT21-BR21</f>
+        <v>33.98</v>
+      </c>
+      <c r="BT21" s="24">
+        <v>1866.34</v>
+      </c>
+      <c r="BU21" s="24">
+        <f>BV21-BT21</f>
+        <v>15.5600000000002</v>
+      </c>
+      <c r="BV21" s="24">
+        <v>1881.9</v>
+      </c>
+      <c r="BW21" s="24">
+        <f>BX21-BV21</f>
+        <v>34.51</v>
+      </c>
+      <c r="BX21" s="24">
+        <v>1916.41</v>
+      </c>
+      <c r="BY21" s="24">
+        <f>BZ21-BX21</f>
+        <v>21.02</v>
+      </c>
+      <c r="BZ21" s="24">
+        <v>1937.43</v>
+      </c>
+      <c r="CA21" s="24">
+        <f>CB21-BZ21</f>
+        <v>34.8799999999999</v>
+      </c>
+      <c r="CB21" s="24">
+        <v>1972.31</v>
+      </c>
+      <c r="CC21" s="24">
+        <f>CD21-CB21</f>
+        <v>30.26</v>
+      </c>
+      <c r="CD21" s="24">
+        <v>2002.57</v>
+      </c>
+      <c r="CE21" s="24">
+        <f>CF21-CD21</f>
+        <v>22.74</v>
+      </c>
+      <c r="CF21" s="24">
+        <v>2025.31</v>
+      </c>
+      <c r="CG21" s="24">
+        <f>CH21-CF21</f>
+        <v>47.1799999999998</v>
+      </c>
+      <c r="CH21" s="24">
+        <v>2072.49</v>
+      </c>
+      <c r="CI21" s="24">
+        <f>CJ21-CH21</f>
+        <v>42.1100000000001</v>
+      </c>
+      <c r="CJ21" s="24">
+        <v>2114.6</v>
+      </c>
+      <c r="CK21" s="24">
+        <f>CL21-CJ21</f>
+        <v>16.4500000000003</v>
+      </c>
+      <c r="CL21" s="24">
+        <v>2131.05</v>
+      </c>
+      <c r="CM21" s="24">
+        <f>CN21-CL21</f>
+        <v>11.02</v>
+      </c>
+      <c r="CN21" s="24">
+        <v>2142.07</v>
+      </c>
+      <c r="CO21" s="24">
+        <f>CP21-CN21</f>
+        <v>4.62999999999965</v>
+      </c>
+      <c r="CP21" s="24">
+        <v>2146.7</v>
+      </c>
+      <c r="CQ21" s="24">
+        <f>CR21-CP21</f>
+        <v>26.1200000000003</v>
+      </c>
+      <c r="CR21" s="24">
+        <v>2172.82</v>
+      </c>
+      <c r="CS21" s="24">
+        <f>CT21-CR21</f>
+        <v>85.5899999999997</v>
+      </c>
+      <c r="CT21" s="24">
+        <v>2258.41</v>
+      </c>
+      <c r="CU21" s="24">
+        <f>CV21-CT21</f>
+        <v>28.8800000000001</v>
+      </c>
+      <c r="CV21" s="24">
+        <v>2287.29</v>
+      </c>
+      <c r="CW21" s="23">
+        <f>CX21-CV21</f>
+        <v>20.4700000000003</v>
+      </c>
+      <c r="CX21" s="24">
+        <v>2307.76</v>
+      </c>
+      <c r="CY21" s="24">
+        <f>CZ21-CX21</f>
+        <v>17.9299999999998</v>
+      </c>
+      <c r="CZ21" s="24">
+        <v>2325.69</v>
+      </c>
+      <c r="DA21" s="24">
+        <f>DB21-CZ21</f>
+        <v>20.1900000000001</v>
+      </c>
+      <c r="DB21" s="24">
+        <v>2345.88</v>
+      </c>
+      <c r="DC21" s="24">
+        <f>DD21-DB21</f>
+        <v>29.1399999999999</v>
+      </c>
+      <c r="DD21" s="24">
+        <v>2375.02</v>
+      </c>
+      <c r="DE21" s="24">
+        <f>DF21-DD21</f>
+        <v>31.1799999999998</v>
+      </c>
+      <c r="DF21" s="24">
+        <v>2406.2</v>
+      </c>
+      <c r="DG21" s="24">
+        <f>DH21-DF21</f>
+        <v>18.8600000000001</v>
+      </c>
+      <c r="DH21" s="24">
+        <v>2425.06</v>
+      </c>
+      <c r="DI21" s="24">
+        <f>DJ21-DH21</f>
+        <v>35.0900000000001</v>
+      </c>
       <c r="DJ21" s="24">
-        <v>2158.34</v>
+        <v>2460.15</v>
       </c>
       <c r="DK21" s="24">
         <f>DL21-DJ21</f>
-        <v>0</v>
+        <v>14.3800000000001</v>
       </c>
       <c r="DL21" s="24">
-        <v>2158.34</v>
+        <v>2474.53</v>
       </c>
       <c r="DM21" s="24">
         <f>DN21-DL21</f>
-        <v>55.6999999999998</v>
+        <v>21.7099999999996</v>
       </c>
       <c r="DN21" s="24">
-        <v>2214.04</v>
+        <v>2496.24</v>
       </c>
       <c r="DO21" s="23">
         <f>DP21-DN21</f>
-        <v>21.9099999999999</v>
+        <v>21.0900000000001</v>
       </c>
       <c r="DP21" s="24">
-        <v>2235.95</v>
+        <v>2517.33</v>
       </c>
       <c r="DQ21" s="24">
         <f>DR21-DP21</f>
-        <v>57.5800000000004</v>
+        <v>23.04</v>
       </c>
       <c r="DR21" s="24">
-        <v>2293.53</v>
+        <v>2540.37</v>
       </c>
       <c r="DS21" s="24">
         <f>DT21-DR21</f>
-        <v>52.4899999999998</v>
+        <v>17.1600000000003</v>
       </c>
       <c r="DT21" s="24">
-        <v>2346.02</v>
+        <v>2557.53</v>
       </c>
       <c r="DU21" s="24">
         <f>DV21-DT21</f>
-        <v>0.0399999999999636</v>
+        <v>24.04</v>
       </c>
       <c r="DV21" s="24">
-        <v>2346.06</v>
+        <v>2581.57</v>
       </c>
       <c r="DW21" s="24">
         <f>DX21-DV21</f>
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="DX21" s="24">
-        <v>2346.06</v>
+        <v>2600.07</v>
       </c>
       <c r="DY21" s="24">
         <f>DZ21-DX21</f>
-        <v>38.7600000000002</v>
+        <v>42.25</v>
       </c>
       <c r="DZ21" s="24">
-        <v>2384.82</v>
+        <v>2642.32</v>
       </c>
       <c r="EA21" s="24">
         <f>EB21-DZ21</f>
-        <v>41.4099999999999</v>
+        <v>5.78999999999996</v>
       </c>
       <c r="EB21" s="24">
-        <v>2426.23</v>
+        <v>2648.11</v>
       </c>
       <c r="EC21" s="24">
         <f>ED21-EB21</f>
-        <v>149.86</v>
+        <v>9.62999999999965</v>
       </c>
       <c r="ED21" s="24">
-        <v>2576.09</v>
+        <v>2657.74</v>
       </c>
       <c r="EE21" s="24">
         <f>EF21-ED21</f>
-        <v>79.1099999999997</v>
+        <v>15.6100000000001</v>
       </c>
       <c r="EF21" s="24">
-        <v>2655.2</v>
+        <v>2673.35</v>
       </c>
       <c r="EG21" s="24">
         <f>EH21-EF21</f>
-        <v>43.48</v>
+        <v>2.74000000000024</v>
       </c>
       <c r="EH21" s="24">
-        <v>2698.68</v>
+        <v>2676.09</v>
       </c>
       <c r="EI21" s="24">
         <f>EJ21-EH21</f>
-        <v>76.3099999999999</v>
+        <v>26.8699999999999</v>
       </c>
       <c r="EJ21" s="24">
-        <v>2774.99</v>
+        <v>2702.96</v>
       </c>
       <c r="EK21" s="24">
         <f>EL21-EJ21</f>
-        <v>65.2200000000003</v>
+        <v>35.9299999999998</v>
       </c>
       <c r="EL21" s="24">
-        <v>2840.21</v>
+        <v>2738.89</v>
       </c>
       <c r="EM21" s="24">
         <f>EN21-EL21</f>
-        <v>84.2199999999998</v>
+        <v>5.05000000000018</v>
       </c>
       <c r="EN21" s="24">
-        <v>2924.43</v>
+        <v>2743.94</v>
       </c>
       <c r="EO21" s="24">
         <f>EP21-EN21</f>
-        <v>40.5300000000002</v>
+        <v>15.4899999999998</v>
       </c>
       <c r="EP21" s="24">
-        <v>2964.96</v>
+        <v>2759.43</v>
       </c>
       <c r="EQ21" s="24">
         <f>ER21-EP21</f>
-        <v>43.6199999999999</v>
+        <v>0.460000000000036</v>
       </c>
       <c r="ER21" s="24">
-        <v>3008.58</v>
+        <v>2759.89</v>
       </c>
       <c r="ES21" s="24">
         <f>ET21-ER21</f>
-        <v>27.79</v>
+        <v>1.38000000000011</v>
       </c>
       <c r="ET21" s="24">
-        <v>3036.37</v>
+        <v>2761.27</v>
       </c>
       <c r="EU21" s="24">
         <f>EV21-ET21</f>
-        <v>47.5500000000002</v>
+        <v>3.98000000000002</v>
       </c>
       <c r="EV21" s="24">
-        <v>3083.92</v>
-      </c>
-      <c r="EW21" s="23" t="s">
-        <v>105</v>
-      </c>
-      <c r="EX21" s="22">
-        <v>600.73</v>
-      </c>
-      <c r="EY21" s="22"/>
-      <c r="EZ21" s="22"/>
-      <c r="FA21" s="8"/>
-      <c r="FB21" s="8"/>
-      <c r="FC21" s="8"/>
-      <c r="FD21" s="9">
-        <f>2.79/(EV21/EX21)</f>
-        <v>0.543476062932891</v>
-      </c>
-      <c r="FE21" s="9"/>
+        <v>2765.25</v>
+      </c>
+      <c r="EW21" s="24">
+        <f>EX21-EV21</f>
+        <v>2.36000000000013</v>
+      </c>
+      <c r="EX21" s="24">
+        <v>2767.61</v>
+      </c>
+      <c r="EY21" s="23" t="s">
+        <v>100</v>
+      </c>
+      <c r="EZ21" s="21">
+        <v>1197.27</v>
+      </c>
+      <c r="FA21" s="18" t="s">
+        <v>115</v>
+      </c>
+      <c r="FB21" s="18">
+        <v>556.77</v>
+      </c>
+      <c r="FC21" s="2">
+        <v>30</v>
+      </c>
+      <c r="FD21" s="2">
+        <v>3.2</v>
+      </c>
+      <c r="FE21" s="2">
+        <v>78989</v>
+      </c>
+      <c r="FF21" s="9">
+        <f>2.43/(EX21/EZ21)</f>
+        <v>1.05121968051857</v>
+      </c>
+      <c r="FG21" s="9">
+        <f>BP21-D21</f>
+        <v>967.13</v>
+      </c>
+      <c r="FH21" s="9">
+        <f>EX21-ER21</f>
+        <v>7.72000000000025</v>
+      </c>
     </row>
-    <row r="22" spans="1:161">
+    <row r="22" spans="1:164">
       <c r="A22" s="8" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B22" s="8" t="s">
+        <v>147</v>
+      </c>
+      <c r="C22" s="8" t="s">
         <v>144</v>
       </c>
-      <c r="C22" s="8" t="s">
-        <v>132</v>
-      </c>
       <c r="D22" s="8">
-        <v>848.93</v>
+        <v>363.88</v>
       </c>
       <c r="E22" s="8">
         <f>F22-D22</f>
-        <v>34.5600000000001</v>
+        <v>14.21</v>
       </c>
       <c r="F22" s="8">
-        <v>883.49</v>
+        <v>378.09</v>
       </c>
       <c r="G22" s="8">
         <f>H22-F22</f>
-        <v>46.08</v>
+        <v>11.22</v>
       </c>
       <c r="H22" s="8">
-        <v>929.57</v>
+        <v>389.31</v>
       </c>
       <c r="I22" s="8">
         <f>J22-H22</f>
-        <v>27.7399999999999</v>
+        <v>13.62</v>
       </c>
       <c r="J22" s="8">
-        <v>957.31</v>
+        <v>402.93</v>
       </c>
       <c r="K22" s="8">
         <f>L22-J22</f>
-        <v>47.36</v>
+        <v>11.13</v>
       </c>
       <c r="L22" s="8">
-        <v>1004.67</v>
+        <v>414.06</v>
       </c>
       <c r="M22" s="8">
         <f>N22-L22</f>
-        <v>25.9399999999999</v>
+        <v>17.39</v>
       </c>
       <c r="N22" s="8">
-        <v>1030.61</v>
+        <v>431.45</v>
       </c>
       <c r="O22" s="8">
         <f>P22-N22</f>
-        <v>37.71</v>
+        <v>6.32999999999998</v>
       </c>
       <c r="P22" s="8">
-        <v>1068.32</v>
+        <v>437.78</v>
       </c>
       <c r="Q22" s="8">
         <f>R22-P22</f>
-        <v>18.3800000000001</v>
+        <v>53.01</v>
       </c>
       <c r="R22" s="8">
-        <v>1086.7</v>
+        <v>490.79</v>
       </c>
       <c r="S22" s="8">
         <f>T22-R22</f>
-        <v>21.04</v>
+        <v>11.82</v>
       </c>
       <c r="T22" s="8">
-        <v>1107.74</v>
+        <v>502.61</v>
       </c>
       <c r="U22" s="8">
         <f>V22-T22</f>
-        <v>32.7</v>
-      </c>
-      <c r="V22" s="21">
-        <v>1140.44</v>
+        <v>19.3099999999999</v>
+      </c>
+      <c r="V22" s="22">
+        <v>521.92</v>
       </c>
       <c r="W22" s="8">
         <f>X22-V22</f>
-        <v>26.9299999999998</v>
-      </c>
-      <c r="X22" s="21">
-        <v>1167.37</v>
+        <v>29.5400000000001</v>
+      </c>
+      <c r="X22" s="22">
+        <v>551.46</v>
       </c>
       <c r="Y22" s="8">
         <f>Z22-X22</f>
-        <v>37.0300000000002</v>
+        <v>36.98</v>
       </c>
       <c r="Z22" s="8">
-        <v>1204.4</v>
+        <v>588.44</v>
       </c>
       <c r="AA22" s="8">
         <f>AB22-Z22</f>
-        <v>33.6199999999999</v>
+        <v>21.17</v>
       </c>
       <c r="AB22" s="8">
-        <v>1238.02</v>
+        <v>609.61</v>
       </c>
       <c r="AC22" s="8">
         <f>AD22-AB22</f>
-        <v>53.73</v>
+        <v>17.4399999999999</v>
       </c>
       <c r="AD22" s="8">
-        <v>1291.75</v>
-      </c>
-      <c r="AE22" s="22">
+        <v>627.05</v>
+      </c>
+      <c r="AE22" s="21">
         <f>AF22-AD22</f>
-        <v>23.99</v>
-      </c>
-      <c r="AF22" s="22">
-        <v>1315.74</v>
-      </c>
-      <c r="AG22" s="22">
+        <v>21.0500000000001</v>
+      </c>
+      <c r="AF22" s="21">
+        <v>648.1</v>
+      </c>
+      <c r="AG22" s="21">
         <f>AH22-AF22</f>
-        <v>29.53</v>
-      </c>
-      <c r="AH22" s="22">
-        <v>1345.27</v>
-      </c>
-      <c r="AI22" s="22">
+        <v>37.27</v>
+      </c>
+      <c r="AH22" s="21">
+        <v>685.37</v>
+      </c>
+      <c r="AI22" s="21">
         <f>AJ22-AH22</f>
-        <v>26.6100000000001</v>
-      </c>
-      <c r="AJ22" s="22">
-        <v>1371.88</v>
-      </c>
-      <c r="AK22" s="22">
+        <v>25.0700000000001</v>
+      </c>
+      <c r="AJ22" s="21">
+        <v>710.44</v>
+      </c>
+      <c r="AK22" s="21">
         <f>AL22-AJ22</f>
-        <v>40.3999999999999</v>
-      </c>
-      <c r="AL22" s="22">
-        <v>1412.28</v>
-      </c>
-      <c r="AM22" s="22">
+        <v>22.64</v>
+      </c>
+      <c r="AL22" s="21">
+        <v>733.08</v>
+      </c>
+      <c r="AM22" s="21">
         <f>AN22-AL22</f>
-        <v>19.74</v>
-      </c>
-      <c r="AN22" s="22">
-        <v>1432.02</v>
-      </c>
-      <c r="AO22" s="22">
+        <v>28.76</v>
+      </c>
+      <c r="AN22" s="21">
+        <v>761.84</v>
+      </c>
+      <c r="AO22" s="21">
         <f>AP22-AN22</f>
-        <v>53.23</v>
-      </c>
-      <c r="AP22" s="22">
-        <v>1485.25</v>
-      </c>
-      <c r="AQ22" s="22">
+        <v>12.24</v>
+      </c>
+      <c r="AP22" s="21">
+        <v>774.08</v>
+      </c>
+      <c r="AQ22" s="21">
         <f>AR22-AP22</f>
-        <v>21.1800000000001</v>
-      </c>
-      <c r="AR22" s="22">
-        <v>1506.43</v>
-      </c>
-      <c r="AS22" s="22">
+        <v>29.39</v>
+      </c>
+      <c r="AR22" s="21">
+        <v>803.47</v>
+      </c>
+      <c r="AS22" s="21">
         <f>AT22-AR22</f>
-        <v>17.1199999999999</v>
-      </c>
-      <c r="AT22" s="22">
-        <v>1523.55</v>
+        <v>33.97</v>
+      </c>
+      <c r="AT22" s="21">
+        <v>837.44</v>
       </c>
       <c r="AU22" s="23">
         <f>AV22-AT22</f>
-        <v>52.4000000000001</v>
+        <v>29.6999999999999</v>
       </c>
       <c r="AV22" s="23">
-        <v>1575.95</v>
+        <v>867.14</v>
       </c>
       <c r="AW22" s="24">
         <f>AX22-AV22</f>
-        <v>22.8</v>
+        <v>21.75</v>
       </c>
       <c r="AX22" s="24">
-        <v>1598.75</v>
+        <v>888.89</v>
       </c>
       <c r="AY22" s="24">
         <f>AZ22-AX22</f>
-        <v>41.49</v>
+        <v>37.0600000000001</v>
       </c>
       <c r="AZ22" s="24">
-        <v>1640.24</v>
+        <v>925.95</v>
       </c>
       <c r="BA22" s="24">
         <f>BB22-AZ22</f>
-        <v>17.73</v>
+        <v>14.3</v>
       </c>
       <c r="BB22" s="24">
-        <v>1657.97</v>
+        <v>940.25</v>
       </c>
       <c r="BC22" s="24">
         <f>BD22-BB22</f>
-        <v>17.8899999999999</v>
+        <v>12.04</v>
       </c>
       <c r="BD22" s="24">
-        <v>1675.86</v>
+        <v>952.29</v>
       </c>
       <c r="BE22" s="23">
         <f>BF22-BD22</f>
-        <v>36.3500000000001</v>
+        <v>39.5300000000001</v>
       </c>
       <c r="BF22" s="24">
-        <v>1712.21</v>
+        <v>991.82</v>
       </c>
       <c r="BG22" s="24">
         <f>BH22-BF22</f>
-        <v>39.54</v>
+        <v>38.2599999999999</v>
       </c>
       <c r="BH22" s="24">
-        <v>1751.75</v>
+        <v>1030.08</v>
       </c>
       <c r="BI22" s="24">
         <f>BJ22-BH22</f>
-        <v>13.1800000000001</v>
+        <v>35.53</v>
       </c>
       <c r="BJ22" s="24">
-        <v>1764.93</v>
+        <v>1065.61</v>
       </c>
       <c r="BK22" s="24">
         <f>BL22-BJ22</f>
-        <v>13.76</v>
+        <v>36.8300000000002</v>
       </c>
       <c r="BL22" s="24">
-        <v>1778.69</v>
+        <v>1102.44</v>
       </c>
       <c r="BM22" s="24">
         <f>BN22-BL22</f>
-        <v>13.1299999999999</v>
+        <v>30.4199999999998</v>
       </c>
       <c r="BN22" s="24">
-        <v>1791.82</v>
+        <v>1132.86</v>
       </c>
       <c r="BO22" s="24">
         <f>BP22-BN22</f>
-        <v>24.24</v>
+        <v>21.5400000000002</v>
       </c>
       <c r="BP22" s="24">
-        <v>1816.06</v>
+        <v>1154.4</v>
       </c>
       <c r="BQ22" s="24">
         <f>BR22-BP22</f>
-        <v>16.3</v>
+        <v>41.52</v>
       </c>
       <c r="BR22" s="24">
-        <v>1832.36</v>
+        <v>1195.92</v>
       </c>
       <c r="BS22" s="24">
         <f>BT22-BR22</f>
-        <v>33.98</v>
+        <v>10.8</v>
       </c>
       <c r="BT22" s="24">
-        <v>1866.34</v>
+        <v>1206.72</v>
       </c>
       <c r="BU22" s="24">
         <f>BV22-BT22</f>
-        <v>15.5600000000002</v>
+        <v>13.96</v>
       </c>
       <c r="BV22" s="24">
-        <v>1881.9</v>
+        <v>1220.68</v>
       </c>
       <c r="BW22" s="24">
         <f>BX22-BV22</f>
-        <v>34.51</v>
+        <v>10.74</v>
       </c>
       <c r="BX22" s="24">
-        <v>1916.41</v>
+        <v>1231.42</v>
       </c>
       <c r="BY22" s="24">
         <f>BZ22-BX22</f>
-        <v>21.02</v>
+        <v>28.03</v>
       </c>
       <c r="BZ22" s="24">
-        <v>1937.43</v>
+        <v>1259.45</v>
       </c>
       <c r="CA22" s="24">
         <f>CB22-BZ22</f>
-        <v>34.8799999999999</v>
+        <v>47.29</v>
       </c>
       <c r="CB22" s="24">
-        <v>1972.31</v>
+        <v>1306.74</v>
       </c>
       <c r="CC22" s="24">
         <f>CD22-CB22</f>
-        <v>30.26</v>
+        <v>22.47</v>
       </c>
       <c r="CD22" s="24">
-        <v>2002.57</v>
+        <v>1329.21</v>
       </c>
       <c r="CE22" s="24">
         <f>CF22-CD22</f>
-        <v>22.74</v>
+        <v>9.03999999999996</v>
       </c>
       <c r="CF22" s="24">
-        <v>2025.31</v>
+        <v>1338.25</v>
       </c>
       <c r="CG22" s="24">
         <f>CH22-CF22</f>
-        <v>47.1799999999998</v>
+        <v>24.3599999999999</v>
       </c>
       <c r="CH22" s="24">
-        <v>2072.49</v>
+        <v>1362.61</v>
       </c>
       <c r="CI22" s="24">
         <f>CJ22-CH22</f>
-        <v>42.1100000000001</v>
+        <v>22.9300000000001</v>
       </c>
       <c r="CJ22" s="24">
-        <v>2114.6</v>
+        <v>1385.54</v>
       </c>
       <c r="CK22" s="24">
         <f>CL22-CJ22</f>
-        <v>16.4500000000003</v>
+        <v>29.2</v>
       </c>
       <c r="CL22" s="24">
-        <v>2131.05</v>
+        <v>1414.74</v>
       </c>
       <c r="CM22" s="24">
         <f>CN22-CL22</f>
-        <v>11.02</v>
+        <v>13.6700000000001</v>
       </c>
       <c r="CN22" s="24">
-        <v>2142.07</v>
+        <v>1428.41</v>
       </c>
       <c r="CO22" s="24">
         <f>CP22-CN22</f>
-        <v>4.62999999999965</v>
+        <v>28.1699999999998</v>
       </c>
       <c r="CP22" s="24">
-        <v>2146.7</v>
+        <v>1456.58</v>
       </c>
       <c r="CQ22" s="24">
         <f>CR22-CP22</f>
-        <v>26.1200000000003</v>
+        <v>19.3000000000002</v>
       </c>
       <c r="CR22" s="24">
-        <v>2172.82</v>
+        <v>1475.88</v>
       </c>
       <c r="CS22" s="24">
         <f>CT22-CR22</f>
-        <v>85.5899999999997</v>
+        <v>37.8199999999999</v>
       </c>
       <c r="CT22" s="24">
-        <v>2258.41</v>
+        <v>1513.7</v>
       </c>
       <c r="CU22" s="24">
         <f>CV22-CT22</f>
-        <v>28.8800000000001</v>
+        <v>16.77</v>
       </c>
       <c r="CV22" s="24">
-        <v>2287.29</v>
+        <v>1530.47</v>
       </c>
       <c r="CW22" s="23">
         <f>CX22-CV22</f>
-        <v>20.4700000000003</v>
+        <v>17.99</v>
       </c>
       <c r="CX22" s="24">
-        <v>2307.76</v>
+        <v>1548.46</v>
       </c>
       <c r="CY22" s="24">
         <f>CZ22-CX22</f>
-        <v>17.9299999999998</v>
+        <v>13.6399999999999</v>
       </c>
       <c r="CZ22" s="24">
-        <v>2325.69</v>
+        <v>1562.1</v>
       </c>
       <c r="DA22" s="24">
         <f>DB22-CZ22</f>
-        <v>20.1900000000001</v>
+        <v>63.24</v>
       </c>
       <c r="DB22" s="24">
-        <v>2345.88</v>
+        <v>1625.34</v>
       </c>
       <c r="DC22" s="24">
         <f>DD22-DB22</f>
-        <v>29.1399999999999</v>
+        <v>23.72</v>
       </c>
       <c r="DD22" s="24">
-        <v>2375.02</v>
+        <v>1649.06</v>
       </c>
       <c r="DE22" s="24">
         <f>DF22-DD22</f>
-        <v>31.1799999999998</v>
+        <v>10.8099999999999</v>
       </c>
       <c r="DF22" s="24">
-        <v>2406.2</v>
+        <v>1659.87</v>
       </c>
       <c r="DG22" s="24">
         <f>DH22-DF22</f>
-        <v>18.8600000000001</v>
+        <v>26.6400000000001</v>
       </c>
       <c r="DH22" s="24">
-        <v>2425.06</v>
+        <v>1686.51</v>
       </c>
       <c r="DI22" s="24">
         <f>DJ22-DH22</f>
-        <v>35.0900000000001</v>
+        <v>20.54</v>
       </c>
       <c r="DJ22" s="24">
-        <v>2460.15</v>
+        <v>1707.05</v>
       </c>
       <c r="DK22" s="24">
         <f>DL22-DJ22</f>
-        <v>14.3800000000001</v>
+        <v>21.1100000000001</v>
       </c>
       <c r="DL22" s="24">
-        <v>2474.53</v>
+        <v>1728.16</v>
       </c>
       <c r="DM22" s="24">
         <f>DN22-DL22</f>
-        <v>21.7099999999996</v>
+        <v>45.05</v>
       </c>
       <c r="DN22" s="24">
-        <v>2496.24</v>
+        <v>1773.21</v>
       </c>
       <c r="DO22" s="23">
         <f>DP22-DN22</f>
-        <v>21.0900000000001</v>
+        <v>33.6599999999999</v>
       </c>
       <c r="DP22" s="24">
-        <v>2517.33</v>
+        <v>1806.87</v>
       </c>
       <c r="DQ22" s="24">
         <f>DR22-DP22</f>
-        <v>23.04</v>
+        <v>18.3400000000001</v>
       </c>
       <c r="DR22" s="24">
-        <v>2540.37</v>
+        <v>1825.21</v>
       </c>
       <c r="DS22" s="24">
         <f>DT22-DR22</f>
-        <v>17.1600000000003</v>
+        <v>33.3499999999999</v>
       </c>
       <c r="DT22" s="24">
-        <v>2557.53</v>
+        <v>1858.56</v>
       </c>
       <c r="DU22" s="24">
         <f>DV22-DT22</f>
-        <v>24.04</v>
+        <v>33.5</v>
       </c>
       <c r="DV22" s="24">
-        <v>2581.57</v>
+        <v>1892.06</v>
       </c>
       <c r="DW22" s="24">
         <f>DX22-DV22</f>
-        <v>18.5</v>
+        <v>23.9200000000001</v>
       </c>
       <c r="DX22" s="24">
-        <v>2600.07</v>
+        <v>1915.98</v>
       </c>
       <c r="DY22" s="24">
         <f>DZ22-DX22</f>
-        <v>42.25</v>
+        <v>19.04</v>
       </c>
       <c r="DZ22" s="24">
-        <v>2642.32</v>
+        <v>1935.02</v>
       </c>
       <c r="EA22" s="24">
         <f>EB22-DZ22</f>
-        <v>5.78999999999996</v>
+        <v>22.23</v>
       </c>
       <c r="EB22" s="24">
-        <v>2648.11</v>
+        <v>1957.25</v>
       </c>
       <c r="EC22" s="24">
         <f>ED22-EB22</f>
-        <v>9.62999999999965</v>
+        <v>15.51</v>
       </c>
       <c r="ED22" s="24">
-        <v>2657.74</v>
+        <v>1972.76</v>
       </c>
       <c r="EE22" s="24">
         <f>EF22-ED22</f>
-        <v>15.6100000000001</v>
+        <v>11.26</v>
       </c>
       <c r="EF22" s="24">
-        <v>2673.35</v>
+        <v>1984.02</v>
       </c>
       <c r="EG22" s="24">
         <f>EH22-EF22</f>
-        <v>2.74000000000024</v>
+        <v>25.0699999999999</v>
       </c>
       <c r="EH22" s="24">
-        <v>2676.09</v>
+        <v>2009.09</v>
       </c>
       <c r="EI22" s="24">
         <f>EJ22-EH22</f>
-        <v>26.8699999999999</v>
+        <v>23.4400000000001</v>
       </c>
       <c r="EJ22" s="24">
-        <v>2702.96</v>
+        <v>2032.53</v>
       </c>
       <c r="EK22" s="24">
         <f>EL22-EJ22</f>
-        <v>35.9299999999998</v>
+        <v>34.3300000000002</v>
       </c>
       <c r="EL22" s="24">
-        <v>2738.89</v>
+        <v>2066.86</v>
       </c>
       <c r="EM22" s="24">
         <f>EN22-EL22</f>
-        <v>5.05000000000018</v>
+        <v>10.48</v>
       </c>
       <c r="EN22" s="24">
-        <v>2743.94</v>
+        <v>2077.34</v>
       </c>
       <c r="EO22" s="24">
         <f>EP22-EN22</f>
-        <v>15.4899999999998</v>
+        <v>39.2399999999998</v>
       </c>
       <c r="EP22" s="24">
-        <v>2759.43</v>
+        <v>2116.58</v>
       </c>
       <c r="EQ22" s="24">
         <f>ER22-EP22</f>
-        <v>0.460000000000036</v>
+        <v>34.4200000000001</v>
       </c>
       <c r="ER22" s="24">
-        <v>2759.89</v>
+        <v>2151</v>
       </c>
       <c r="ES22" s="24">
         <f>ET22-ER22</f>
-        <v>1.38000000000011</v>
+        <v>26.2399999999998</v>
       </c>
       <c r="ET22" s="24">
-        <v>2761.27</v>
+        <v>2177.24</v>
       </c>
       <c r="EU22" s="24">
         <f>EV22-ET22</f>
-        <v>3.98000000000002</v>
+        <v>29</v>
       </c>
       <c r="EV22" s="24">
-        <v>2765.25</v>
-      </c>
-      <c r="EW22" s="23" t="s">
-        <v>97</v>
-      </c>
-      <c r="EX22" s="22">
-        <v>1206.37</v>
-      </c>
-      <c r="EY22" s="18" t="s">
-        <v>112</v>
-      </c>
-      <c r="EZ22" s="18">
-        <v>556.77</v>
-      </c>
-      <c r="FA22" s="2">
-        <v>30</v>
-      </c>
-      <c r="FB22" s="2">
-        <v>3.2</v>
-      </c>
-      <c r="FC22" s="2">
-        <v>78989</v>
-      </c>
-      <c r="FD22" s="9">
-        <f>2.79/(EV22/EX22)</f>
-        <v>1.21716745321399</v>
-      </c>
-      <c r="FE22" s="9">
+        <v>2206.24</v>
+      </c>
+      <c r="EW22" s="24">
+        <f>EX22-EV22</f>
+        <v>13.3000000000002</v>
+      </c>
+      <c r="EX22" s="24">
+        <v>2219.54</v>
+      </c>
+      <c r="EY22" s="23" t="s">
+        <v>123</v>
+      </c>
+      <c r="EZ22" s="21">
+        <v>745.39</v>
+      </c>
+      <c r="FA22" s="21" t="s">
+        <v>142</v>
+      </c>
+      <c r="FB22" s="21">
+        <v>368.34</v>
+      </c>
+      <c r="FC22" s="8">
+        <v>0</v>
+      </c>
+      <c r="FD22" s="8">
+        <v>1</v>
+      </c>
+      <c r="FE22" s="8">
+        <v>47256</v>
+      </c>
+      <c r="FF22" s="9">
+        <f>2.43/(EX22/EZ22)</f>
+        <v>0.816068960235004</v>
+      </c>
+      <c r="FG22" s="9">
         <f>BP22-D22</f>
-        <v>967.13</v>
+        <v>790.52</v>
+      </c>
+      <c r="FH22" s="9">
+        <f>EX22-ER22</f>
+        <v>68.54</v>
       </c>
     </row>
-    <row r="23" spans="1:161">
-      <c r="A23" s="8" t="s">
-        <v>98</v>
-      </c>
-      <c r="B23" s="8" t="s">
-        <v>145</v>
-      </c>
-      <c r="C23" s="8" t="s">
-        <v>141</v>
-      </c>
-      <c r="D23" s="8">
-        <v>363.88</v>
-      </c>
-      <c r="E23" s="8">
-        <f>F23-D23</f>
-        <v>14.21</v>
-      </c>
-      <c r="F23" s="8">
-        <v>378.09</v>
-      </c>
-      <c r="G23" s="8">
-        <f>H23-F23</f>
-        <v>11.22</v>
-      </c>
-      <c r="H23" s="8">
-        <v>389.31</v>
-      </c>
-      <c r="I23" s="8">
-        <f>J23-H23</f>
-        <v>13.62</v>
-      </c>
-      <c r="J23" s="8">
-        <v>402.93</v>
-      </c>
-      <c r="K23" s="8">
-        <f>L23-J23</f>
-        <v>11.13</v>
-      </c>
-      <c r="L23" s="8">
-        <v>414.06</v>
-      </c>
-      <c r="M23" s="8">
-        <f>N23-L23</f>
-        <v>17.39</v>
-      </c>
-      <c r="N23" s="8">
-        <v>431.45</v>
-      </c>
-      <c r="O23" s="8">
-        <f>P23-N23</f>
-        <v>6.32999999999998</v>
-      </c>
-      <c r="P23" s="8">
-        <v>437.78</v>
-      </c>
-      <c r="Q23" s="8">
-        <f>R23-P23</f>
-        <v>53.01</v>
-      </c>
-      <c r="R23" s="8">
-        <v>490.79</v>
-      </c>
-      <c r="S23" s="8">
-        <f>T23-R23</f>
-        <v>11.82</v>
-      </c>
-      <c r="T23" s="8">
-        <v>502.61</v>
-      </c>
-      <c r="U23" s="8">
-        <f>V23-T23</f>
-        <v>19.3099999999999</v>
-      </c>
-      <c r="V23" s="21">
-        <v>521.92</v>
-      </c>
-      <c r="W23" s="8">
-        <f>X23-V23</f>
-        <v>29.5400000000001</v>
-      </c>
-      <c r="X23" s="21">
-        <v>551.46</v>
-      </c>
-      <c r="Y23" s="8">
-        <f>Z23-X23</f>
-        <v>36.98</v>
-      </c>
-      <c r="Z23" s="8">
-        <v>588.44</v>
-      </c>
-      <c r="AA23" s="8">
-        <f>AB23-Z23</f>
-        <v>21.17</v>
-      </c>
-      <c r="AB23" s="8">
-        <v>609.61</v>
-      </c>
-      <c r="AC23" s="8">
-        <f>AD23-AB23</f>
-        <v>17.4399999999999</v>
-      </c>
-      <c r="AD23" s="8">
-        <v>627.05</v>
-      </c>
-      <c r="AE23" s="22">
-        <f>AF23-AD23</f>
-        <v>21.0500000000001</v>
-      </c>
-      <c r="AF23" s="22">
-        <v>648.1</v>
-      </c>
-      <c r="AG23" s="22">
-        <f>AH23-AF23</f>
-        <v>37.27</v>
-      </c>
-      <c r="AH23" s="22">
-        <v>685.37</v>
-      </c>
-      <c r="AI23" s="22">
-        <f>AJ23-AH23</f>
-        <v>25.0700000000001</v>
-      </c>
-      <c r="AJ23" s="22">
-        <v>710.44</v>
-      </c>
-      <c r="AK23" s="22">
-        <f>AL23-AJ23</f>
-        <v>22.64</v>
-      </c>
-      <c r="AL23" s="22">
-        <v>733.08</v>
-      </c>
-      <c r="AM23" s="22">
-        <f>AN23-AL23</f>
-        <v>28.76</v>
-      </c>
-      <c r="AN23" s="22">
-        <v>761.84</v>
-      </c>
-      <c r="AO23" s="22">
-        <f>AP23-AN23</f>
-        <v>12.24</v>
-      </c>
-      <c r="AP23" s="22">
-        <v>774.08</v>
-      </c>
-      <c r="AQ23" s="22">
-        <f>AR23-AP23</f>
-        <v>29.39</v>
-      </c>
-      <c r="AR23" s="22">
-        <v>803.47</v>
-      </c>
-      <c r="AS23" s="22">
+    <row r="23" spans="1:164">
+      <c r="A23" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="C23" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="D23" s="3"/>
+      <c r="E23" s="3"/>
+      <c r="F23" s="3"/>
+      <c r="G23" s="3"/>
+      <c r="H23" s="3"/>
+      <c r="I23" s="3"/>
+      <c r="J23" s="3"/>
+      <c r="K23" s="3"/>
+      <c r="L23" s="3"/>
+      <c r="M23" s="3"/>
+      <c r="N23" s="3"/>
+      <c r="O23" s="3"/>
+      <c r="P23" s="3"/>
+      <c r="Q23" s="3"/>
+      <c r="R23" s="3"/>
+      <c r="S23" s="3"/>
+      <c r="T23" s="3"/>
+      <c r="U23" s="3"/>
+      <c r="V23" s="25"/>
+      <c r="W23" s="3"/>
+      <c r="X23" s="25"/>
+      <c r="Y23" s="3"/>
+      <c r="Z23" s="3"/>
+      <c r="AA23" s="3"/>
+      <c r="AB23" s="3"/>
+      <c r="AC23" s="3"/>
+      <c r="AD23" s="3"/>
+      <c r="AE23" s="26"/>
+      <c r="AF23" s="26"/>
+      <c r="AG23" s="26"/>
+      <c r="AH23" s="26"/>
+      <c r="AI23" s="26"/>
+      <c r="AJ23" s="26"/>
+      <c r="AK23" s="26"/>
+      <c r="AL23" s="26"/>
+      <c r="AM23" s="26"/>
+      <c r="AN23" s="26"/>
+      <c r="AO23" s="26"/>
+      <c r="AP23" s="26"/>
+      <c r="AQ23" s="26"/>
+      <c r="AR23" s="26">
+        <v>686.23</v>
+      </c>
+      <c r="AS23" s="26">
         <f>AT23-AR23</f>
-        <v>33.97</v>
-      </c>
-      <c r="AT23" s="22">
-        <v>837.44</v>
-      </c>
-      <c r="AU23" s="23">
+        <v>0</v>
+      </c>
+      <c r="AT23" s="26">
+        <v>686.23</v>
+      </c>
+      <c r="AU23" s="27">
         <f>AV23-AT23</f>
-        <v>29.6999999999999</v>
-      </c>
-      <c r="AV23" s="23">
-        <v>867.14</v>
-      </c>
-      <c r="AW23" s="24">
+        <v>33.75</v>
+      </c>
+      <c r="AV23" s="27">
+        <v>719.98</v>
+      </c>
+      <c r="AW23" s="28">
         <f>AX23-AV23</f>
-        <v>21.75</v>
-      </c>
-      <c r="AX23" s="24">
-        <v>888.89</v>
-      </c>
-      <c r="AY23" s="24">
+        <v>24.6999999999999</v>
+      </c>
+      <c r="AX23" s="28">
+        <v>744.68</v>
+      </c>
+      <c r="AY23" s="28">
         <f>AZ23-AX23</f>
-        <v>37.0600000000001</v>
-      </c>
-      <c r="AZ23" s="24">
-        <v>925.95</v>
-      </c>
-      <c r="BA23" s="24">
+        <v>7.6400000000001</v>
+      </c>
+      <c r="AZ23" s="28">
+        <v>752.32</v>
+      </c>
+      <c r="BA23" s="28">
         <f>BB23-AZ23</f>
-        <v>14.3</v>
-      </c>
-      <c r="BB23" s="24">
-        <v>940.25</v>
-      </c>
-      <c r="BC23" s="24">
+        <v>41.02</v>
+      </c>
+      <c r="BB23" s="28">
+        <v>793.34</v>
+      </c>
+      <c r="BC23" s="28">
         <f>BD23-BB23</f>
-        <v>12.04</v>
-      </c>
-      <c r="BD23" s="24">
-        <v>952.29</v>
-      </c>
-      <c r="BE23" s="23">
+        <v>17.66</v>
+      </c>
+      <c r="BD23" s="28">
+        <v>811</v>
+      </c>
+      <c r="BE23" s="27">
         <f>BF23-BD23</f>
-        <v>39.5300000000001</v>
-      </c>
-      <c r="BF23" s="24">
-        <v>991.82</v>
-      </c>
-      <c r="BG23" s="24">
+        <v>6.5</v>
+      </c>
+      <c r="BF23" s="28">
+        <v>817.5</v>
+      </c>
+      <c r="BG23" s="28">
         <f>BH23-BF23</f>
-        <v>38.2599999999999</v>
-      </c>
-      <c r="BH23" s="24">
-        <v>1030.08</v>
-      </c>
-      <c r="BI23" s="24">
+        <v>13.03</v>
+      </c>
+      <c r="BH23" s="28">
+        <v>830.53</v>
+      </c>
+      <c r="BI23" s="28">
         <f>BJ23-BH23</f>
-        <v>35.53</v>
-      </c>
-      <c r="BJ23" s="24">
-        <v>1065.61</v>
-      </c>
-      <c r="BK23" s="24">
+        <v>11.5600000000001</v>
+      </c>
+      <c r="BJ23" s="28">
+        <v>842.09</v>
+      </c>
+      <c r="BK23" s="28">
         <f>BL23-BJ23</f>
-        <v>36.8300000000002</v>
-      </c>
-      <c r="BL23" s="24">
-        <v>1102.44</v>
-      </c>
-      <c r="BM23" s="24">
+        <v>11.9499999999999</v>
+      </c>
+      <c r="BL23" s="28">
+        <v>854.04</v>
+      </c>
+      <c r="BM23" s="28">
         <f>BN23-BL23</f>
-        <v>30.4199999999998</v>
-      </c>
-      <c r="BN23" s="24">
-        <v>1132.86</v>
-      </c>
-      <c r="BO23" s="24">
+        <v>28.2800000000001</v>
+      </c>
+      <c r="BN23" s="28">
+        <v>882.32</v>
+      </c>
+      <c r="BO23" s="28">
         <f>BP23-BN23</f>
-        <v>21.5400000000002</v>
-      </c>
-      <c r="BP23" s="24">
-        <v>1154.4</v>
-      </c>
-      <c r="BQ23" s="24">
+        <v>15.0799999999999</v>
+      </c>
+      <c r="BP23" s="28">
+        <v>897.4</v>
+      </c>
+      <c r="BQ23" s="28">
         <f>BR23-BP23</f>
-        <v>41.52</v>
-      </c>
-      <c r="BR23" s="24">
-        <v>1195.92</v>
-      </c>
-      <c r="BS23" s="24">
+        <v>8.04000000000008</v>
+      </c>
+      <c r="BR23" s="28">
+        <v>905.44</v>
+      </c>
+      <c r="BS23" s="28">
         <f>BT23-BR23</f>
-        <v>10.8</v>
-      </c>
-      <c r="BT23" s="24">
-        <v>1206.72</v>
-      </c>
-      <c r="BU23" s="24">
+        <v>35.1899999999999</v>
+      </c>
+      <c r="BT23" s="28">
+        <v>940.63</v>
+      </c>
+      <c r="BU23" s="28">
         <f>BV23-BT23</f>
-        <v>13.96</v>
-      </c>
-      <c r="BV23" s="24">
-        <v>1220.68</v>
-      </c>
-      <c r="BW23" s="24">
+        <v>-1.37</v>
+      </c>
+      <c r="BV23" s="28">
+        <v>939.26</v>
+      </c>
+      <c r="BW23" s="28">
         <f>BX23-BV23</f>
-        <v>10.74</v>
-      </c>
-      <c r="BX23" s="24">
-        <v>1231.42</v>
-      </c>
-      <c r="BY23" s="24">
+        <v>34.1</v>
+      </c>
+      <c r="BX23" s="28">
+        <v>973.36</v>
+      </c>
+      <c r="BY23" s="28">
         <f>BZ23-BX23</f>
-        <v>28.03</v>
-      </c>
-      <c r="BZ23" s="24">
-        <v>1259.45</v>
-      </c>
-      <c r="CA23" s="24">
+        <v>16.52</v>
+      </c>
+      <c r="BZ23" s="28">
+        <v>989.88</v>
+      </c>
+      <c r="CA23" s="28">
         <f>CB23-BZ23</f>
-        <v>47.29</v>
-      </c>
-      <c r="CB23" s="24">
-        <v>1306.74</v>
-      </c>
-      <c r="CC23" s="24">
+        <v>42.6799999999999</v>
+      </c>
+      <c r="CB23" s="28">
+        <v>1032.56</v>
+      </c>
+      <c r="CC23" s="28">
         <f>CD23-CB23</f>
-        <v>22.47</v>
-      </c>
-      <c r="CD23" s="24">
-        <v>1329.21</v>
-      </c>
-      <c r="CE23" s="24">
+        <v>23.6000000000001</v>
+      </c>
+      <c r="CD23" s="28">
+        <v>1056.16</v>
+      </c>
+      <c r="CE23" s="28">
         <f>CF23-CD23</f>
-        <v>9.03999999999996</v>
-      </c>
-      <c r="CF23" s="24">
-        <v>1338.25</v>
-      </c>
-      <c r="CG23" s="24">
+        <v>7.55999999999995</v>
+      </c>
+      <c r="CF23" s="28">
+        <v>1063.72</v>
+      </c>
+      <c r="CG23" s="28">
         <f>CH23-CF23</f>
-        <v>24.3599999999999</v>
-      </c>
-      <c r="CH23" s="24">
-        <v>1362.61</v>
-      </c>
-      <c r="CI23" s="24">
+        <v>14.1499999999999</v>
+      </c>
+      <c r="CH23" s="28">
+        <v>1077.87</v>
+      </c>
+      <c r="CI23" s="28">
         <f>CJ23-CH23</f>
-        <v>22.9300000000001</v>
-      </c>
-      <c r="CJ23" s="24">
-        <v>1385.54</v>
-      </c>
-      <c r="CK23" s="24">
+        <v>12.9200000000001</v>
+      </c>
+      <c r="CJ23" s="28">
+        <v>1090.79</v>
+      </c>
+      <c r="CK23" s="28">
         <f>CL23-CJ23</f>
-        <v>29.2</v>
-      </c>
-      <c r="CL23" s="24">
-        <v>1414.74</v>
-      </c>
-      <c r="CM23" s="24">
+        <v>14.96</v>
+      </c>
+      <c r="CL23" s="28">
+        <v>1105.75</v>
+      </c>
+      <c r="CM23" s="28">
         <f>CN23-CL23</f>
-        <v>13.6700000000001</v>
-      </c>
-      <c r="CN23" s="24">
-        <v>1428.41</v>
-      </c>
-      <c r="CO23" s="24">
+        <v>12.6400000000001</v>
+      </c>
+      <c r="CN23" s="28">
+        <v>1118.39</v>
+      </c>
+      <c r="CO23" s="28">
         <f>CP23-CN23</f>
-        <v>28.1699999999998</v>
-      </c>
-      <c r="CP23" s="24">
-        <v>1456.58</v>
-      </c>
-      <c r="CQ23" s="24">
+        <v>15.3399999999999</v>
+      </c>
+      <c r="CP23" s="28">
+        <v>1133.73</v>
+      </c>
+      <c r="CQ23" s="28">
         <f>CR23-CP23</f>
-        <v>19.3000000000002</v>
-      </c>
-      <c r="CR23" s="24">
-        <v>1475.88</v>
-      </c>
-      <c r="CS23" s="24">
+        <v>21.96</v>
+      </c>
+      <c r="CR23" s="28">
+        <v>1155.69</v>
+      </c>
+      <c r="CS23" s="28">
         <f>CT23-CR23</f>
-        <v>37.8199999999999</v>
-      </c>
-      <c r="CT23" s="24">
-        <v>1513.7</v>
-      </c>
-      <c r="CU23" s="24">
+        <v>32.4199999999998</v>
+      </c>
+      <c r="CT23" s="28">
+        <v>1188.11</v>
+      </c>
+      <c r="CU23" s="28">
         <f>CV23-CT23</f>
-        <v>16.77</v>
-      </c>
-      <c r="CV23" s="24">
-        <v>1530.47</v>
-      </c>
-      <c r="CW23" s="23">
+        <v>12.6300000000001</v>
+      </c>
+      <c r="CV23" s="28">
+        <v>1200.74</v>
+      </c>
+      <c r="CW23" s="27">
         <f>CX23-CV23</f>
-        <v>17.99</v>
-      </c>
-      <c r="CX23" s="24">
-        <v>1548.46</v>
-      </c>
-      <c r="CY23" s="24">
+        <v>23.8099999999999</v>
+      </c>
+      <c r="CX23" s="28">
+        <v>1224.55</v>
+      </c>
+      <c r="CY23" s="28">
         <f>CZ23-CX23</f>
-        <v>13.6399999999999</v>
-      </c>
-      <c r="CZ23" s="24">
-        <v>1562.1</v>
-      </c>
-      <c r="DA23" s="24">
+        <v>19.8800000000001</v>
+      </c>
+      <c r="CZ23" s="28">
+        <v>1244.43</v>
+      </c>
+      <c r="DA23" s="28">
         <f>DB23-CZ23</f>
-        <v>63.24</v>
-      </c>
-      <c r="DB23" s="24">
-        <v>1625.34</v>
-      </c>
-      <c r="DC23" s="24">
+        <v>15.3199999999999</v>
+      </c>
+      <c r="DB23" s="28">
+        <v>1259.75</v>
+      </c>
+      <c r="DC23" s="28">
         <f>DD23-DB23</f>
-        <v>23.72</v>
-      </c>
-      <c r="DD23" s="24">
-        <v>1649.06</v>
-      </c>
-      <c r="DE23" s="24">
+        <v>23.8399999999999</v>
+      </c>
+      <c r="DD23" s="28">
+        <v>1283.59</v>
+      </c>
+      <c r="DE23" s="28">
         <f>DF23-DD23</f>
-        <v>10.8099999999999</v>
-      </c>
-      <c r="DF23" s="24">
-        <v>1659.87</v>
-      </c>
-      <c r="DG23" s="24">
+        <v>39.6800000000001</v>
+      </c>
+      <c r="DF23" s="28">
+        <v>1323.27</v>
+      </c>
+      <c r="DG23" s="28">
         <f>DH23-DF23</f>
-        <v>26.6400000000001</v>
-      </c>
-      <c r="DH23" s="24">
-        <v>1686.51</v>
-      </c>
-      <c r="DI23" s="24">
+        <v>13.27</v>
+      </c>
+      <c r="DH23" s="28">
+        <v>1336.54</v>
+      </c>
+      <c r="DI23" s="28">
         <f>DJ23-DH23</f>
-        <v>20.54</v>
-      </c>
-      <c r="DJ23" s="24">
-        <v>1707.05</v>
-      </c>
-      <c r="DK23" s="24">
+        <v>13.74</v>
+      </c>
+      <c r="DJ23" s="28">
+        <v>1350.28</v>
+      </c>
+      <c r="DK23" s="28">
         <f>DL23-DJ23</f>
-        <v>21.1100000000001</v>
-      </c>
-      <c r="DL23" s="24">
-        <v>1728.16</v>
-      </c>
-      <c r="DM23" s="24">
+        <v>17.97</v>
+      </c>
+      <c r="DL23" s="28">
+        <v>1368.25</v>
+      </c>
+      <c r="DM23" s="28">
         <f>DN23-DL23</f>
-        <v>45.05</v>
-      </c>
-      <c r="DN23" s="24">
-        <v>1773.21</v>
-      </c>
-      <c r="DO23" s="23">
+        <v>19.3800000000001</v>
+      </c>
+      <c r="DN23" s="28">
+        <v>1387.63</v>
+      </c>
+      <c r="DO23" s="27">
         <f>DP23-DN23</f>
-        <v>33.6599999999999</v>
-      </c>
-      <c r="DP23" s="24">
-        <v>1806.87</v>
-      </c>
-      <c r="DQ23" s="24">
+        <v>10.4699999999998</v>
+      </c>
+      <c r="DP23" s="28">
+        <v>1398.1</v>
+      </c>
+      <c r="DQ23" s="28">
         <f>DR23-DP23</f>
-        <v>18.3400000000001</v>
-      </c>
-      <c r="DR23" s="24">
-        <v>1825.21</v>
-      </c>
-      <c r="DS23" s="24">
+        <v>48.6300000000001</v>
+      </c>
+      <c r="DR23" s="28">
+        <v>1446.73</v>
+      </c>
+      <c r="DS23" s="28">
         <f>DT23-DR23</f>
-        <v>33.3499999999999</v>
-      </c>
-      <c r="DT23" s="24">
-        <v>1858.56</v>
-      </c>
-      <c r="DU23" s="24">
+        <v>15.5999999999999</v>
+      </c>
+      <c r="DT23" s="28">
+        <v>1462.33</v>
+      </c>
+      <c r="DU23" s="28">
         <f>DV23-DT23</f>
-        <v>33.5</v>
-      </c>
-      <c r="DV23" s="24">
-        <v>1892.06</v>
-      </c>
-      <c r="DW23" s="24">
+        <v>56.0800000000002</v>
+      </c>
+      <c r="DV23" s="28">
+        <v>1518.41</v>
+      </c>
+      <c r="DW23" s="28">
         <f>DX23-DV23</f>
-        <v>23.9200000000001</v>
-      </c>
-      <c r="DX23" s="24">
-        <v>1915.98</v>
-      </c>
-      <c r="DY23" s="24">
+        <v>34.0599999999999</v>
+      </c>
+      <c r="DX23" s="28">
+        <v>1552.47</v>
+      </c>
+      <c r="DY23" s="28">
         <f>DZ23-DX23</f>
-        <v>19.04</v>
-      </c>
-      <c r="DZ23" s="24">
-        <v>1935.02</v>
-      </c>
-      <c r="EA23" s="24">
+        <v>15.0799999999999</v>
+      </c>
+      <c r="DZ23" s="28">
+        <v>1567.55</v>
+      </c>
+      <c r="EA23" s="28">
         <f>EB23-DZ23</f>
-        <v>22.23</v>
-      </c>
-      <c r="EB23" s="24">
-        <v>1957.25</v>
-      </c>
-      <c r="EC23" s="24">
+        <v>10.51</v>
+      </c>
+      <c r="EB23" s="28">
+        <v>1578.06</v>
+      </c>
+      <c r="EC23" s="28">
         <f>ED23-EB23</f>
-        <v>15.51</v>
-      </c>
-      <c r="ED23" s="24">
-        <v>1972.76</v>
-      </c>
-      <c r="EE23" s="24">
+        <v>31.3500000000001</v>
+      </c>
+      <c r="ED23" s="28">
+        <v>1609.41</v>
+      </c>
+      <c r="EE23" s="28">
         <f>EF23-ED23</f>
-        <v>11.26</v>
-      </c>
-      <c r="EF23" s="24">
-        <v>1984.02</v>
-      </c>
-      <c r="EG23" s="24">
+        <v>13.4199999999998</v>
+      </c>
+      <c r="EF23" s="28">
+        <v>1622.83</v>
+      </c>
+      <c r="EG23" s="28">
         <f>EH23-EF23</f>
-        <v>25.0699999999999</v>
-      </c>
-      <c r="EH23" s="24">
-        <v>2009.09</v>
-      </c>
-      <c r="EI23" s="24">
+        <v>33.8800000000001</v>
+      </c>
+      <c r="EH23" s="28">
+        <v>1656.71</v>
+      </c>
+      <c r="EI23" s="28">
         <f>EJ23-EH23</f>
-        <v>23.4400000000001</v>
-      </c>
-      <c r="EJ23" s="24">
-        <v>2032.53</v>
-      </c>
-      <c r="EK23" s="24">
+        <v>9.04999999999995</v>
+      </c>
+      <c r="EJ23" s="28">
+        <v>1665.76</v>
+      </c>
+      <c r="EK23" s="28">
         <f>EL23-EJ23</f>
-        <v>34.3300000000002</v>
-      </c>
-      <c r="EL23" s="24">
-        <v>2066.86</v>
-      </c>
-      <c r="EM23" s="24">
+        <v>41.21</v>
+      </c>
+      <c r="EL23" s="28">
+        <v>1706.97</v>
+      </c>
+      <c r="EM23" s="28">
         <f>EN23-EL23</f>
-        <v>10.48</v>
-      </c>
-      <c r="EN23" s="24">
-        <v>2077.34</v>
-      </c>
-      <c r="EO23" s="24">
+        <v>18.49</v>
+      </c>
+      <c r="EN23" s="28">
+        <v>1725.46</v>
+      </c>
+      <c r="EO23" s="28">
         <f>EP23-EN23</f>
-        <v>39.2399999999998</v>
-      </c>
-      <c r="EP23" s="24">
-        <v>2116.58</v>
-      </c>
-      <c r="EQ23" s="24">
+        <v>50.95</v>
+      </c>
+      <c r="EP23" s="28">
+        <v>1776.41</v>
+      </c>
+      <c r="EQ23" s="28">
         <f>ER23-EP23</f>
-        <v>34.4200000000001</v>
-      </c>
-      <c r="ER23" s="24">
-        <v>2151</v>
-      </c>
-      <c r="ES23" s="24">
+        <v>18.5799999999999</v>
+      </c>
+      <c r="ER23" s="28">
+        <v>1794.99</v>
+      </c>
+      <c r="ES23" s="28">
         <f>ET23-ER23</f>
-        <v>26.2399999999998</v>
-      </c>
-      <c r="ET23" s="24">
-        <v>2177.24</v>
-      </c>
-      <c r="EU23" s="24">
+        <v>-0.589999999999918</v>
+      </c>
+      <c r="ET23" s="28">
+        <v>1794.4</v>
+      </c>
+      <c r="EU23" s="28">
         <f>EV23-ET23</f>
-        <v>29</v>
-      </c>
-      <c r="EV23" s="24">
-        <v>2206.24</v>
-      </c>
-      <c r="EW23" s="23" t="s">
-        <v>120</v>
-      </c>
-      <c r="EX23" s="22">
-        <v>733.43</v>
-      </c>
-      <c r="EY23" s="22" t="s">
-        <v>139</v>
-      </c>
-      <c r="EZ23" s="22">
-        <v>368.34</v>
-      </c>
-      <c r="FA23" s="8">
-        <v>0</v>
-      </c>
-      <c r="FB23" s="8">
-        <v>1</v>
-      </c>
-      <c r="FC23" s="8">
-        <v>47256</v>
-      </c>
-      <c r="FD23" s="9">
-        <f>2.79/(EV23/EX23)</f>
-        <v>0.927491886648778</v>
-      </c>
-      <c r="FE23" s="9">
+        <v>11.0899999999999</v>
+      </c>
+      <c r="EV23" s="28">
+        <v>1805.49</v>
+      </c>
+      <c r="EW23" s="28">
+        <f>EX23-EV23</f>
+        <v>40.75</v>
+      </c>
+      <c r="EX23" s="28">
+        <v>1846.24</v>
+      </c>
+      <c r="EY23" s="27" t="s">
+        <v>137</v>
+      </c>
+      <c r="EZ23" s="26">
+        <v>434.94</v>
+      </c>
+      <c r="FA23" s="21" t="s">
+        <v>136</v>
+      </c>
+      <c r="FB23" s="21">
+        <v>148.34</v>
+      </c>
+      <c r="FC23" s="8"/>
+      <c r="FD23" s="8"/>
+      <c r="FE23" s="8"/>
+      <c r="FF23" s="9">
+        <f>2.43/(EX23/EZ23)</f>
+        <v>0.572463060057197</v>
+      </c>
+      <c r="FG23" s="9">
         <f>BP23-D23</f>
-        <v>790.52</v>
+        <v>897.4</v>
+      </c>
+      <c r="FH23" s="9">
+        <f>EX23-ER23</f>
+        <v>51.25</v>
       </c>
     </row>
-    <row r="24" spans="1:161">
+    <row r="24" spans="1:164">
       <c r="A24" s="3" t="s">
-        <v>98</v>
+        <v>105</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="D24" s="3"/>
       <c r="E24" s="3"/>
@@ -13995,2007 +14253,1734 @@
       <c r="AP24" s="26"/>
       <c r="AQ24" s="26"/>
       <c r="AR24" s="26">
-        <v>686.23</v>
+        <v>788.5</v>
       </c>
       <c r="AS24" s="26">
         <f>AT24-AR24</f>
         <v>0</v>
       </c>
       <c r="AT24" s="26">
-        <v>686.23</v>
+        <v>788.5</v>
       </c>
       <c r="AU24" s="27">
         <f>AV24-AT24</f>
-        <v>33.75</v>
+        <v>20.29</v>
       </c>
       <c r="AV24" s="27">
-        <v>719.98</v>
+        <v>808.79</v>
       </c>
       <c r="AW24" s="28">
         <f>AX24-AV24</f>
-        <v>24.6999999999999</v>
+        <v>8.25999999999999</v>
       </c>
       <c r="AX24" s="28">
-        <v>744.68</v>
+        <v>817.05</v>
       </c>
       <c r="AY24" s="28">
         <f>AZ24-AX24</f>
-        <v>7.6400000000001</v>
+        <v>15.9300000000001</v>
       </c>
       <c r="AZ24" s="28">
-        <v>752.32</v>
+        <v>832.98</v>
       </c>
       <c r="BA24" s="28">
         <f>BB24-AZ24</f>
-        <v>41.02</v>
+        <v>25.21</v>
       </c>
       <c r="BB24" s="28">
-        <v>793.34</v>
+        <v>858.19</v>
       </c>
       <c r="BC24" s="28">
         <f>BD24-BB24</f>
-        <v>17.66</v>
+        <v>13.5699999999999</v>
       </c>
       <c r="BD24" s="28">
-        <v>811</v>
+        <v>871.76</v>
       </c>
       <c r="BE24" s="27">
         <f>BF24-BD24</f>
-        <v>6.5</v>
+        <v>30.02</v>
       </c>
       <c r="BF24" s="28">
-        <v>817.5</v>
+        <v>901.78</v>
       </c>
       <c r="BG24" s="28">
         <f>BH24-BF24</f>
-        <v>13.03</v>
+        <v>44.85</v>
       </c>
       <c r="BH24" s="28">
-        <v>830.53</v>
+        <v>946.63</v>
       </c>
       <c r="BI24" s="28">
         <f>BJ24-BH24</f>
-        <v>11.5600000000001</v>
+        <v>31.9299999999999</v>
       </c>
       <c r="BJ24" s="28">
-        <v>842.09</v>
+        <v>978.56</v>
       </c>
       <c r="BK24" s="28">
         <f>BL24-BJ24</f>
-        <v>11.9499999999999</v>
+        <v>13.87</v>
       </c>
       <c r="BL24" s="28">
-        <v>854.04</v>
+        <v>992.43</v>
       </c>
       <c r="BM24" s="28">
         <f>BN24-BL24</f>
-        <v>28.2800000000001</v>
+        <v>37.7300000000001</v>
       </c>
       <c r="BN24" s="28">
-        <v>882.32</v>
+        <v>1030.16</v>
       </c>
       <c r="BO24" s="28">
         <f>BP24-BN24</f>
-        <v>15.0799999999999</v>
+        <v>14.8899999999999</v>
       </c>
       <c r="BP24" s="28">
-        <v>897.4</v>
+        <v>1045.05</v>
       </c>
       <c r="BQ24" s="28">
         <f>BR24-BP24</f>
-        <v>8.04000000000008</v>
+        <v>16.22</v>
       </c>
       <c r="BR24" s="28">
-        <v>905.44</v>
+        <v>1061.27</v>
       </c>
       <c r="BS24" s="28">
         <f>BT24-BR24</f>
-        <v>35.1899999999999</v>
+        <v>22.3299999999999</v>
       </c>
       <c r="BT24" s="28">
-        <v>940.63</v>
+        <v>1083.6</v>
       </c>
       <c r="BU24" s="28">
         <f>BV24-BT24</f>
-        <v>-1.37</v>
+        <v>14.6300000000001</v>
       </c>
       <c r="BV24" s="28">
-        <v>939.26</v>
+        <v>1098.23</v>
       </c>
       <c r="BW24" s="28">
         <f>BX24-BV24</f>
-        <v>34.1</v>
+        <v>18.8899999999999</v>
       </c>
       <c r="BX24" s="28">
-        <v>973.36</v>
+        <v>1117.12</v>
       </c>
       <c r="BY24" s="28">
         <f>BZ24-BX24</f>
-        <v>16.52</v>
+        <v>19.5900000000001</v>
       </c>
       <c r="BZ24" s="28">
-        <v>989.88</v>
+        <v>1136.71</v>
       </c>
       <c r="CA24" s="28">
         <f>CB24-BZ24</f>
-        <v>42.6799999999999</v>
+        <v>12.4099999999999</v>
       </c>
       <c r="CB24" s="28">
-        <v>1032.56</v>
+        <v>1149.12</v>
       </c>
       <c r="CC24" s="28">
         <f>CD24-CB24</f>
-        <v>23.6000000000001</v>
+        <v>13.6400000000001</v>
       </c>
       <c r="CD24" s="28">
-        <v>1056.16</v>
+        <v>1162.76</v>
       </c>
       <c r="CE24" s="28">
         <f>CF24-CD24</f>
-        <v>7.55999999999995</v>
+        <v>9.80999999999995</v>
       </c>
       <c r="CF24" s="28">
-        <v>1063.72</v>
+        <v>1172.57</v>
       </c>
       <c r="CG24" s="28">
         <f>CH24-CF24</f>
-        <v>14.1499999999999</v>
+        <v>47.8700000000001</v>
       </c>
       <c r="CH24" s="28">
-        <v>1077.87</v>
+        <v>1220.44</v>
       </c>
       <c r="CI24" s="28">
         <f>CJ24-CH24</f>
-        <v>12.9200000000001</v>
+        <v>10.6199999999999</v>
       </c>
       <c r="CJ24" s="28">
-        <v>1090.79</v>
+        <v>1231.06</v>
       </c>
       <c r="CK24" s="28">
         <f>CL24-CJ24</f>
-        <v>14.96</v>
+        <v>16.49</v>
       </c>
       <c r="CL24" s="28">
-        <v>1105.75</v>
+        <v>1247.55</v>
       </c>
       <c r="CM24" s="28">
         <f>CN24-CL24</f>
-        <v>12.6400000000001</v>
+        <v>20.51</v>
       </c>
       <c r="CN24" s="28">
-        <v>1118.39</v>
+        <v>1268.06</v>
       </c>
       <c r="CO24" s="28">
         <f>CP24-CN24</f>
-        <v>15.3399999999999</v>
+        <v>9.00999999999999</v>
       </c>
       <c r="CP24" s="28">
-        <v>1133.73</v>
+        <v>1277.07</v>
       </c>
       <c r="CQ24" s="28">
         <f>CR24-CP24</f>
-        <v>21.96</v>
+        <v>16.3300000000002</v>
       </c>
       <c r="CR24" s="28">
-        <v>1155.69</v>
+        <v>1293.4</v>
       </c>
       <c r="CS24" s="28">
         <f>CT24-CR24</f>
-        <v>32.4199999999998</v>
+        <v>25.78</v>
       </c>
       <c r="CT24" s="28">
-        <v>1188.11</v>
+        <v>1319.18</v>
       </c>
       <c r="CU24" s="28">
         <f>CV24-CT24</f>
-        <v>12.6300000000001</v>
+        <v>11.8799999999999</v>
       </c>
       <c r="CV24" s="28">
-        <v>1200.74</v>
+        <v>1331.06</v>
       </c>
       <c r="CW24" s="27">
         <f>CX24-CV24</f>
-        <v>23.8099999999999</v>
+        <v>9.26999999999998</v>
       </c>
       <c r="CX24" s="28">
-        <v>1224.55</v>
+        <v>1340.33</v>
       </c>
       <c r="CY24" s="28">
         <f>CZ24-CX24</f>
-        <v>19.8800000000001</v>
+        <v>11.6200000000001</v>
       </c>
       <c r="CZ24" s="28">
-        <v>1244.43</v>
+        <v>1351.95</v>
       </c>
       <c r="DA24" s="28">
         <f>DB24-CZ24</f>
-        <v>15.3199999999999</v>
+        <v>11.47</v>
       </c>
       <c r="DB24" s="28">
-        <v>1259.75</v>
+        <v>1363.42</v>
       </c>
       <c r="DC24" s="28">
         <f>DD24-DB24</f>
-        <v>23.8399999999999</v>
+        <v>12.4399999999998</v>
       </c>
       <c r="DD24" s="28">
-        <v>1283.59</v>
+        <v>1375.86</v>
       </c>
       <c r="DE24" s="28">
         <f>DF24-DD24</f>
-        <v>39.6800000000001</v>
+        <v>14.1400000000001</v>
       </c>
       <c r="DF24" s="28">
-        <v>1323.27</v>
+        <v>1390</v>
       </c>
       <c r="DG24" s="28">
         <f>DH24-DF24</f>
-        <v>13.27</v>
+        <v>19.78</v>
       </c>
       <c r="DH24" s="28">
-        <v>1336.54</v>
+        <v>1409.78</v>
       </c>
       <c r="DI24" s="28">
         <f>DJ24-DH24</f>
-        <v>13.74</v>
+        <v>12.99</v>
       </c>
       <c r="DJ24" s="28">
-        <v>1350.28</v>
+        <v>1422.77</v>
       </c>
       <c r="DK24" s="28">
         <f>DL24-DJ24</f>
-        <v>17.97</v>
+        <v>16.4300000000001</v>
       </c>
       <c r="DL24" s="28">
-        <v>1368.25</v>
+        <v>1439.2</v>
       </c>
       <c r="DM24" s="28">
         <f>DN24-DL24</f>
-        <v>19.3800000000001</v>
+        <v>23.8</v>
       </c>
       <c r="DN24" s="28">
-        <v>1387.63</v>
+        <v>1463</v>
       </c>
       <c r="DO24" s="27">
         <f>DP24-DN24</f>
-        <v>10.4699999999998</v>
+        <v>21.5699999999999</v>
       </c>
       <c r="DP24" s="28">
-        <v>1398.1</v>
+        <v>1484.57</v>
       </c>
       <c r="DQ24" s="28">
         <f>DR24-DP24</f>
-        <v>48.6300000000001</v>
+        <v>22.8100000000002</v>
       </c>
       <c r="DR24" s="28">
-        <v>1446.73</v>
+        <v>1507.38</v>
       </c>
       <c r="DS24" s="28">
         <f>DT24-DR24</f>
-        <v>15.5999999999999</v>
+        <v>19.1599999999999</v>
       </c>
       <c r="DT24" s="28">
-        <v>1462.33</v>
+        <v>1526.54</v>
       </c>
       <c r="DU24" s="28">
         <f>DV24-DT24</f>
-        <v>56.0800000000002</v>
+        <v>14.26</v>
       </c>
       <c r="DV24" s="28">
-        <v>1518.41</v>
+        <v>1540.8</v>
       </c>
       <c r="DW24" s="28">
         <f>DX24-DV24</f>
-        <v>34.0599999999999</v>
+        <v>32.03</v>
       </c>
       <c r="DX24" s="28">
-        <v>1552.47</v>
+        <v>1572.83</v>
       </c>
       <c r="DY24" s="28">
         <f>DZ24-DX24</f>
-        <v>15.0799999999999</v>
+        <v>9.72000000000003</v>
       </c>
       <c r="DZ24" s="28">
-        <v>1567.55</v>
+        <v>1582.55</v>
       </c>
       <c r="EA24" s="28">
         <f>EB24-DZ24</f>
-        <v>10.51</v>
+        <v>13.6700000000001</v>
       </c>
       <c r="EB24" s="28">
-        <v>1578.06</v>
+        <v>1596.22</v>
       </c>
       <c r="EC24" s="28">
         <f>ED24-EB24</f>
-        <v>31.3500000000001</v>
+        <v>17.6199999999999</v>
       </c>
       <c r="ED24" s="28">
-        <v>1609.41</v>
+        <v>1613.84</v>
       </c>
       <c r="EE24" s="28">
         <f>EF24-ED24</f>
-        <v>13.4199999999998</v>
+        <v>31.77</v>
       </c>
       <c r="EF24" s="28">
-        <v>1622.83</v>
+        <v>1645.61</v>
       </c>
       <c r="EG24" s="28">
         <f>EH24-EF24</f>
-        <v>33.8800000000001</v>
+        <v>13.0200000000002</v>
       </c>
       <c r="EH24" s="28">
-        <v>1656.71</v>
+        <v>1658.63</v>
       </c>
       <c r="EI24" s="28">
         <f>EJ24-EH24</f>
-        <v>9.04999999999995</v>
+        <v>12.3299999999999</v>
       </c>
       <c r="EJ24" s="28">
-        <v>1665.76</v>
+        <v>1670.96</v>
       </c>
       <c r="EK24" s="28">
         <f>EL24-EJ24</f>
-        <v>41.21</v>
+        <v>12.8899999999999</v>
       </c>
       <c r="EL24" s="28">
-        <v>1706.97</v>
+        <v>1683.85</v>
       </c>
       <c r="EM24" s="28">
         <f>EN24-EL24</f>
-        <v>18.49</v>
+        <v>12.45</v>
       </c>
       <c r="EN24" s="28">
-        <v>1725.46</v>
+        <v>1696.3</v>
       </c>
       <c r="EO24" s="28">
         <f>EP24-EN24</f>
-        <v>50.95</v>
+        <v>17.0800000000002</v>
       </c>
       <c r="EP24" s="28">
-        <v>1776.41</v>
+        <v>1713.38</v>
       </c>
       <c r="EQ24" s="28">
         <f>ER24-EP24</f>
-        <v>18.5799999999999</v>
+        <v>14.2299999999998</v>
       </c>
       <c r="ER24" s="28">
-        <v>1794.99</v>
+        <v>1727.61</v>
       </c>
       <c r="ES24" s="28">
         <f>ET24-ER24</f>
-        <v>-0.589999999999918</v>
+        <v>0.0200000000002092</v>
       </c>
       <c r="ET24" s="28">
-        <v>1794.4</v>
+        <v>1727.63</v>
       </c>
       <c r="EU24" s="28">
         <f>EV24-ET24</f>
-        <v>11.0899999999999</v>
+        <v>0</v>
       </c>
       <c r="EV24" s="28">
-        <v>1805.49</v>
-      </c>
-      <c r="EW24" s="27" t="s">
-        <v>134</v>
-      </c>
-      <c r="EX24" s="26">
-        <v>399.87</v>
-      </c>
-      <c r="EY24" s="22" t="s">
-        <v>133</v>
-      </c>
-      <c r="EZ24" s="22">
-        <v>148.34</v>
-      </c>
-      <c r="FA24" s="8"/>
-      <c r="FB24" s="8"/>
+        <v>1727.63</v>
+      </c>
+      <c r="EW24" s="28">
+        <f>EX24-EV24</f>
+        <v>0</v>
+      </c>
+      <c r="EX24" s="28">
+        <v>1727.63</v>
+      </c>
+      <c r="EY24" s="27" t="s">
+        <v>142</v>
+      </c>
+      <c r="EZ24" s="26">
+        <v>397.94</v>
+      </c>
+      <c r="FA24" s="21" t="s">
+        <v>123</v>
+      </c>
+      <c r="FB24" s="21">
+        <v>184.85</v>
+      </c>
       <c r="FC24" s="8"/>
-      <c r="FD24" s="9">
-        <f>2.79/(EV24/EX24)</f>
-        <v>0.617913862718708</v>
-      </c>
-      <c r="FE24" s="9">
+      <c r="FD24" s="8"/>
+      <c r="FE24" s="8"/>
+      <c r="FF24" s="9">
+        <f>2.43/(EX24/EZ24)</f>
+        <v>0.559722973090303</v>
+      </c>
+      <c r="FG24" s="9">
         <f>BP24-D24</f>
-        <v>897.4</v>
+        <v>1045.05</v>
+      </c>
+      <c r="FH24" s="9">
+        <f>EX24-ER24</f>
+        <v>0.0200000000002092</v>
       </c>
     </row>
-    <row r="25" spans="1:161">
+    <row r="25" spans="1:164">
       <c r="A25" s="3" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>141</v>
-      </c>
-      <c r="D25" s="3"/>
-      <c r="E25" s="3"/>
-      <c r="F25" s="3"/>
-      <c r="G25" s="3"/>
-      <c r="H25" s="3"/>
-      <c r="I25" s="3"/>
-      <c r="J25" s="3"/>
-      <c r="K25" s="3"/>
-      <c r="L25" s="3"/>
-      <c r="M25" s="3"/>
-      <c r="N25" s="3"/>
-      <c r="O25" s="3"/>
-      <c r="P25" s="3"/>
-      <c r="Q25" s="3"/>
-      <c r="R25" s="3"/>
-      <c r="S25" s="3"/>
-      <c r="T25" s="3"/>
-      <c r="U25" s="3"/>
-      <c r="V25" s="25"/>
-      <c r="W25" s="3"/>
-      <c r="X25" s="25"/>
-      <c r="Y25" s="3"/>
-      <c r="Z25" s="3"/>
-      <c r="AA25" s="3"/>
-      <c r="AB25" s="3"/>
-      <c r="AC25" s="3"/>
-      <c r="AD25" s="3"/>
-      <c r="AE25" s="26"/>
-      <c r="AF25" s="26"/>
-      <c r="AG25" s="26"/>
-      <c r="AH25" s="26"/>
-      <c r="AI25" s="26"/>
-      <c r="AJ25" s="26"/>
-      <c r="AK25" s="26"/>
-      <c r="AL25" s="26"/>
-      <c r="AM25" s="26"/>
-      <c r="AN25" s="26"/>
-      <c r="AO25" s="26"/>
-      <c r="AP25" s="26"/>
-      <c r="AQ25" s="26"/>
+        <v>135</v>
+      </c>
+      <c r="D25" s="3">
+        <v>407.35</v>
+      </c>
+      <c r="E25" s="3">
+        <f>F25-D25</f>
+        <v>13.86</v>
+      </c>
+      <c r="F25" s="3">
+        <v>421.21</v>
+      </c>
+      <c r="G25" s="3">
+        <f>H25-F25</f>
+        <v>16.43</v>
+      </c>
+      <c r="H25" s="3">
+        <v>437.64</v>
+      </c>
+      <c r="I25" s="3">
+        <f>J25-H25</f>
+        <v>13.64</v>
+      </c>
+      <c r="J25" s="3">
+        <v>451.28</v>
+      </c>
+      <c r="K25" s="3">
+        <f>L25-J25</f>
+        <v>11.6</v>
+      </c>
+      <c r="L25" s="3">
+        <v>462.88</v>
+      </c>
+      <c r="M25" s="3">
+        <f>N25-L25</f>
+        <v>47.68</v>
+      </c>
+      <c r="N25" s="3">
+        <v>510.56</v>
+      </c>
+      <c r="O25" s="3">
+        <f>P25-N25</f>
+        <v>20.51</v>
+      </c>
+      <c r="P25" s="3">
+        <v>531.07</v>
+      </c>
+      <c r="Q25" s="3">
+        <f>R25-P25</f>
+        <v>18.6099999999999</v>
+      </c>
+      <c r="R25" s="3">
+        <v>549.68</v>
+      </c>
+      <c r="S25" s="3">
+        <f>T25-R25</f>
+        <v>11.9400000000001</v>
+      </c>
+      <c r="T25" s="3">
+        <v>561.62</v>
+      </c>
+      <c r="U25" s="3">
+        <f>V25-T25</f>
+        <v>16.23</v>
+      </c>
+      <c r="V25" s="25">
+        <v>577.85</v>
+      </c>
+      <c r="W25" s="3">
+        <f>X25-V25</f>
+        <v>15.28</v>
+      </c>
+      <c r="X25" s="25">
+        <v>593.13</v>
+      </c>
+      <c r="Y25" s="3">
+        <f>Z25-X25</f>
+        <v>33.2</v>
+      </c>
+      <c r="Z25" s="3">
+        <v>626.33</v>
+      </c>
+      <c r="AA25" s="3">
+        <f>AB25-Z25</f>
+        <v>16.7199999999999</v>
+      </c>
+      <c r="AB25" s="3">
+        <v>643.05</v>
+      </c>
+      <c r="AC25" s="3">
+        <f>AD25-AB25</f>
+        <v>11.9300000000001</v>
+      </c>
+      <c r="AD25" s="3">
+        <v>654.98</v>
+      </c>
+      <c r="AE25" s="26">
+        <f>AF25-AD25</f>
+        <v>9.16999999999996</v>
+      </c>
+      <c r="AF25" s="26">
+        <v>664.15</v>
+      </c>
+      <c r="AG25" s="26">
+        <f>AH25-AF25</f>
+        <v>25.0500000000001</v>
+      </c>
+      <c r="AH25" s="26">
+        <v>689.2</v>
+      </c>
+      <c r="AI25" s="26">
+        <f>AJ25-AH25</f>
+        <v>9.88999999999999</v>
+      </c>
+      <c r="AJ25" s="26">
+        <v>699.09</v>
+      </c>
+      <c r="AK25" s="26">
+        <f>AL25-AJ25</f>
+        <v>19.55</v>
+      </c>
+      <c r="AL25" s="26">
+        <v>718.64</v>
+      </c>
+      <c r="AM25" s="26">
+        <f>AN25-AL25</f>
+        <v>15.5</v>
+      </c>
+      <c r="AN25" s="26">
+        <v>734.14</v>
+      </c>
+      <c r="AO25" s="26">
+        <f>AP25-AN25</f>
+        <v>17.77</v>
+      </c>
+      <c r="AP25" s="26">
+        <v>751.91</v>
+      </c>
+      <c r="AQ25" s="26">
+        <f>AR25-AP25</f>
+        <v>6.73000000000002</v>
+      </c>
       <c r="AR25" s="26">
-        <v>788.5</v>
+        <v>758.64</v>
       </c>
       <c r="AS25" s="26">
         <f>AT25-AR25</f>
-        <v>0</v>
+        <v>25.71</v>
       </c>
       <c r="AT25" s="26">
-        <v>788.5</v>
+        <v>784.35</v>
       </c>
       <c r="AU25" s="27">
         <f>AV25-AT25</f>
-        <v>20.29</v>
+        <v>6.80999999999995</v>
       </c>
       <c r="AV25" s="27">
-        <v>808.79</v>
+        <v>791.16</v>
       </c>
       <c r="AW25" s="28">
         <f>AX25-AV25</f>
-        <v>8.25999999999999</v>
+        <v>22.99</v>
       </c>
       <c r="AX25" s="28">
-        <v>817.05</v>
+        <v>814.15</v>
       </c>
       <c r="AY25" s="28">
         <f>AZ25-AX25</f>
-        <v>15.9300000000001</v>
+        <v>7.02999999999997</v>
       </c>
       <c r="AZ25" s="28">
-        <v>832.98</v>
+        <v>821.18</v>
       </c>
       <c r="BA25" s="28">
         <f>BB25-AZ25</f>
-        <v>25.21</v>
+        <v>10.8000000000001</v>
       </c>
       <c r="BB25" s="28">
-        <v>858.19</v>
+        <v>831.98</v>
       </c>
       <c r="BC25" s="28">
         <f>BD25-BB25</f>
-        <v>13.5699999999999</v>
+        <v>9.29999999999995</v>
       </c>
       <c r="BD25" s="28">
-        <v>871.76</v>
+        <v>841.28</v>
       </c>
       <c r="BE25" s="27">
         <f>BF25-BD25</f>
-        <v>30.02</v>
+        <v>10.27</v>
       </c>
       <c r="BF25" s="28">
-        <v>901.78</v>
+        <v>851.55</v>
       </c>
       <c r="BG25" s="28">
         <f>BH25-BF25</f>
-        <v>44.85</v>
+        <v>5.25</v>
       </c>
       <c r="BH25" s="28">
-        <v>946.63</v>
+        <v>856.8</v>
       </c>
       <c r="BI25" s="28">
         <f>BJ25-BH25</f>
-        <v>31.9299999999999</v>
+        <v>38.2900000000001</v>
       </c>
       <c r="BJ25" s="28">
-        <v>978.56</v>
+        <v>895.09</v>
       </c>
       <c r="BK25" s="28">
         <f>BL25-BJ25</f>
-        <v>13.87</v>
+        <v>5.57999999999993</v>
       </c>
       <c r="BL25" s="28">
-        <v>992.43</v>
+        <v>900.67</v>
       </c>
       <c r="BM25" s="28">
         <f>BN25-BL25</f>
-        <v>37.7300000000001</v>
+        <v>8.44000000000005</v>
       </c>
       <c r="BN25" s="28">
-        <v>1030.16</v>
+        <v>909.11</v>
       </c>
       <c r="BO25" s="28">
         <f>BP25-BN25</f>
-        <v>14.8899999999999</v>
+        <v>15.85</v>
       </c>
       <c r="BP25" s="28">
-        <v>1045.05</v>
+        <v>924.96</v>
       </c>
       <c r="BQ25" s="28">
         <f>BR25-BP25</f>
-        <v>16.22</v>
+        <v>18.7199999999999</v>
       </c>
       <c r="BR25" s="28">
-        <v>1061.27</v>
+        <v>943.68</v>
       </c>
       <c r="BS25" s="28">
         <f>BT25-BR25</f>
-        <v>22.3299999999999</v>
+        <v>7.2600000000001</v>
       </c>
       <c r="BT25" s="28">
-        <v>1083.6</v>
+        <v>950.94</v>
       </c>
       <c r="BU25" s="28">
         <f>BV25-BT25</f>
-        <v>14.6300000000001</v>
+        <v>12.5599999999999</v>
       </c>
       <c r="BV25" s="28">
-        <v>1098.23</v>
+        <v>963.5</v>
       </c>
       <c r="BW25" s="28">
         <f>BX25-BV25</f>
-        <v>18.8899999999999</v>
+        <v>22.38</v>
       </c>
       <c r="BX25" s="28">
-        <v>1117.12</v>
+        <v>985.88</v>
       </c>
       <c r="BY25" s="28">
         <f>BZ25-BX25</f>
-        <v>19.5900000000001</v>
+        <v>6.41999999999996</v>
       </c>
       <c r="BZ25" s="28">
-        <v>1136.71</v>
+        <v>992.3</v>
       </c>
       <c r="CA25" s="28">
         <f>CB25-BZ25</f>
-        <v>12.4099999999999</v>
+        <v>17.48</v>
       </c>
       <c r="CB25" s="28">
-        <v>1149.12</v>
+        <v>1009.78</v>
       </c>
       <c r="CC25" s="28">
         <f>CD25-CB25</f>
-        <v>13.6400000000001</v>
+        <v>12.87</v>
       </c>
       <c r="CD25" s="28">
-        <v>1162.76</v>
+        <v>1022.65</v>
       </c>
       <c r="CE25" s="28">
         <f>CF25-CD25</f>
-        <v>9.80999999999995</v>
+        <v>15.34</v>
       </c>
       <c r="CF25" s="28">
-        <v>1172.57</v>
+        <v>1037.99</v>
       </c>
       <c r="CG25" s="28">
         <f>CH25-CF25</f>
-        <v>47.8700000000001</v>
+        <v>11.4200000000001</v>
       </c>
       <c r="CH25" s="28">
-        <v>1220.44</v>
+        <v>1049.41</v>
       </c>
       <c r="CI25" s="28">
         <f>CJ25-CH25</f>
-        <v>10.6199999999999</v>
+        <v>17.9299999999998</v>
       </c>
       <c r="CJ25" s="28">
-        <v>1231.06</v>
+        <v>1067.34</v>
       </c>
       <c r="CK25" s="28">
         <f>CL25-CJ25</f>
-        <v>16.49</v>
+        <v>16.5</v>
       </c>
       <c r="CL25" s="28">
-        <v>1247.55</v>
+        <v>1083.84</v>
       </c>
       <c r="CM25" s="28">
         <f>CN25-CL25</f>
-        <v>20.51</v>
+        <v>12.4100000000001</v>
       </c>
       <c r="CN25" s="28">
-        <v>1268.06</v>
+        <v>1096.25</v>
       </c>
       <c r="CO25" s="28">
         <f>CP25-CN25</f>
-        <v>9.00999999999999</v>
+        <v>12.45</v>
       </c>
       <c r="CP25" s="28">
-        <v>1277.07</v>
+        <v>1108.7</v>
       </c>
       <c r="CQ25" s="28">
         <f>CR25-CP25</f>
-        <v>16.3300000000002</v>
+        <v>6.53999999999996</v>
       </c>
       <c r="CR25" s="28">
-        <v>1293.4</v>
+        <v>1115.24</v>
       </c>
       <c r="CS25" s="28">
         <f>CT25-CR25</f>
-        <v>25.78</v>
+        <v>19.04</v>
       </c>
       <c r="CT25" s="28">
-        <v>1319.18</v>
+        <v>1134.28</v>
       </c>
       <c r="CU25" s="28">
         <f>CV25-CT25</f>
-        <v>11.8799999999999</v>
+        <v>12.6100000000001</v>
       </c>
       <c r="CV25" s="28">
-        <v>1331.06</v>
+        <v>1146.89</v>
       </c>
       <c r="CW25" s="27">
         <f>CX25-CV25</f>
-        <v>9.26999999999998</v>
+        <v>3.52999999999997</v>
       </c>
       <c r="CX25" s="28">
-        <v>1340.33</v>
+        <v>1150.42</v>
       </c>
       <c r="CY25" s="28">
         <f>CZ25-CX25</f>
-        <v>11.6200000000001</v>
+        <v>44.3299999999999</v>
       </c>
       <c r="CZ25" s="28">
-        <v>1351.95</v>
+        <v>1194.75</v>
       </c>
       <c r="DA25" s="28">
         <f>DB25-CZ25</f>
-        <v>11.47</v>
+        <v>3.44000000000005</v>
       </c>
       <c r="DB25" s="28">
-        <v>1363.42</v>
+        <v>1198.19</v>
       </c>
       <c r="DC25" s="28">
         <f>DD25-DB25</f>
-        <v>12.4399999999998</v>
+        <v>11.3199999999999</v>
       </c>
       <c r="DD25" s="28">
-        <v>1375.86</v>
+        <v>1209.51</v>
       </c>
       <c r="DE25" s="28">
         <f>DF25-DD25</f>
-        <v>14.1400000000001</v>
+        <v>6.08999999999992</v>
       </c>
       <c r="DF25" s="28">
-        <v>1390</v>
+        <v>1215.6</v>
       </c>
       <c r="DG25" s="28">
         <f>DH25-DF25</f>
-        <v>19.78</v>
+        <v>2.80000000000018</v>
       </c>
       <c r="DH25" s="28">
-        <v>1409.78</v>
+        <v>1218.4</v>
       </c>
       <c r="DI25" s="28">
         <f>DJ25-DH25</f>
-        <v>12.99</v>
+        <v>11.3899999999999</v>
       </c>
       <c r="DJ25" s="28">
-        <v>1422.77</v>
+        <v>1229.79</v>
       </c>
       <c r="DK25" s="28">
         <f>DL25-DJ25</f>
-        <v>16.4300000000001</v>
+        <v>14.1500000000001</v>
       </c>
       <c r="DL25" s="28">
-        <v>1439.2</v>
+        <v>1243.94</v>
       </c>
       <c r="DM25" s="28">
         <f>DN25-DL25</f>
-        <v>23.8</v>
+        <v>12.46</v>
       </c>
       <c r="DN25" s="28">
-        <v>1463</v>
+        <v>1256.4</v>
       </c>
       <c r="DO25" s="27">
         <f>DP25-DN25</f>
-        <v>21.5699999999999</v>
+        <v>6.90999999999985</v>
       </c>
       <c r="DP25" s="28">
-        <v>1484.57</v>
+        <v>1263.31</v>
       </c>
       <c r="DQ25" s="28">
         <f>DR25-DP25</f>
-        <v>22.8100000000002</v>
+        <v>9.53999999999996</v>
       </c>
       <c r="DR25" s="28">
-        <v>1507.38</v>
+        <v>1272.85</v>
       </c>
       <c r="DS25" s="28">
         <f>DT25-DR25</f>
-        <v>19.1599999999999</v>
+        <v>9.12000000000012</v>
       </c>
       <c r="DT25" s="28">
-        <v>1526.54</v>
+        <v>1281.97</v>
       </c>
       <c r="DU25" s="28">
         <f>DV25-DT25</f>
-        <v>14.26</v>
+        <v>17.4300000000001</v>
       </c>
       <c r="DV25" s="28">
-        <v>1540.8</v>
+        <v>1299.4</v>
       </c>
       <c r="DW25" s="28">
         <f>DX25-DV25</f>
-        <v>32.03</v>
+        <v>10.1099999999999</v>
       </c>
       <c r="DX25" s="28">
-        <v>1572.83</v>
+        <v>1309.51</v>
       </c>
       <c r="DY25" s="28">
         <f>DZ25-DX25</f>
-        <v>9.72000000000003</v>
+        <v>6.31999999999994</v>
       </c>
       <c r="DZ25" s="28">
-        <v>1582.55</v>
+        <v>1315.83</v>
       </c>
       <c r="EA25" s="28">
         <f>EB25-DZ25</f>
-        <v>13.6700000000001</v>
+        <v>15.03</v>
       </c>
       <c r="EB25" s="28">
-        <v>1596.22</v>
+        <v>1330.86</v>
       </c>
       <c r="EC25" s="28">
         <f>ED25-EB25</f>
-        <v>17.6199999999999</v>
+        <v>34.6300000000001</v>
       </c>
       <c r="ED25" s="28">
-        <v>1613.84</v>
+        <v>1365.49</v>
       </c>
       <c r="EE25" s="28">
         <f>EF25-ED25</f>
-        <v>31.77</v>
+        <v>-2.88000000000011</v>
       </c>
       <c r="EF25" s="28">
-        <v>1645.61</v>
+        <v>1362.61</v>
       </c>
       <c r="EG25" s="28">
         <f>EH25-EF25</f>
-        <v>13.0200000000002</v>
+        <v>24.0300000000002</v>
       </c>
       <c r="EH25" s="28">
-        <v>1658.63</v>
+        <v>1386.64</v>
       </c>
       <c r="EI25" s="28">
         <f>EJ25-EH25</f>
-        <v>12.3299999999999</v>
+        <v>2.06999999999994</v>
       </c>
       <c r="EJ25" s="28">
-        <v>1670.96</v>
+        <v>1388.71</v>
       </c>
       <c r="EK25" s="28">
         <f>EL25-EJ25</f>
-        <v>12.8899999999999</v>
+        <v>6.64999999999986</v>
       </c>
       <c r="EL25" s="28">
-        <v>1683.85</v>
+        <v>1395.36</v>
       </c>
       <c r="EM25" s="28">
         <f>EN25-EL25</f>
-        <v>12.45</v>
+        <v>8.23000000000002</v>
       </c>
       <c r="EN25" s="28">
-        <v>1696.3</v>
+        <v>1403.59</v>
       </c>
       <c r="EO25" s="28">
         <f>EP25-EN25</f>
-        <v>17.0800000000002</v>
+        <v>19.0700000000002</v>
       </c>
       <c r="EP25" s="28">
-        <v>1713.38</v>
+        <v>1422.66</v>
       </c>
       <c r="EQ25" s="28">
         <f>ER25-EP25</f>
-        <v>14.2299999999998</v>
+        <v>1.39999999999986</v>
       </c>
       <c r="ER25" s="28">
-        <v>1727.61</v>
+        <v>1424.06</v>
       </c>
       <c r="ES25" s="28">
         <f>ET25-ER25</f>
-        <v>0.0200000000002092</v>
+        <v>4.52999999999997</v>
       </c>
       <c r="ET25" s="28">
-        <v>1727.63</v>
+        <v>1428.59</v>
       </c>
       <c r="EU25" s="28">
         <f>EV25-ET25</f>
         <v>0</v>
       </c>
       <c r="EV25" s="28">
-        <v>1727.63</v>
-      </c>
-      <c r="EW25" s="27" t="s">
-        <v>139</v>
-      </c>
-      <c r="EX25" s="26">
-        <v>397.94</v>
-      </c>
-      <c r="EY25" s="22" t="s">
-        <v>120</v>
-      </c>
-      <c r="EZ25" s="22">
-        <v>184.85</v>
-      </c>
-      <c r="FA25" s="8"/>
-      <c r="FB25" s="8"/>
-      <c r="FC25" s="8"/>
-      <c r="FD25" s="9">
-        <f>2.79/(EV25/EX25)</f>
-        <v>0.642644895029607</v>
-      </c>
-      <c r="FE25" s="9">
+        <v>1428.59</v>
+      </c>
+      <c r="EW25" s="28">
+        <f>EX25-EV25</f>
+        <v>0</v>
+      </c>
+      <c r="EX25" s="28">
+        <v>1428.59</v>
+      </c>
+      <c r="EY25" s="27" t="s">
+        <v>108</v>
+      </c>
+      <c r="EZ25" s="26">
+        <v>674.85</v>
+      </c>
+      <c r="FA25" s="21" t="s">
+        <v>151</v>
+      </c>
+      <c r="FB25" s="21">
+        <v>293.75</v>
+      </c>
+      <c r="FC25" s="8">
+        <v>30</v>
+      </c>
+      <c r="FD25" s="8">
+        <v>2.4</v>
+      </c>
+      <c r="FE25" s="8">
+        <v>43895</v>
+      </c>
+      <c r="FF25" s="9">
+        <f>2.43/(EX25/EZ25)</f>
+        <v>1.14790492723595</v>
+      </c>
+      <c r="FG25" s="9">
         <f>BP25-D25</f>
-        <v>1045.05</v>
+        <v>517.61</v>
+      </c>
+      <c r="FH25" s="9">
+        <f>EX25-ER25</f>
+        <v>4.52999999999997</v>
       </c>
     </row>
-    <row r="26" spans="1:161">
+    <row r="26" spans="1:164">
       <c r="A26" s="3" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>132</v>
+        <v>144</v>
       </c>
       <c r="D26" s="3">
-        <v>407.35</v>
+        <v>552.79</v>
       </c>
       <c r="E26" s="3">
         <f>F26-D26</f>
-        <v>13.86</v>
+        <v>15.9400000000001</v>
       </c>
       <c r="F26" s="3">
-        <v>421.21</v>
+        <v>568.73</v>
       </c>
       <c r="G26" s="3">
         <f>H26-F26</f>
-        <v>16.43</v>
+        <v>1.61000000000001</v>
       </c>
       <c r="H26" s="3">
-        <v>437.64</v>
+        <v>570.34</v>
       </c>
       <c r="I26" s="3">
         <f>J26-H26</f>
-        <v>13.64</v>
+        <v>7.13999999999999</v>
       </c>
       <c r="J26" s="3">
-        <v>451.28</v>
+        <v>577.48</v>
       </c>
       <c r="K26" s="3">
         <f>L26-J26</f>
-        <v>11.6</v>
+        <v>2.88999999999999</v>
       </c>
       <c r="L26" s="3">
-        <v>462.88</v>
+        <v>580.37</v>
       </c>
       <c r="M26" s="3">
         <f>N26-L26</f>
-        <v>47.68</v>
+        <v>2.55999999999995</v>
       </c>
       <c r="N26" s="3">
-        <v>510.56</v>
+        <v>582.93</v>
       </c>
       <c r="O26" s="3">
         <f>P26-N26</f>
-        <v>20.51</v>
+        <v>24.99</v>
       </c>
       <c r="P26" s="3">
-        <v>531.07</v>
+        <v>607.92</v>
       </c>
       <c r="Q26" s="3">
         <f>R26-P26</f>
-        <v>18.6099999999999</v>
+        <v>0.330000000000041</v>
       </c>
       <c r="R26" s="3">
-        <v>549.68</v>
+        <v>608.25</v>
       </c>
       <c r="S26" s="3">
         <f>T26-R26</f>
-        <v>11.9400000000001</v>
+        <v>1.80999999999995</v>
       </c>
       <c r="T26" s="3">
-        <v>561.62</v>
+        <v>610.06</v>
       </c>
       <c r="U26" s="3">
         <f>V26-T26</f>
-        <v>16.23</v>
+        <v>0.560000000000059</v>
       </c>
       <c r="V26" s="25">
-        <v>577.85</v>
+        <v>610.62</v>
       </c>
       <c r="W26" s="3">
         <f>X26-V26</f>
-        <v>15.28</v>
+        <v>3.83000000000004</v>
       </c>
       <c r="X26" s="25">
-        <v>593.13</v>
+        <v>614.45</v>
       </c>
       <c r="Y26" s="3">
         <f>Z26-X26</f>
-        <v>33.2</v>
+        <v>0.189999999999941</v>
       </c>
       <c r="Z26" s="3">
-        <v>626.33</v>
+        <v>614.64</v>
       </c>
       <c r="AA26" s="3">
         <f>AB26-Z26</f>
-        <v>16.7199999999999</v>
+        <v>0.690000000000055</v>
       </c>
       <c r="AB26" s="3">
-        <v>643.05</v>
+        <v>615.33</v>
       </c>
       <c r="AC26" s="3">
         <f>AD26-AB26</f>
-        <v>11.9300000000001</v>
+        <v>6.64999999999998</v>
       </c>
       <c r="AD26" s="3">
-        <v>654.98</v>
+        <v>621.98</v>
       </c>
       <c r="AE26" s="26">
         <f>AF26-AD26</f>
-        <v>9.16999999999996</v>
+        <v>0</v>
       </c>
       <c r="AF26" s="26">
-        <v>664.15</v>
+        <v>621.98</v>
       </c>
       <c r="AG26" s="26">
         <f>AH26-AF26</f>
-        <v>25.0500000000001</v>
+        <v>13.62</v>
       </c>
       <c r="AH26" s="26">
-        <v>689.2</v>
+        <v>635.6</v>
       </c>
       <c r="AI26" s="26">
         <f>AJ26-AH26</f>
-        <v>9.88999999999999</v>
+        <v>16.48</v>
       </c>
       <c r="AJ26" s="26">
-        <v>699.09</v>
+        <v>652.08</v>
       </c>
       <c r="AK26" s="26">
         <f>AL26-AJ26</f>
-        <v>19.55</v>
+        <v>5.84999999999991</v>
       </c>
       <c r="AL26" s="26">
-        <v>718.64</v>
+        <v>657.93</v>
       </c>
       <c r="AM26" s="26">
         <f>AN26-AL26</f>
-        <v>15.5</v>
+        <v>5.80000000000007</v>
       </c>
       <c r="AN26" s="26">
-        <v>734.14</v>
+        <v>663.73</v>
       </c>
       <c r="AO26" s="26">
         <f>AP26-AN26</f>
-        <v>17.77</v>
+        <v>13.75</v>
       </c>
       <c r="AP26" s="26">
-        <v>751.91</v>
+        <v>677.48</v>
       </c>
       <c r="AQ26" s="26">
         <f>AR26-AP26</f>
-        <v>6.73000000000002</v>
+        <v>3.60000000000002</v>
       </c>
       <c r="AR26" s="26">
-        <v>758.64</v>
+        <v>681.08</v>
       </c>
       <c r="AS26" s="26">
         <f>AT26-AR26</f>
-        <v>25.71</v>
+        <v>12.0799999999999</v>
       </c>
       <c r="AT26" s="26">
-        <v>784.35</v>
+        <v>693.16</v>
       </c>
       <c r="AU26" s="27">
         <f>AV26-AT26</f>
-        <v>6.80999999999995</v>
+        <v>4.29000000000008</v>
       </c>
       <c r="AV26" s="27">
-        <v>791.16</v>
+        <v>697.45</v>
       </c>
       <c r="AW26" s="28">
         <f>AX26-AV26</f>
-        <v>22.99</v>
+        <v>1.69999999999993</v>
       </c>
       <c r="AX26" s="28">
-        <v>814.15</v>
+        <v>699.15</v>
       </c>
       <c r="AY26" s="28">
         <f>AZ26-AX26</f>
-        <v>7.02999999999997</v>
+        <v>1.69000000000005</v>
       </c>
       <c r="AZ26" s="28">
-        <v>821.18</v>
+        <v>700.84</v>
       </c>
       <c r="BA26" s="28">
         <f>BB26-AZ26</f>
-        <v>10.8000000000001</v>
+        <v>8.5</v>
       </c>
       <c r="BB26" s="28">
-        <v>831.98</v>
+        <v>709.34</v>
       </c>
       <c r="BC26" s="28">
         <f>BD26-BB26</f>
-        <v>9.29999999999995</v>
+        <v>2.5</v>
       </c>
       <c r="BD26" s="28">
-        <v>841.28</v>
+        <v>711.84</v>
       </c>
       <c r="BE26" s="27">
         <f>BF26-BD26</f>
-        <v>10.27</v>
+        <v>0</v>
       </c>
       <c r="BF26" s="28">
-        <v>851.55</v>
+        <v>711.84</v>
       </c>
       <c r="BG26" s="28">
         <f>BH26-BF26</f>
-        <v>5.25</v>
+        <v>5.63999999999999</v>
       </c>
       <c r="BH26" s="28">
-        <v>856.8</v>
+        <v>717.48</v>
       </c>
       <c r="BI26" s="28">
         <f>BJ26-BH26</f>
-        <v>38.2900000000001</v>
+        <v>3.46000000000004</v>
       </c>
       <c r="BJ26" s="28">
-        <v>895.09</v>
+        <v>720.94</v>
       </c>
       <c r="BK26" s="28">
         <f>BL26-BJ26</f>
-        <v>5.57999999999993</v>
+        <v>0.75</v>
       </c>
       <c r="BL26" s="28">
-        <v>900.67</v>
+        <v>721.69</v>
       </c>
       <c r="BM26" s="28">
         <f>BN26-BL26</f>
-        <v>8.44000000000005</v>
+        <v>4.17999999999995</v>
       </c>
       <c r="BN26" s="28">
-        <v>909.11</v>
+        <v>725.87</v>
       </c>
       <c r="BO26" s="28">
         <f>BP26-BN26</f>
-        <v>15.85</v>
+        <v>1.95000000000005</v>
       </c>
       <c r="BP26" s="28">
-        <v>924.96</v>
+        <v>727.82</v>
       </c>
       <c r="BQ26" s="28">
         <f>BR26-BP26</f>
-        <v>18.7199999999999</v>
+        <v>7.20999999999992</v>
       </c>
       <c r="BR26" s="28">
-        <v>943.68</v>
+        <v>735.03</v>
       </c>
       <c r="BS26" s="28">
         <f>BT26-BR26</f>
-        <v>7.2600000000001</v>
+        <v>0</v>
       </c>
       <c r="BT26" s="28">
-        <v>950.94</v>
+        <v>735.03</v>
       </c>
       <c r="BU26" s="28">
         <f>BV26-BT26</f>
-        <v>12.5599999999999</v>
+        <v>1.37</v>
       </c>
       <c r="BV26" s="28">
-        <v>963.5</v>
+        <v>736.4</v>
       </c>
       <c r="BW26" s="28">
         <f>BX26-BV26</f>
-        <v>22.38</v>
+        <v>4.48000000000002</v>
       </c>
       <c r="BX26" s="28">
-        <v>985.88</v>
+        <v>740.88</v>
       </c>
       <c r="BY26" s="28">
         <f>BZ26-BX26</f>
-        <v>6.41999999999996</v>
+        <v>0</v>
       </c>
       <c r="BZ26" s="28">
-        <v>992.3</v>
+        <v>740.88</v>
       </c>
       <c r="CA26" s="28">
         <f>CB26-BZ26</f>
-        <v>17.48</v>
+        <v>0.259999999999991</v>
       </c>
       <c r="CB26" s="28">
-        <v>1009.78</v>
+        <v>741.14</v>
       </c>
       <c r="CC26" s="28">
         <f>CD26-CB26</f>
-        <v>12.87</v>
+        <v>0.610000000000014</v>
       </c>
       <c r="CD26" s="28">
-        <v>1022.65</v>
+        <v>741.75</v>
       </c>
       <c r="CE26" s="28">
         <f>CF26-CD26</f>
-        <v>15.34</v>
+        <v>4.10000000000002</v>
       </c>
       <c r="CF26" s="28">
-        <v>1037.99</v>
+        <v>745.85</v>
       </c>
       <c r="CG26" s="28">
         <f>CH26-CF26</f>
-        <v>11.4200000000001</v>
+        <v>13.17</v>
       </c>
       <c r="CH26" s="28">
-        <v>1049.41</v>
+        <v>759.02</v>
       </c>
       <c r="CI26" s="28">
         <f>CJ26-CH26</f>
-        <v>17.9299999999998</v>
+        <v>1.38999999999999</v>
       </c>
       <c r="CJ26" s="28">
-        <v>1067.34</v>
+        <v>760.41</v>
       </c>
       <c r="CK26" s="28">
         <f>CL26-CJ26</f>
-        <v>16.5</v>
+        <v>5.99000000000001</v>
       </c>
       <c r="CL26" s="28">
-        <v>1083.84</v>
+        <v>766.4</v>
       </c>
       <c r="CM26" s="28">
         <f>CN26-CL26</f>
-        <v>12.4100000000001</v>
+        <v>1.76999999999998</v>
       </c>
       <c r="CN26" s="28">
-        <v>1096.25</v>
+        <v>768.17</v>
       </c>
       <c r="CO26" s="28">
         <f>CP26-CN26</f>
-        <v>12.45</v>
+        <v>0.129999999999995</v>
       </c>
       <c r="CP26" s="28">
-        <v>1108.7</v>
+        <v>768.3</v>
       </c>
       <c r="CQ26" s="28">
         <f>CR26-CP26</f>
-        <v>6.53999999999996</v>
+        <v>0.0900000000000318</v>
       </c>
       <c r="CR26" s="28">
-        <v>1115.24</v>
+        <v>768.39</v>
       </c>
       <c r="CS26" s="28">
         <f>CT26-CR26</f>
-        <v>19.04</v>
+        <v>5.5</v>
       </c>
       <c r="CT26" s="28">
-        <v>1134.28</v>
+        <v>773.89</v>
       </c>
       <c r="CU26" s="28">
         <f>CV26-CT26</f>
-        <v>12.6100000000001</v>
+        <v>16.8100000000001</v>
       </c>
       <c r="CV26" s="28">
-        <v>1146.89</v>
+        <v>790.7</v>
       </c>
       <c r="CW26" s="27">
         <f>CX26-CV26</f>
-        <v>3.52999999999997</v>
+        <v>1.14999999999998</v>
       </c>
       <c r="CX26" s="28">
-        <v>1150.42</v>
+        <v>791.85</v>
       </c>
       <c r="CY26" s="28">
         <f>CZ26-CX26</f>
-        <v>44.3299999999999</v>
+        <v>14.1999999999999</v>
       </c>
       <c r="CZ26" s="28">
-        <v>1194.75</v>
+        <v>806.05</v>
       </c>
       <c r="DA26" s="28">
         <f>DB26-CZ26</f>
-        <v>3.44000000000005</v>
+        <v>8.29000000000008</v>
       </c>
       <c r="DB26" s="28">
-        <v>1198.19</v>
+        <v>814.34</v>
       </c>
       <c r="DC26" s="28">
         <f>DD26-DB26</f>
-        <v>11.3199999999999</v>
+        <v>9.43999999999994</v>
       </c>
       <c r="DD26" s="28">
-        <v>1209.51</v>
+        <v>823.78</v>
       </c>
       <c r="DE26" s="28">
         <f>DF26-DD26</f>
-        <v>6.08999999999992</v>
+        <v>3.77999999999997</v>
       </c>
       <c r="DF26" s="28">
-        <v>1215.6</v>
+        <v>827.56</v>
       </c>
       <c r="DG26" s="28">
         <f>DH26-DF26</f>
-        <v>2.80000000000018</v>
+        <v>12.59</v>
       </c>
       <c r="DH26" s="28">
-        <v>1218.4</v>
+        <v>840.15</v>
       </c>
       <c r="DI26" s="28">
         <f>DJ26-DH26</f>
-        <v>11.3899999999999</v>
+        <v>12.65</v>
       </c>
       <c r="DJ26" s="28">
-        <v>1229.79</v>
+        <v>852.8</v>
       </c>
       <c r="DK26" s="28">
         <f>DL26-DJ26</f>
-        <v>14.1500000000001</v>
+        <v>9.09000000000003</v>
       </c>
       <c r="DL26" s="28">
-        <v>1243.94</v>
+        <v>861.89</v>
       </c>
       <c r="DM26" s="28">
         <f>DN26-DL26</f>
-        <v>12.46</v>
+        <v>6.33000000000004</v>
       </c>
       <c r="DN26" s="28">
-        <v>1256.4</v>
+        <v>868.22</v>
       </c>
       <c r="DO26" s="27">
         <f>DP26-DN26</f>
-        <v>6.90999999999985</v>
+        <v>9.32999999999993</v>
       </c>
       <c r="DP26" s="28">
-        <v>1263.31</v>
+        <v>877.55</v>
       </c>
       <c r="DQ26" s="28">
         <f>DR26-DP26</f>
-        <v>9.53999999999996</v>
+        <v>13.6900000000001</v>
       </c>
       <c r="DR26" s="28">
-        <v>1272.85</v>
+        <v>891.24</v>
       </c>
       <c r="DS26" s="28">
         <f>DT26-DR26</f>
-        <v>9.12000000000012</v>
+        <v>5.73000000000002</v>
       </c>
       <c r="DT26" s="28">
-        <v>1281.97</v>
+        <v>896.97</v>
       </c>
       <c r="DU26" s="28">
         <f>DV26-DT26</f>
-        <v>17.4300000000001</v>
+        <v>5</v>
       </c>
       <c r="DV26" s="28">
-        <v>1299.4</v>
+        <v>901.97</v>
       </c>
       <c r="DW26" s="28">
         <f>DX26-DV26</f>
-        <v>10.1099999999999</v>
+        <v>4.62</v>
       </c>
       <c r="DX26" s="28">
-        <v>1309.51</v>
+        <v>906.59</v>
       </c>
       <c r="DY26" s="28">
         <f>DZ26-DX26</f>
-        <v>6.31999999999994</v>
+        <v>24.29</v>
       </c>
       <c r="DZ26" s="28">
-        <v>1315.83</v>
+        <v>930.88</v>
       </c>
       <c r="EA26" s="28">
         <f>EB26-DZ26</f>
-        <v>15.03</v>
+        <v>7.73000000000002</v>
       </c>
       <c r="EB26" s="28">
-        <v>1330.86</v>
+        <v>938.61</v>
       </c>
       <c r="EC26" s="28">
         <f>ED26-EB26</f>
-        <v>34.6300000000001</v>
+        <v>8.51999999999998</v>
       </c>
       <c r="ED26" s="28">
-        <v>1365.49</v>
+        <v>947.13</v>
       </c>
       <c r="EE26" s="28">
         <f>EF26-ED26</f>
-        <v>-2.88000000000011</v>
+        <v>5.41999999999996</v>
       </c>
       <c r="EF26" s="28">
-        <v>1362.61</v>
+        <v>952.55</v>
       </c>
       <c r="EG26" s="28">
         <f>EH26-EF26</f>
-        <v>24.0300000000002</v>
+        <v>4.41000000000008</v>
       </c>
       <c r="EH26" s="28">
-        <v>1386.64</v>
+        <v>956.96</v>
       </c>
       <c r="EI26" s="28">
         <f>EJ26-EH26</f>
-        <v>2.06999999999994</v>
+        <v>3.56999999999994</v>
       </c>
       <c r="EJ26" s="28">
-        <v>1388.71</v>
+        <v>960.53</v>
       </c>
       <c r="EK26" s="28">
         <f>EL26-EJ26</f>
-        <v>6.64999999999986</v>
+        <v>11.35</v>
       </c>
       <c r="EL26" s="28">
-        <v>1395.36</v>
+        <v>971.88</v>
       </c>
       <c r="EM26" s="28">
         <f>EN26-EL26</f>
-        <v>8.23000000000002</v>
+        <v>1.25999999999999</v>
       </c>
       <c r="EN26" s="28">
-        <v>1403.59</v>
+        <v>973.14</v>
       </c>
       <c r="EO26" s="28">
         <f>EP26-EN26</f>
-        <v>19.0700000000002</v>
+        <v>7.15999999999997</v>
       </c>
       <c r="EP26" s="28">
-        <v>1422.66</v>
+        <v>980.3</v>
       </c>
       <c r="EQ26" s="28">
         <f>ER26-EP26</f>
-        <v>1.39999999999986</v>
+        <v>1.87</v>
       </c>
       <c r="ER26" s="28">
-        <v>1424.06</v>
+        <v>982.17</v>
       </c>
       <c r="ES26" s="28">
         <f>ET26-ER26</f>
-        <v>4.52999999999997</v>
+        <v>2.03000000000009</v>
       </c>
       <c r="ET26" s="28">
-        <v>1428.59</v>
+        <v>984.2</v>
       </c>
       <c r="EU26" s="28">
         <f>EV26-ET26</f>
+        <v>9.88999999999999</v>
+      </c>
+      <c r="EV26" s="28">
+        <v>994.09</v>
+      </c>
+      <c r="EW26" s="28">
+        <f>EX26-EV26</f>
+        <v>0.659999999999968</v>
+      </c>
+      <c r="EX26" s="28">
+        <v>994.75</v>
+      </c>
+      <c r="EY26" s="27" t="s">
+        <v>123</v>
+      </c>
+      <c r="EZ26" s="26">
+        <v>298.94</v>
+      </c>
+      <c r="FA26" s="26" t="s">
+        <v>142</v>
+      </c>
+      <c r="FB26" s="26">
+        <v>171.75</v>
+      </c>
+      <c r="FC26" s="3">
         <v>0</v>
       </c>
-      <c r="EV26" s="28">
-        <v>1428.59</v>
-      </c>
-      <c r="EW26" s="27" t="s">
-        <v>105</v>
-      </c>
-      <c r="EX26" s="26">
-        <v>674.85</v>
-      </c>
-      <c r="EY26" s="22" t="s">
-        <v>149</v>
-      </c>
-      <c r="EZ26" s="22">
-        <v>293.75</v>
-      </c>
-      <c r="FA26" s="8">
-        <v>30</v>
-      </c>
-      <c r="FB26" s="8">
-        <v>2.4</v>
-      </c>
-      <c r="FC26" s="8">
-        <v>43895</v>
-      </c>
-      <c r="FD26" s="9">
-        <f>2.79/(EV26/EX26)</f>
-        <v>1.31796491645609</v>
-      </c>
-      <c r="FE26" s="9">
+      <c r="FD26" s="3">
+        <v>0.5</v>
+      </c>
+      <c r="FE26" s="3">
+        <v>49654</v>
+      </c>
+      <c r="FF26" s="9">
+        <f>2.43/(EX26/EZ26)</f>
+        <v>0.730258054787635</v>
+      </c>
+      <c r="FG26" s="9">
         <f>BP26-D26</f>
-        <v>517.61</v>
+        <v>175.03</v>
+      </c>
+      <c r="FH26" s="9">
+        <f>EX26-ER26</f>
+        <v>12.58</v>
       </c>
     </row>
-    <row r="27" spans="1:161">
-      <c r="A27" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="B27" s="3" t="s">
-        <v>150</v>
-      </c>
-      <c r="C27" s="3" t="s">
-        <v>141</v>
-      </c>
-      <c r="D27" s="3">
-        <v>552.79</v>
-      </c>
-      <c r="E27" s="3">
-        <f>F27-D27</f>
-        <v>15.9400000000001</v>
-      </c>
-      <c r="F27" s="3">
-        <v>568.73</v>
-      </c>
-      <c r="G27" s="3">
-        <f>H27-F27</f>
-        <v>1.61000000000001</v>
-      </c>
-      <c r="H27" s="3">
-        <v>570.34</v>
-      </c>
-      <c r="I27" s="3">
-        <f>J27-H27</f>
-        <v>7.13999999999999</v>
-      </c>
-      <c r="J27" s="3">
-        <v>577.48</v>
-      </c>
-      <c r="K27" s="3">
-        <f>L27-J27</f>
-        <v>2.88999999999999</v>
-      </c>
-      <c r="L27" s="3">
-        <v>580.37</v>
-      </c>
-      <c r="M27" s="3">
-        <f>N27-L27</f>
-        <v>2.55999999999995</v>
-      </c>
-      <c r="N27" s="3">
-        <v>582.93</v>
-      </c>
-      <c r="O27" s="3">
-        <f>P27-N27</f>
-        <v>24.99</v>
-      </c>
-      <c r="P27" s="3">
-        <v>607.92</v>
-      </c>
-      <c r="Q27" s="3">
-        <f>R27-P27</f>
-        <v>0.330000000000041</v>
-      </c>
-      <c r="R27" s="3">
-        <v>608.25</v>
-      </c>
-      <c r="S27" s="3">
-        <f>T27-R27</f>
-        <v>1.80999999999995</v>
-      </c>
-      <c r="T27" s="3">
-        <v>610.06</v>
-      </c>
-      <c r="U27" s="3">
-        <f>V27-T27</f>
-        <v>0.560000000000059</v>
-      </c>
-      <c r="V27" s="25">
-        <v>610.62</v>
-      </c>
-      <c r="W27" s="3">
-        <f>X27-V27</f>
-        <v>3.83000000000004</v>
-      </c>
-      <c r="X27" s="25">
-        <v>614.45</v>
-      </c>
-      <c r="Y27" s="3">
-        <f>Z27-X27</f>
-        <v>0.189999999999941</v>
-      </c>
-      <c r="Z27" s="3">
-        <v>614.64</v>
-      </c>
-      <c r="AA27" s="3">
-        <f>AB27-Z27</f>
-        <v>0.690000000000055</v>
-      </c>
-      <c r="AB27" s="3">
-        <v>615.33</v>
-      </c>
-      <c r="AC27" s="3">
-        <f>AD27-AB27</f>
-        <v>6.64999999999998</v>
-      </c>
-      <c r="AD27" s="3">
-        <v>621.98</v>
-      </c>
-      <c r="AE27" s="26">
-        <f>AF27-AD27</f>
-        <v>0</v>
-      </c>
-      <c r="AF27" s="26">
-        <v>621.98</v>
-      </c>
-      <c r="AG27" s="26">
-        <f>AH27-AF27</f>
-        <v>13.62</v>
-      </c>
-      <c r="AH27" s="26">
-        <v>635.6</v>
-      </c>
-      <c r="AI27" s="26">
-        <f>AJ27-AH27</f>
-        <v>16.48</v>
-      </c>
-      <c r="AJ27" s="26">
-        <v>652.08</v>
-      </c>
-      <c r="AK27" s="26">
-        <f>AL27-AJ27</f>
-        <v>5.84999999999991</v>
-      </c>
-      <c r="AL27" s="26">
-        <v>657.93</v>
-      </c>
-      <c r="AM27" s="26">
-        <f>AN27-AL27</f>
-        <v>5.80000000000007</v>
-      </c>
-      <c r="AN27" s="26">
-        <v>663.73</v>
-      </c>
-      <c r="AO27" s="26">
-        <f>AP27-AN27</f>
-        <v>13.75</v>
-      </c>
-      <c r="AP27" s="26">
-        <v>677.48</v>
-      </c>
-      <c r="AQ27" s="26">
-        <f>AR27-AP27</f>
-        <v>3.60000000000002</v>
-      </c>
-      <c r="AR27" s="26">
-        <v>681.08</v>
-      </c>
-      <c r="AS27" s="26">
-        <f>AT27-AR27</f>
-        <v>12.0799999999999</v>
-      </c>
-      <c r="AT27" s="26">
-        <v>693.16</v>
-      </c>
-      <c r="AU27" s="27">
-        <f>AV27-AT27</f>
-        <v>4.29000000000008</v>
-      </c>
-      <c r="AV27" s="27">
-        <v>697.45</v>
-      </c>
-      <c r="AW27" s="28">
-        <f>AX27-AV27</f>
-        <v>1.69999999999993</v>
-      </c>
-      <c r="AX27" s="28">
-        <v>699.15</v>
-      </c>
-      <c r="AY27" s="28">
-        <f>AZ27-AX27</f>
-        <v>1.69000000000005</v>
-      </c>
-      <c r="AZ27" s="28">
-        <v>700.84</v>
-      </c>
-      <c r="BA27" s="28">
-        <f>BB27-AZ27</f>
-        <v>8.5</v>
-      </c>
-      <c r="BB27" s="28">
-        <v>709.34</v>
-      </c>
-      <c r="BC27" s="28">
-        <f>BD27-BB27</f>
-        <v>2.5</v>
-      </c>
-      <c r="BD27" s="28">
-        <v>711.84</v>
-      </c>
-      <c r="BE27" s="27">
-        <f>BF27-BD27</f>
-        <v>0</v>
-      </c>
-      <c r="BF27" s="28">
-        <v>711.84</v>
-      </c>
-      <c r="BG27" s="28">
-        <f>BH27-BF27</f>
-        <v>5.63999999999999</v>
-      </c>
-      <c r="BH27" s="28">
-        <v>717.48</v>
-      </c>
-      <c r="BI27" s="28">
-        <f>BJ27-BH27</f>
-        <v>3.46000000000004</v>
-      </c>
-      <c r="BJ27" s="28">
-        <v>720.94</v>
-      </c>
-      <c r="BK27" s="28">
-        <f>BL27-BJ27</f>
-        <v>0.75</v>
-      </c>
-      <c r="BL27" s="28">
-        <v>721.69</v>
-      </c>
-      <c r="BM27" s="28">
-        <f>BN27-BL27</f>
-        <v>4.17999999999995</v>
-      </c>
-      <c r="BN27" s="28">
-        <v>725.87</v>
-      </c>
-      <c r="BO27" s="28">
-        <f>BP27-BN27</f>
-        <v>1.95000000000005</v>
-      </c>
-      <c r="BP27" s="28">
-        <v>727.82</v>
-      </c>
-      <c r="BQ27" s="28">
-        <f>BR27-BP27</f>
-        <v>7.20999999999992</v>
-      </c>
-      <c r="BR27" s="28">
-        <v>735.03</v>
-      </c>
-      <c r="BS27" s="28">
-        <f>BT27-BR27</f>
-        <v>0</v>
-      </c>
-      <c r="BT27" s="28">
-        <v>735.03</v>
-      </c>
-      <c r="BU27" s="28">
-        <f>BV27-BT27</f>
-        <v>1.37</v>
-      </c>
-      <c r="BV27" s="28">
-        <v>736.4</v>
-      </c>
-      <c r="BW27" s="28">
-        <f>BX27-BV27</f>
-        <v>4.48000000000002</v>
-      </c>
-      <c r="BX27" s="28">
-        <v>740.88</v>
-      </c>
-      <c r="BY27" s="28">
-        <f>BZ27-BX27</f>
-        <v>0</v>
-      </c>
-      <c r="BZ27" s="28">
-        <v>740.88</v>
-      </c>
-      <c r="CA27" s="28">
-        <f>CB27-BZ27</f>
-        <v>0.259999999999991</v>
-      </c>
-      <c r="CB27" s="28">
-        <v>741.14</v>
-      </c>
-      <c r="CC27" s="28">
-        <f>CD27-CB27</f>
-        <v>0.610000000000014</v>
-      </c>
-      <c r="CD27" s="28">
-        <v>741.75</v>
-      </c>
-      <c r="CE27" s="28">
-        <f>CF27-CD27</f>
-        <v>4.10000000000002</v>
-      </c>
-      <c r="CF27" s="28">
-        <v>745.85</v>
-      </c>
-      <c r="CG27" s="28">
-        <f>CH27-CF27</f>
-        <v>13.17</v>
-      </c>
-      <c r="CH27" s="28">
-        <v>759.02</v>
-      </c>
-      <c r="CI27" s="28">
-        <f>CJ27-CH27</f>
-        <v>1.38999999999999</v>
-      </c>
-      <c r="CJ27" s="28">
-        <v>760.41</v>
-      </c>
-      <c r="CK27" s="28">
-        <f>CL27-CJ27</f>
-        <v>5.99000000000001</v>
-      </c>
-      <c r="CL27" s="28">
-        <v>766.4</v>
-      </c>
-      <c r="CM27" s="28">
-        <f>CN27-CL27</f>
-        <v>1.76999999999998</v>
-      </c>
-      <c r="CN27" s="28">
-        <v>768.17</v>
-      </c>
-      <c r="CO27" s="28">
-        <f>CP27-CN27</f>
-        <v>0.129999999999995</v>
-      </c>
-      <c r="CP27" s="28">
-        <v>768.3</v>
-      </c>
-      <c r="CQ27" s="28">
-        <f>CR27-CP27</f>
-        <v>0.0900000000000318</v>
-      </c>
-      <c r="CR27" s="28">
-        <v>768.39</v>
-      </c>
-      <c r="CS27" s="28">
-        <f>CT27-CR27</f>
-        <v>5.5</v>
-      </c>
-      <c r="CT27" s="28">
-        <v>773.89</v>
-      </c>
-      <c r="CU27" s="28">
-        <f>CV27-CT27</f>
-        <v>16.8100000000001</v>
-      </c>
-      <c r="CV27" s="28">
-        <v>790.7</v>
-      </c>
-      <c r="CW27" s="27">
-        <f>CX27-CV27</f>
-        <v>1.14999999999998</v>
-      </c>
-      <c r="CX27" s="28">
-        <v>791.85</v>
-      </c>
-      <c r="CY27" s="28">
-        <f>CZ27-CX27</f>
-        <v>14.1999999999999</v>
-      </c>
-      <c r="CZ27" s="28">
-        <v>806.05</v>
-      </c>
-      <c r="DA27" s="28">
-        <f>DB27-CZ27</f>
-        <v>8.29000000000008</v>
-      </c>
-      <c r="DB27" s="28">
-        <v>814.34</v>
-      </c>
-      <c r="DC27" s="28">
-        <f>DD27-DB27</f>
-        <v>9.43999999999994</v>
-      </c>
-      <c r="DD27" s="28">
-        <v>823.78</v>
-      </c>
-      <c r="DE27" s="28">
-        <f>DF27-DD27</f>
-        <v>3.77999999999997</v>
-      </c>
-      <c r="DF27" s="28">
-        <v>827.56</v>
-      </c>
-      <c r="DG27" s="28">
-        <f>DH27-DF27</f>
-        <v>12.59</v>
-      </c>
-      <c r="DH27" s="28">
-        <v>840.15</v>
-      </c>
-      <c r="DI27" s="28">
-        <f>DJ27-DH27</f>
-        <v>12.65</v>
-      </c>
-      <c r="DJ27" s="28">
-        <v>852.8</v>
-      </c>
-      <c r="DK27" s="28">
-        <f>DL27-DJ27</f>
-        <v>9.09000000000003</v>
-      </c>
-      <c r="DL27" s="28">
-        <v>861.89</v>
-      </c>
-      <c r="DM27" s="28">
-        <f>DN27-DL27</f>
-        <v>6.33000000000004</v>
-      </c>
-      <c r="DN27" s="28">
-        <v>868.22</v>
-      </c>
-      <c r="DO27" s="27">
-        <f>DP27-DN27</f>
-        <v>9.32999999999993</v>
-      </c>
-      <c r="DP27" s="28">
-        <v>877.55</v>
-      </c>
-      <c r="DQ27" s="28">
-        <f>DR27-DP27</f>
-        <v>13.6900000000001</v>
-      </c>
-      <c r="DR27" s="28">
-        <v>891.24</v>
-      </c>
-      <c r="DS27" s="28">
-        <f>DT27-DR27</f>
-        <v>5.73000000000002</v>
-      </c>
-      <c r="DT27" s="28">
-        <v>896.97</v>
-      </c>
-      <c r="DU27" s="28">
-        <f>DV27-DT27</f>
-        <v>5</v>
-      </c>
-      <c r="DV27" s="28">
-        <v>901.97</v>
-      </c>
-      <c r="DW27" s="28">
-        <f>DX27-DV27</f>
-        <v>4.62</v>
-      </c>
-      <c r="DX27" s="28">
-        <v>906.59</v>
-      </c>
-      <c r="DY27" s="28">
-        <f>DZ27-DX27</f>
-        <v>24.29</v>
-      </c>
-      <c r="DZ27" s="28">
-        <v>930.88</v>
-      </c>
-      <c r="EA27" s="28">
-        <f>EB27-DZ27</f>
-        <v>7.73000000000002</v>
-      </c>
-      <c r="EB27" s="28">
-        <v>938.61</v>
-      </c>
-      <c r="EC27" s="28">
-        <f>ED27-EB27</f>
-        <v>8.51999999999998</v>
-      </c>
-      <c r="ED27" s="28">
-        <v>947.13</v>
-      </c>
-      <c r="EE27" s="28">
-        <f>EF27-ED27</f>
-        <v>5.41999999999996</v>
-      </c>
-      <c r="EF27" s="28">
-        <v>952.55</v>
-      </c>
-      <c r="EG27" s="28">
-        <f>EH27-EF27</f>
-        <v>4.41000000000008</v>
-      </c>
-      <c r="EH27" s="28">
-        <v>956.96</v>
-      </c>
-      <c r="EI27" s="28">
-        <f>EJ27-EH27</f>
-        <v>3.56999999999994</v>
-      </c>
-      <c r="EJ27" s="28">
-        <v>960.53</v>
-      </c>
-      <c r="EK27" s="28">
-        <f>EL27-EJ27</f>
-        <v>11.35</v>
-      </c>
-      <c r="EL27" s="28">
-        <v>971.88</v>
-      </c>
-      <c r="EM27" s="28">
-        <f>EN27-EL27</f>
-        <v>1.25999999999999</v>
-      </c>
-      <c r="EN27" s="28">
-        <v>973.14</v>
-      </c>
-      <c r="EO27" s="28">
-        <f>EP27-EN27</f>
-        <v>7.15999999999997</v>
-      </c>
-      <c r="EP27" s="28">
-        <v>980.3</v>
-      </c>
-      <c r="EQ27" s="28">
-        <f>ER27-EP27</f>
-        <v>1.87</v>
-      </c>
-      <c r="ER27" s="28">
-        <v>982.17</v>
-      </c>
-      <c r="ES27" s="28">
-        <f>ET27-ER27</f>
-        <v>2.03000000000009</v>
-      </c>
-      <c r="ET27" s="28">
-        <v>984.2</v>
-      </c>
-      <c r="EU27" s="28">
-        <f>EV27-ET27</f>
-        <v>9.88999999999999</v>
-      </c>
-      <c r="EV27" s="28">
-        <v>994.09</v>
-      </c>
-      <c r="EW27" s="27" t="s">
-        <v>120</v>
-      </c>
-      <c r="EX27" s="26">
-        <v>298.94</v>
-      </c>
-      <c r="EY27" s="26" t="s">
-        <v>139</v>
-      </c>
-      <c r="EZ27" s="26">
-        <v>171.75</v>
-      </c>
-      <c r="FA27" s="3">
-        <v>0</v>
-      </c>
-      <c r="FB27" s="3">
-        <v>0.5</v>
-      </c>
-      <c r="FC27" s="3">
-        <v>49654</v>
-      </c>
-      <c r="FD27" s="9">
-        <f>2.79/(EV27/EX27)</f>
-        <v>0.839001096480198</v>
-      </c>
-      <c r="FE27" s="9">
-        <f>BP27-D27</f>
-        <v>175.03</v>
-      </c>
+    <row r="29" spans="1:164">
+      <c r="A29" t="s">
+        <v>153</v>
+      </c>
+      <c r="B29" t="s">
+        <v>154</v>
+      </c>
+      <c r="C29" s="29"/>
+      <c r="D29" s="29"/>
+      <c r="E29" s="29"/>
+      <c r="F29" s="29"/>
+      <c r="G29" s="29"/>
+      <c r="H29" s="29"/>
+      <c r="I29" s="29"/>
+      <c r="J29" s="29"/>
+      <c r="K29" s="29"/>
+      <c r="L29" s="29"/>
+      <c r="M29" s="29"/>
+      <c r="N29" s="29"/>
+      <c r="O29" s="29"/>
+      <c r="P29" s="29"/>
+      <c r="Q29" s="29"/>
+      <c r="R29" s="29"/>
+      <c r="S29" s="29"/>
+      <c r="T29" s="29"/>
+      <c r="U29" s="29"/>
+      <c r="V29" s="29"/>
+      <c r="W29" s="29"/>
+      <c r="X29" s="29"/>
+      <c r="Y29" s="29"/>
+      <c r="Z29" s="29"/>
+      <c r="AA29" s="29"/>
+      <c r="AB29" s="29"/>
+      <c r="AC29" s="29"/>
+      <c r="AD29" s="29"/>
+      <c r="AE29" s="29"/>
+      <c r="AF29" s="29"/>
+      <c r="AG29" s="29"/>
+      <c r="AH29" s="29"/>
+      <c r="AI29" s="29"/>
+      <c r="AJ29" s="29"/>
+      <c r="AK29" s="29"/>
+      <c r="AL29" s="29"/>
+      <c r="AM29" s="29"/>
+      <c r="AN29" s="29"/>
+      <c r="AO29" s="29"/>
+      <c r="AP29" s="29"/>
+      <c r="AQ29" s="29"/>
+      <c r="AR29" s="29"/>
+      <c r="AS29" s="29"/>
+      <c r="AT29" s="29"/>
+      <c r="AU29" s="29"/>
+      <c r="AV29" s="29"/>
+      <c r="AW29" s="29"/>
+      <c r="AX29" s="29"/>
+      <c r="AY29" s="29"/>
+      <c r="AZ29" s="29"/>
+      <c r="BA29" s="29"/>
+      <c r="BB29" s="29"/>
+      <c r="BC29" s="30"/>
+      <c r="BD29" s="29"/>
+      <c r="BE29" s="29"/>
+      <c r="BF29" s="29"/>
+      <c r="BG29" s="29"/>
+      <c r="BH29" s="29"/>
+      <c r="BI29" s="29"/>
+      <c r="BJ29" s="29"/>
+      <c r="BK29" s="29"/>
+      <c r="BL29" s="29"/>
+      <c r="BM29" s="29"/>
+      <c r="BN29" s="29"/>
+      <c r="BO29" s="29"/>
+      <c r="BP29" s="29"/>
+      <c r="BQ29" s="29"/>
+      <c r="BR29" s="29"/>
+      <c r="BS29" s="29"/>
+      <c r="BT29" s="29"/>
+      <c r="BU29" s="29"/>
+      <c r="BV29" s="29"/>
+      <c r="BW29" s="29"/>
+      <c r="BX29" s="29"/>
+      <c r="BY29" s="29"/>
+      <c r="BZ29" s="29"/>
+      <c r="CA29" s="29"/>
+      <c r="CB29" s="29"/>
+      <c r="CC29" s="29"/>
+      <c r="CD29" s="29"/>
+      <c r="CE29" s="29"/>
+      <c r="CF29" s="29"/>
+      <c r="CG29" s="29"/>
+      <c r="CH29" s="29"/>
+      <c r="CI29" s="29"/>
+      <c r="CJ29" s="29"/>
+      <c r="CK29" s="29"/>
+      <c r="CL29" s="29"/>
+      <c r="CM29" s="29"/>
+      <c r="CN29" s="29"/>
+      <c r="CO29" s="29"/>
+      <c r="CP29" s="29"/>
+      <c r="CQ29" s="29"/>
+      <c r="CR29" s="29"/>
+      <c r="CS29" s="29"/>
+      <c r="CT29" s="29"/>
+      <c r="CU29" s="29"/>
+      <c r="CV29" s="29"/>
+      <c r="CW29" s="29"/>
+      <c r="CX29" s="29"/>
+      <c r="CY29" s="29"/>
+      <c r="CZ29" s="29"/>
+      <c r="DA29" s="29"/>
+      <c r="DB29" s="29"/>
+      <c r="DC29" s="29"/>
+      <c r="DD29" s="29"/>
+      <c r="DE29" s="29"/>
+      <c r="DF29" s="29"/>
+      <c r="DG29" s="29"/>
+      <c r="DH29" s="29"/>
+      <c r="DI29" s="29"/>
+      <c r="DJ29" s="29"/>
+      <c r="DK29" s="29"/>
+      <c r="DL29" s="29"/>
+      <c r="DM29" s="29"/>
+      <c r="DN29" s="29"/>
+      <c r="DO29" s="29"/>
+      <c r="DP29" s="29"/>
+      <c r="DQ29" s="29"/>
+      <c r="DR29" s="29"/>
+      <c r="DS29" s="29"/>
+      <c r="DT29" s="29"/>
+      <c r="DU29" s="29"/>
+      <c r="DV29" s="29"/>
+      <c r="DW29" s="29"/>
+      <c r="DX29" s="29"/>
+      <c r="DY29" s="29"/>
+      <c r="DZ29" s="29"/>
+      <c r="EA29" s="29"/>
+      <c r="EB29" s="29"/>
+      <c r="EC29" s="29"/>
+      <c r="ED29" s="29"/>
+      <c r="EE29" s="29"/>
+      <c r="EF29" s="29"/>
+      <c r="EG29" s="29"/>
+      <c r="EH29" s="29"/>
+      <c r="EI29" s="29"/>
+      <c r="EJ29" s="29"/>
+      <c r="EK29" s="29"/>
+      <c r="EL29" s="29"/>
+      <c r="EM29" s="29"/>
+      <c r="EN29" s="29"/>
+      <c r="EO29" s="29"/>
+      <c r="EP29" s="29"/>
+      <c r="EQ29" s="29"/>
+      <c r="ER29" s="29"/>
+      <c r="ES29" s="29"/>
+      <c r="ET29" s="29"/>
+      <c r="EU29" s="29"/>
+      <c r="EV29" s="29"/>
+      <c r="EW29" s="29"/>
+      <c r="EX29" s="29"/>
+      <c r="EY29" s="29"/>
+      <c r="EZ29" s="29"/>
     </row>
-    <row r="30" spans="1:161">
+    <row r="30" spans="1:164">
       <c r="A30" t="s">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="B30" t="s">
-        <v>152</v>
-      </c>
-      <c r="C30" s="29"/>
-      <c r="D30" s="29"/>
-      <c r="E30" s="29"/>
-      <c r="F30" s="29"/>
-      <c r="G30" s="29"/>
-      <c r="H30" s="29"/>
-      <c r="I30" s="29"/>
-      <c r="J30" s="29"/>
-      <c r="K30" s="29"/>
-      <c r="L30" s="29"/>
-      <c r="M30" s="29"/>
-      <c r="N30" s="29"/>
-      <c r="O30" s="29"/>
+        <v>156</v>
+      </c>
       <c r="P30" s="29"/>
       <c r="Q30" s="29"/>
       <c r="R30" s="29"/>
@@ -16135,375 +16120,232 @@
       <c r="EV30" s="29"/>
       <c r="EW30" s="29"/>
       <c r="EX30" s="29"/>
+      <c r="EY30" s="29"/>
+      <c r="EZ30" s="29"/>
+      <c r="FA30" s="29"/>
+      <c r="FB30" s="29"/>
+      <c r="FC30" s="29"/>
     </row>
-    <row r="31" spans="1:161">
+    <row r="31" spans="1:164">
       <c r="A31" t="s">
-        <v>153</v>
+        <v>144</v>
       </c>
       <c r="B31" t="s">
-        <v>154</v>
-      </c>
-      <c r="P31" s="29"/>
-      <c r="Q31" s="29"/>
-      <c r="R31" s="29"/>
-      <c r="S31" s="29"/>
-      <c r="T31" s="29"/>
-      <c r="U31" s="29"/>
-      <c r="V31" s="29"/>
-      <c r="W31" s="29"/>
-      <c r="X31" s="29"/>
-      <c r="Y31" s="29"/>
-      <c r="Z31" s="29"/>
-      <c r="AA31" s="29"/>
-      <c r="AB31" s="29"/>
-      <c r="AC31" s="29"/>
-      <c r="AD31" s="29"/>
-      <c r="AE31" s="29"/>
-      <c r="AF31" s="29"/>
-      <c r="AG31" s="29"/>
-      <c r="AH31" s="29"/>
-      <c r="AI31" s="29"/>
-      <c r="AJ31" s="29"/>
-      <c r="AK31" s="29"/>
-      <c r="AL31" s="29"/>
-      <c r="AM31" s="29"/>
-      <c r="AN31" s="29"/>
-      <c r="AO31" s="29"/>
-      <c r="AP31" s="29"/>
-      <c r="AQ31" s="29"/>
-      <c r="AR31" s="29"/>
-      <c r="AS31" s="29"/>
-      <c r="AT31" s="29"/>
-      <c r="AU31" s="29"/>
-      <c r="AV31" s="29"/>
-      <c r="AW31" s="29"/>
-      <c r="AX31" s="29"/>
-      <c r="AY31" s="29"/>
-      <c r="AZ31" s="29"/>
-      <c r="BA31" s="29"/>
-      <c r="BB31" s="29"/>
-      <c r="BC31" s="30"/>
-      <c r="BD31" s="29"/>
-      <c r="BE31" s="29"/>
-      <c r="BF31" s="29"/>
-      <c r="BG31" s="29"/>
-      <c r="BH31" s="29"/>
-      <c r="BI31" s="29"/>
-      <c r="BJ31" s="29"/>
-      <c r="BK31" s="29"/>
-      <c r="BL31" s="29"/>
-      <c r="BM31" s="29"/>
-      <c r="BN31" s="29"/>
-      <c r="BO31" s="29"/>
-      <c r="BP31" s="29"/>
-      <c r="BQ31" s="29"/>
-      <c r="BR31" s="29"/>
-      <c r="BS31" s="29"/>
-      <c r="BT31" s="29"/>
-      <c r="BU31" s="29"/>
-      <c r="BV31" s="29"/>
-      <c r="BW31" s="29"/>
-      <c r="BX31" s="29"/>
-      <c r="BY31" s="29"/>
-      <c r="BZ31" s="29"/>
-      <c r="CA31" s="29"/>
-      <c r="CB31" s="29"/>
-      <c r="CC31" s="29"/>
-      <c r="CD31" s="29"/>
-      <c r="CE31" s="29"/>
-      <c r="CF31" s="29"/>
-      <c r="CG31" s="29"/>
-      <c r="CH31" s="29"/>
-      <c r="CI31" s="29"/>
-      <c r="CJ31" s="29"/>
-      <c r="CK31" s="29"/>
-      <c r="CL31" s="29"/>
-      <c r="CM31" s="29"/>
-      <c r="CN31" s="29"/>
-      <c r="CO31" s="29"/>
-      <c r="CP31" s="29"/>
-      <c r="CQ31" s="29"/>
-      <c r="CR31" s="29"/>
-      <c r="CS31" s="29"/>
-      <c r="CT31" s="29"/>
-      <c r="CU31" s="29"/>
-      <c r="CV31" s="29"/>
-      <c r="CW31" s="29"/>
-      <c r="CX31" s="29"/>
-      <c r="CY31" s="29"/>
-      <c r="CZ31" s="29"/>
-      <c r="DA31" s="29"/>
-      <c r="DB31" s="29"/>
-      <c r="DC31" s="29"/>
-      <c r="DD31" s="29"/>
-      <c r="DE31" s="29"/>
-      <c r="DF31" s="29"/>
-      <c r="DG31" s="29"/>
-      <c r="DH31" s="29"/>
-      <c r="DI31" s="29"/>
-      <c r="DJ31" s="29"/>
-      <c r="DK31" s="29"/>
-      <c r="DL31" s="29"/>
-      <c r="DM31" s="29"/>
-      <c r="DN31" s="29"/>
-      <c r="DO31" s="29"/>
-      <c r="DP31" s="29"/>
-      <c r="DQ31" s="29"/>
-      <c r="DR31" s="29"/>
-      <c r="DS31" s="29"/>
-      <c r="DT31" s="29"/>
-      <c r="DU31" s="29"/>
-      <c r="DV31" s="29"/>
-      <c r="DW31" s="29"/>
-      <c r="DX31" s="29"/>
-      <c r="DY31" s="29"/>
-      <c r="DZ31" s="29"/>
-      <c r="EA31" s="29"/>
-      <c r="EB31" s="29"/>
-      <c r="EC31" s="29"/>
-      <c r="ED31" s="29"/>
-      <c r="EE31" s="29"/>
-      <c r="EF31" s="29"/>
-      <c r="EG31" s="29"/>
-      <c r="EH31" s="29"/>
-      <c r="EI31" s="29"/>
-      <c r="EJ31" s="29"/>
-      <c r="EK31" s="29"/>
-      <c r="EL31" s="29"/>
-      <c r="EM31" s="29"/>
-      <c r="EN31" s="29"/>
-      <c r="EO31" s="29"/>
-      <c r="EP31" s="29"/>
-      <c r="EQ31" s="29"/>
-      <c r="ER31" s="29"/>
-      <c r="ES31" s="29"/>
-      <c r="ET31" s="29"/>
-      <c r="EU31" s="29"/>
-      <c r="EV31" s="29"/>
-      <c r="EW31" s="29"/>
-      <c r="EX31" s="29"/>
-      <c r="EY31" s="29"/>
-      <c r="EZ31" s="29"/>
-      <c r="FA31" s="29"/>
+        <v>157</v>
+      </c>
     </row>
-    <row r="32" spans="1:161">
+    <row r="32" spans="1:164">
       <c r="A32" t="s">
-        <v>141</v>
+        <v>135</v>
       </c>
       <c r="B32" t="s">
-        <v>155</v>
-      </c>
+        <v>158</v>
+      </c>
+      <c r="C32" s="29"/>
+      <c r="D32" s="29"/>
+      <c r="E32" s="29"/>
+      <c r="F32" s="29"/>
+      <c r="G32" s="29"/>
+      <c r="H32" s="29"/>
+      <c r="I32" s="29"/>
+      <c r="J32" s="29"/>
+      <c r="K32" s="29"/>
+      <c r="L32" s="29"/>
+      <c r="M32" s="29"/>
+      <c r="N32" s="29"/>
+      <c r="O32" s="29"/>
+      <c r="P32" s="29"/>
+      <c r="Q32" s="29"/>
+      <c r="R32" s="29"/>
+      <c r="S32" s="29"/>
+      <c r="T32" s="29"/>
+      <c r="U32" s="29"/>
+      <c r="V32" s="29"/>
+      <c r="W32" s="29"/>
+      <c r="X32" s="29"/>
+      <c r="Y32" s="29"/>
+      <c r="Z32" s="29"/>
+      <c r="AA32" s="29"/>
+      <c r="AB32" s="29"/>
+      <c r="AC32" s="29"/>
+      <c r="AD32" s="29"/>
+      <c r="AE32" s="29"/>
+      <c r="AF32" s="29"/>
+      <c r="AG32" s="29"/>
+      <c r="AH32" s="29"/>
+      <c r="AI32" s="29"/>
+      <c r="AJ32" s="29"/>
+      <c r="AK32" s="29"/>
+      <c r="AL32" s="29"/>
+      <c r="AM32" s="29"/>
+      <c r="AN32" s="29"/>
+      <c r="AO32" s="29"/>
+      <c r="AP32" s="29"/>
+      <c r="AQ32" s="29"/>
+      <c r="AR32" s="29"/>
+      <c r="AS32" s="29"/>
+      <c r="AT32" s="29"/>
+      <c r="AU32" s="29"/>
+      <c r="AV32" s="29"/>
+      <c r="AW32" s="29"/>
+      <c r="AX32" s="29"/>
+      <c r="AY32" s="29"/>
+      <c r="AZ32" s="29"/>
+      <c r="BA32" s="29"/>
+      <c r="BB32" s="29"/>
+      <c r="BC32" s="30"/>
+      <c r="BD32" s="29"/>
+      <c r="BE32" s="29"/>
+      <c r="BF32" s="29"/>
+      <c r="BG32" s="29"/>
+      <c r="BH32" s="29"/>
+      <c r="BI32" s="29"/>
+      <c r="BJ32" s="29"/>
+      <c r="BK32" s="29"/>
+      <c r="BL32" s="29"/>
+      <c r="BM32" s="29"/>
+      <c r="BN32" s="29"/>
+      <c r="BO32" s="29"/>
+      <c r="BP32" s="29"/>
+      <c r="BQ32" s="29"/>
+      <c r="BR32" s="29"/>
+      <c r="BS32" s="29"/>
+      <c r="BT32" s="29"/>
+      <c r="BU32" s="29"/>
+      <c r="BV32" s="29"/>
+      <c r="BW32" s="29"/>
+      <c r="BX32" s="29"/>
+      <c r="BY32" s="29"/>
+      <c r="BZ32" s="29"/>
+      <c r="CA32" s="29"/>
+      <c r="CB32" s="29"/>
+      <c r="CC32" s="29"/>
+      <c r="CD32" s="29"/>
+      <c r="CE32" s="29"/>
+      <c r="CF32" s="29"/>
+      <c r="CG32" s="29"/>
+      <c r="CH32" s="29"/>
+      <c r="CI32" s="29"/>
+      <c r="CJ32" s="29"/>
+      <c r="CK32" s="29"/>
+      <c r="CL32" s="29"/>
+      <c r="CM32" s="29"/>
+      <c r="CN32" s="29"/>
+      <c r="CO32" s="29"/>
+      <c r="CP32" s="29"/>
+      <c r="CQ32" s="29"/>
+      <c r="CR32" s="29"/>
+      <c r="CS32" s="29"/>
+      <c r="CT32" s="29"/>
+      <c r="CU32" s="29"/>
+      <c r="CV32" s="29"/>
+      <c r="CW32" s="29"/>
+      <c r="CX32" s="29"/>
+      <c r="CY32" s="29"/>
+      <c r="CZ32" s="29"/>
+      <c r="DA32" s="29"/>
+      <c r="DB32" s="29"/>
+      <c r="DC32" s="29"/>
+      <c r="DD32" s="29"/>
+      <c r="DE32" s="29"/>
+      <c r="DF32" s="29"/>
+      <c r="DG32" s="29"/>
+      <c r="DH32" s="29"/>
+      <c r="DI32" s="29"/>
+      <c r="DJ32" s="29"/>
+      <c r="DK32" s="29"/>
+      <c r="DL32" s="29"/>
+      <c r="DM32" s="29"/>
+      <c r="DN32" s="29"/>
+      <c r="DO32" s="29"/>
+      <c r="DP32" s="29"/>
+      <c r="DQ32" s="29"/>
+      <c r="DR32" s="29"/>
+      <c r="DS32" s="29"/>
+      <c r="DT32" s="29"/>
+      <c r="DU32" s="29"/>
+      <c r="DV32" s="29"/>
+      <c r="DW32" s="29"/>
+      <c r="DX32" s="29"/>
+      <c r="DY32" s="29"/>
+      <c r="DZ32" s="29"/>
+      <c r="EA32" s="29"/>
+      <c r="EB32" s="29"/>
+      <c r="EC32" s="29"/>
+      <c r="ED32" s="29"/>
+      <c r="EE32" s="29"/>
+      <c r="EF32" s="29"/>
+      <c r="EG32" s="29"/>
+      <c r="EH32" s="29"/>
+      <c r="EI32" s="29"/>
+      <c r="EJ32" s="29"/>
+      <c r="EK32" s="29"/>
+      <c r="EL32" s="29"/>
+      <c r="EM32" s="29"/>
+      <c r="EN32" s="29"/>
+      <c r="EO32" s="29"/>
+      <c r="EP32" s="29"/>
+      <c r="EQ32" s="29"/>
+      <c r="ER32" s="29"/>
+      <c r="ES32" s="29"/>
+      <c r="ET32" s="29"/>
+      <c r="EU32" s="29"/>
+      <c r="EV32" s="29"/>
+      <c r="EW32" s="29"/>
+      <c r="EX32" s="29"/>
+      <c r="EY32" s="29"/>
     </row>
-    <row r="33" spans="1:153">
+    <row r="33" spans="1:2">
       <c r="A33" t="s">
-        <v>132</v>
+        <v>120</v>
       </c>
       <c r="B33" t="s">
-        <v>156</v>
-      </c>
-      <c r="C33" s="29"/>
-      <c r="D33" s="29"/>
-      <c r="E33" s="29"/>
-      <c r="F33" s="29"/>
-      <c r="G33" s="29"/>
-      <c r="H33" s="29"/>
-      <c r="I33" s="29"/>
-      <c r="J33" s="29"/>
-      <c r="K33" s="29"/>
-      <c r="L33" s="29"/>
-      <c r="M33" s="29"/>
-      <c r="N33" s="29"/>
-      <c r="O33" s="29"/>
-      <c r="P33" s="29"/>
-      <c r="Q33" s="29"/>
-      <c r="R33" s="29"/>
-      <c r="S33" s="29"/>
-      <c r="T33" s="29"/>
-      <c r="U33" s="29"/>
-      <c r="V33" s="29"/>
-      <c r="W33" s="29"/>
-      <c r="X33" s="29"/>
-      <c r="Y33" s="29"/>
-      <c r="Z33" s="29"/>
-      <c r="AA33" s="29"/>
-      <c r="AB33" s="29"/>
-      <c r="AC33" s="29"/>
-      <c r="AD33" s="29"/>
-      <c r="AE33" s="29"/>
-      <c r="AF33" s="29"/>
-      <c r="AG33" s="29"/>
-      <c r="AH33" s="29"/>
-      <c r="AI33" s="29"/>
-      <c r="AJ33" s="29"/>
-      <c r="AK33" s="29"/>
-      <c r="AL33" s="29"/>
-      <c r="AM33" s="29"/>
-      <c r="AN33" s="29"/>
-      <c r="AO33" s="29"/>
-      <c r="AP33" s="29"/>
-      <c r="AQ33" s="29"/>
-      <c r="AR33" s="29"/>
-      <c r="AS33" s="29"/>
-      <c r="AT33" s="29"/>
-      <c r="AU33" s="29"/>
-      <c r="AV33" s="29"/>
-      <c r="AW33" s="29"/>
-      <c r="AX33" s="29"/>
-      <c r="AY33" s="29"/>
-      <c r="AZ33" s="29"/>
-      <c r="BA33" s="29"/>
-      <c r="BB33" s="29"/>
-      <c r="BC33" s="30"/>
-      <c r="BD33" s="29"/>
-      <c r="BE33" s="29"/>
-      <c r="BF33" s="29"/>
-      <c r="BG33" s="29"/>
-      <c r="BH33" s="29"/>
-      <c r="BI33" s="29"/>
-      <c r="BJ33" s="29"/>
-      <c r="BK33" s="29"/>
-      <c r="BL33" s="29"/>
-      <c r="BM33" s="29"/>
-      <c r="BN33" s="29"/>
-      <c r="BO33" s="29"/>
-      <c r="BP33" s="29"/>
-      <c r="BQ33" s="29"/>
-      <c r="BR33" s="29"/>
-      <c r="BS33" s="29"/>
-      <c r="BT33" s="29"/>
-      <c r="BU33" s="29"/>
-      <c r="BV33" s="29"/>
-      <c r="BW33" s="29"/>
-      <c r="BX33" s="29"/>
-      <c r="BY33" s="29"/>
-      <c r="BZ33" s="29"/>
-      <c r="CA33" s="29"/>
-      <c r="CB33" s="29"/>
-      <c r="CC33" s="29"/>
-      <c r="CD33" s="29"/>
-      <c r="CE33" s="29"/>
-      <c r="CF33" s="29"/>
-      <c r="CG33" s="29"/>
-      <c r="CH33" s="29"/>
-      <c r="CI33" s="29"/>
-      <c r="CJ33" s="29"/>
-      <c r="CK33" s="29"/>
-      <c r="CL33" s="29"/>
-      <c r="CM33" s="29"/>
-      <c r="CN33" s="29"/>
-      <c r="CO33" s="29"/>
-      <c r="CP33" s="29"/>
-      <c r="CQ33" s="29"/>
-      <c r="CR33" s="29"/>
-      <c r="CS33" s="29"/>
-      <c r="CT33" s="29"/>
-      <c r="CU33" s="29"/>
-      <c r="CV33" s="29"/>
-      <c r="CW33" s="29"/>
-      <c r="CX33" s="29"/>
-      <c r="CY33" s="29"/>
-      <c r="CZ33" s="29"/>
-      <c r="DA33" s="29"/>
-      <c r="DB33" s="29"/>
-      <c r="DC33" s="29"/>
-      <c r="DD33" s="29"/>
-      <c r="DE33" s="29"/>
-      <c r="DF33" s="29"/>
-      <c r="DG33" s="29"/>
-      <c r="DH33" s="29"/>
-      <c r="DI33" s="29"/>
-      <c r="DJ33" s="29"/>
-      <c r="DK33" s="29"/>
-      <c r="DL33" s="29"/>
-      <c r="DM33" s="29"/>
-      <c r="DN33" s="29"/>
-      <c r="DO33" s="29"/>
-      <c r="DP33" s="29"/>
-      <c r="DQ33" s="29"/>
-      <c r="DR33" s="29"/>
-      <c r="DS33" s="29"/>
-      <c r="DT33" s="29"/>
-      <c r="DU33" s="29"/>
-      <c r="DV33" s="29"/>
-      <c r="DW33" s="29"/>
-      <c r="DX33" s="29"/>
-      <c r="DY33" s="29"/>
-      <c r="DZ33" s="29"/>
-      <c r="EA33" s="29"/>
-      <c r="EB33" s="29"/>
-      <c r="EC33" s="29"/>
-      <c r="ED33" s="29"/>
-      <c r="EE33" s="29"/>
-      <c r="EF33" s="29"/>
-      <c r="EG33" s="29"/>
-      <c r="EH33" s="29"/>
-      <c r="EI33" s="29"/>
-      <c r="EJ33" s="29"/>
-      <c r="EK33" s="29"/>
-      <c r="EL33" s="29"/>
-      <c r="EM33" s="29"/>
-      <c r="EN33" s="29"/>
-      <c r="EO33" s="29"/>
-      <c r="EP33" s="29"/>
-      <c r="EQ33" s="29"/>
-      <c r="ER33" s="29"/>
-      <c r="ES33" s="29"/>
-      <c r="ET33" s="29"/>
-      <c r="EU33" s="29"/>
-      <c r="EV33" s="29"/>
-      <c r="EW33" s="29"/>
+        <v>159</v>
+      </c>
     </row>
-    <row r="34" spans="1:153">
+    <row r="34" spans="1:2">
       <c r="A34" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="B34" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
     </row>
-    <row r="35" spans="1:153">
+    <row r="35" spans="1:2">
       <c r="A35" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="B35" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
     </row>
-    <row r="36" spans="1:153">
+    <row r="36" spans="1:2">
       <c r="A36" t="s">
-        <v>104</v>
+        <v>94</v>
       </c>
       <c r="B36" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
     </row>
-    <row r="37" spans="1:153">
+    <row r="37" spans="1:2">
       <c r="A37" t="s">
-        <v>92</v>
+        <v>163</v>
       </c>
       <c r="B37" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
     </row>
-    <row r="38" spans="1:153">
+    <row r="38" spans="1:2">
       <c r="A38" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="B38" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="39" spans="1:153">
-      <c r="A39" t="s">
-        <v>163</v>
-      </c>
-      <c r="B39" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
     </row>
   </sheetData>
-  <sortState ref="A2:FE27">
-    <sortCondition ref="EV2" descending="1"/>
+  <sortState ref="A2:FH26">
+    <sortCondition ref="EX2" descending="1"/>
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
@@ -16540,157 +16382,157 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="C1" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="D1" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="E1" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="F1" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="G1" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="H1" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="I1" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="J1" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="K1" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="L1" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="M1" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="N1" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="O1" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="P1" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="Q1" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="R1" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="S1" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="T1" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="U1" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="V1" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="W1" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="X1" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="Y1" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="Z1" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="AA1" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="AB1" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="AC1" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="AD1" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="AE1" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="AF1" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="AG1" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="AH1" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="AI1" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="AJ1" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="AK1" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="AL1" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="AM1" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="AN1" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="AO1" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="AP1" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="AQ1" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="AR1" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="AS1" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="AT1" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="AU1" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="AV1" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="AW1" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="AX1" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="AY1" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="AZ1" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
     </row>
     <row r="2" spans="1:54">
@@ -17991,7 +17833,7 @@
     </row>
     <row r="14" spans="1:54">
       <c r="A14" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="B14">
         <f>SUM(B2:B9)</f>
@@ -18201,7 +18043,7 @@
     <row r="18" ht="10" customHeight="1"/>
     <row r="19" spans="1:52">
       <c r="A19" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
     </row>
     <row r="20" spans="1:52">
@@ -19446,10 +19288,10 @@
     </row>
     <row r="29" spans="1:52">
       <c r="A29" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="AZ29" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
     </row>
     <row r="30" spans="1:52">
@@ -21182,7 +21024,7 @@
   <pageSetup paperSize="9" orientation="portrait"/>
   <headerFooter/>
   <ignoredErrors>
-    <ignoredError sqref="N31:AY38 M31:M39 C31:L38" formulaRange="1"/>
+    <ignoredError sqref="C31:L38 M31:M39 N31:AY38" formulaRange="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/src/utils/sxsyzlzq/zzz_xingyuzhanli.xlsx
+++ b/src/utils/sxsyzlzq/zzz_xingyuzhanli.xlsx
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="366" uniqueCount="224">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="368" uniqueCount="226">
   <si>
     <t>区服</t>
   </si>
@@ -302,6 +302,9 @@
     <t>战力（2026.10.21）</t>
   </si>
   <si>
+    <t>战力（2026.10.28）</t>
+  </si>
+  <si>
     <t>首席（流派）</t>
   </si>
   <si>
@@ -347,6 +350,18 @@
     <t>梅养（养神）</t>
   </si>
   <si>
+    <t>杜佳捷</t>
+  </si>
+  <si>
+    <t>中低氪</t>
+  </si>
+  <si>
+    <t>丽娅（人海）</t>
+  </si>
+  <si>
+    <t>亚芬（压制）</t>
+  </si>
+  <si>
     <t>SZH</t>
   </si>
   <si>
@@ -359,18 +374,6 @@
     <t>格洛（快攻）</t>
   </si>
   <si>
-    <t>杜佳捷</t>
-  </si>
-  <si>
-    <t>中低氪</t>
-  </si>
-  <si>
-    <t>丽娅（人海）</t>
-  </si>
-  <si>
-    <t>亚芬（压制）</t>
-  </si>
-  <si>
     <t>liu</t>
   </si>
   <si>
@@ -380,61 +383,64 @@
     <t>小黑</t>
   </si>
   <si>
+    <t>蒙多（回血）</t>
+  </si>
+  <si>
+    <t>[永恒]</t>
+  </si>
+  <si>
+    <t>低氪</t>
+  </si>
+  <si>
+    <t>146区</t>
+  </si>
+  <si>
+    <t>KB</t>
+  </si>
+  <si>
+    <t>盲女（洞察）</t>
+  </si>
+  <si>
+    <t>洞察女（橙卡）</t>
+  </si>
+  <si>
+    <t>147区</t>
+  </si>
+  <si>
+    <t>没有nic</t>
+  </si>
+  <si>
+    <t>查查（养神）</t>
+  </si>
+  <si>
+    <t>148区</t>
+  </si>
+  <si>
+    <t>大核桃</t>
+  </si>
+  <si>
+    <t>眼镜妹（橙卡）</t>
+  </si>
+  <si>
+    <t>喵喵（橙卡）</t>
+  </si>
+  <si>
+    <t>请叫我阿奎</t>
+  </si>
+  <si>
+    <t>中氪</t>
+  </si>
+  <si>
+    <t>12345。</t>
+  </si>
+  <si>
+    <t>冰男（人海）</t>
+  </si>
+  <si>
+    <t>淘汰郎</t>
+  </si>
+  <si>
     <t>眼镜妹（跳费）</t>
-  </si>
-  <si>
-    <t>[永恒]</t>
-  </si>
-  <si>
-    <t>低氪</t>
-  </si>
-  <si>
-    <t>146区</t>
-  </si>
-  <si>
-    <t>KB</t>
-  </si>
-  <si>
-    <t>盲女（洞察）</t>
-  </si>
-  <si>
-    <t>洞察女（橙卡）</t>
-  </si>
-  <si>
-    <t>147区</t>
-  </si>
-  <si>
-    <t>没有nic</t>
-  </si>
-  <si>
-    <t>查查（养神）</t>
-  </si>
-  <si>
-    <t>148区</t>
-  </si>
-  <si>
-    <t>大核桃</t>
-  </si>
-  <si>
-    <t>眼镜妹（橙卡）</t>
-  </si>
-  <si>
-    <t>喵喵（橙卡）</t>
-  </si>
-  <si>
-    <t>请叫我阿奎</t>
-  </si>
-  <si>
-    <t>中氪</t>
-  </si>
-  <si>
-    <t>12345。</t>
-  </si>
-  <si>
-    <t>冰男（人海）</t>
-  </si>
-  <si>
-    <t>淘汰郎</t>
   </si>
   <si>
     <t>喵喵（跳费）</t>
@@ -1782,7 +1788,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:GC36"/>
+  <dimension ref="A1:GE36"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="11.3666666666667" customWidth="1"/>
@@ -1826,20 +1832,20 @@
     <col min="90" max="90" width="17.9333333333333" hidden="1" customWidth="1"/>
     <col min="91" max="119" width="17.2833333333333" hidden="1" customWidth="1"/>
     <col min="120" max="120" width="18.8" hidden="1" customWidth="1"/>
-    <col min="121" max="163" width="17.2833333333333" hidden="1" customWidth="1"/>
-    <col min="164" max="167" width="17.2833333333333" customWidth="1"/>
-    <col min="168" max="168" width="14.5416666666667" customWidth="1"/>
-    <col min="169" max="169" width="15.1833333333333" hidden="1" customWidth="1"/>
-    <col min="170" max="170" width="13.2583333333333" hidden="1" customWidth="1"/>
-    <col min="171" max="171" width="11.625" hidden="1" customWidth="1"/>
-    <col min="172" max="172" width="12.6083333333333" hidden="1" customWidth="1"/>
-    <col min="173" max="173" width="15.0166666666667" hidden="1" customWidth="1"/>
-    <col min="174" max="174" width="12.625"/>
-    <col min="175" max="175" width="11.4083333333333" hidden="1" customWidth="1"/>
-    <col min="176" max="176" width="10.425" customWidth="1"/>
+    <col min="121" max="165" width="17.2833333333333" hidden="1" customWidth="1"/>
+    <col min="166" max="169" width="17.2833333333333" customWidth="1"/>
+    <col min="170" max="170" width="14.5416666666667" customWidth="1"/>
+    <col min="171" max="171" width="15.1833333333333" hidden="1" customWidth="1"/>
+    <col min="172" max="172" width="13.2583333333333" hidden="1" customWidth="1"/>
+    <col min="173" max="173" width="11.625" hidden="1" customWidth="1"/>
+    <col min="174" max="174" width="12.6083333333333" hidden="1" customWidth="1"/>
+    <col min="175" max="175" width="15.0166666666667" hidden="1" customWidth="1"/>
+    <col min="176" max="176" width="12.625"/>
+    <col min="177" max="177" width="11.4083333333333" hidden="1" customWidth="1"/>
+    <col min="178" max="178" width="10.425" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:185">
+    <row r="1" spans="1:187">
       <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
@@ -2339,45 +2345,51 @@
         <v>87</v>
       </c>
       <c r="FK1" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="FL1" s="5" t="s">
         <v>88</v>
       </c>
-      <c r="FL1" s="5" t="s">
+      <c r="FM1" s="5" t="s">
         <v>89</v>
       </c>
-      <c r="FM1" t="s">
+      <c r="FN1" s="5" t="s">
         <v>90</v>
       </c>
-      <c r="FN1" t="s">
+      <c r="FO1" t="s">
         <v>91</v>
       </c>
-      <c r="FO1" t="s">
+      <c r="FP1" t="s">
         <v>92</v>
       </c>
-      <c r="FP1" t="s">
+      <c r="FQ1" t="s">
         <v>93</v>
       </c>
-      <c r="FQ1" t="s">
+      <c r="FR1" t="s">
         <v>94</v>
       </c>
-      <c r="FR1" t="s">
+      <c r="FS1" t="s">
         <v>95</v>
       </c>
-      <c r="FS1" t="s">
+      <c r="FT1" t="s">
         <v>96</v>
       </c>
-      <c r="FT1" t="s">
+      <c r="FU1" t="s">
         <v>97</v>
       </c>
+      <c r="FV1" t="s">
+        <v>98</v>
+      </c>
     </row>
-    <row r="2" s="8" customFormat="1" spans="1:185">
+    <row r="2" s="8" customFormat="1" spans="1:187">
       <c r="A2" s="1" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="D2" s="1">
         <v>1754.54</v>
@@ -2949,1277 +2961,1298 @@
       <c r="FJ2" s="13">
         <v>8386.99</v>
       </c>
-      <c r="FK2" s="12" t="s">
-        <v>101</v>
-      </c>
-      <c r="FL2" s="11">
-        <v>1854.71</v>
-      </c>
-      <c r="FM2" s="11" t="s">
+      <c r="FK2" s="13">
+        <f>FL2-FJ2</f>
+        <v>31.3400000000001</v>
+      </c>
+      <c r="FL2" s="12">
+        <v>8418.33</v>
+      </c>
+      <c r="FM2" s="12" t="s">
         <v>102</v>
       </c>
       <c r="FN2" s="11">
+        <v>1705.66</v>
+      </c>
+      <c r="FO2" s="11" t="s">
+        <v>103</v>
+      </c>
+      <c r="FP2" s="11">
         <v>686.88</v>
       </c>
-      <c r="FO2" s="1">
+      <c r="FQ2" s="1">
         <v>300</v>
       </c>
-      <c r="FP2" s="1">
+      <c r="FR2" s="1">
         <v>2.2</v>
       </c>
-      <c r="FQ2" s="1">
+      <c r="FS2" s="1">
         <v>132783</v>
       </c>
-      <c r="FR2" s="11">
-        <f>2.3635/(FJ2/FL2)</f>
-        <v>0.522667498709311</v>
-      </c>
-      <c r="FS2" s="11">
+      <c r="FT2" s="11">
+        <f>2.3635/(FL2/FN2)</f>
+        <v>0.478874956196775</v>
+      </c>
+      <c r="FU2" s="11">
         <f>BP2-D2</f>
         <v>2267.65</v>
       </c>
-      <c r="FT2" s="11">
-        <f>FJ2-FB2</f>
-        <v>598.24</v>
+      <c r="FV2" s="11">
+        <f>FL2-FD2</f>
+        <v>395.73</v>
       </c>
     </row>
-    <row r="3" spans="1:185">
+    <row r="3" spans="1:187">
       <c r="A3" s="1" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="D3" s="1">
-        <v>2136.24</v>
+        <v>1726.42</v>
       </c>
       <c r="E3" s="1">
         <f>F3-D3</f>
-        <v>40.8200000000002</v>
+        <v>56.28</v>
       </c>
       <c r="F3" s="1">
-        <v>2177.06</v>
+        <v>1782.7</v>
       </c>
       <c r="G3" s="1">
         <f>H3-F3</f>
-        <v>62.5999999999999</v>
+        <v>70.9199999999998</v>
       </c>
       <c r="H3" s="1">
-        <v>2239.66</v>
+        <v>1853.62</v>
       </c>
       <c r="I3" s="1">
         <f>J3-H3</f>
-        <v>47.0700000000002</v>
+        <v>49.5800000000002</v>
       </c>
       <c r="J3" s="1">
-        <v>2286.73</v>
+        <v>1903.2</v>
       </c>
       <c r="K3" s="1">
         <f>L3-J3</f>
-        <v>25.52</v>
+        <v>40.4099999999999</v>
       </c>
       <c r="L3" s="1">
-        <v>2312.25</v>
+        <v>1943.61</v>
       </c>
       <c r="M3" s="1">
         <f>N3-L3</f>
-        <v>36.7800000000002</v>
+        <v>30.01</v>
       </c>
       <c r="N3" s="1">
-        <v>2349.03</v>
+        <v>1973.62</v>
       </c>
       <c r="O3" s="1">
         <f>P3-N3</f>
-        <v>-18.02</v>
+        <v>83.2800000000002</v>
       </c>
       <c r="P3" s="1">
-        <v>2331.01</v>
+        <v>2056.9</v>
       </c>
       <c r="Q3" s="1">
         <f>R3-P3</f>
-        <v>62.7599999999998</v>
+        <v>25.6399999999999</v>
       </c>
       <c r="R3" s="1">
-        <v>2393.77</v>
+        <v>2082.54</v>
       </c>
       <c r="S3" s="1">
         <f>T3-R3</f>
-        <v>55.5599999999999</v>
+        <v>66.46</v>
       </c>
       <c r="T3" s="1">
-        <v>2449.33</v>
+        <v>2149</v>
       </c>
       <c r="U3" s="1">
         <f>V3-T3</f>
-        <v>31.96</v>
+        <v>43.5599999999999</v>
       </c>
       <c r="V3" s="10">
-        <v>2481.29</v>
+        <v>2192.56</v>
       </c>
       <c r="W3" s="1">
         <f>X3-V3</f>
-        <v>109.47</v>
+        <v>46.3200000000002</v>
       </c>
       <c r="X3" s="10">
-        <v>2590.76</v>
+        <v>2238.88</v>
       </c>
       <c r="Y3" s="1">
         <f>Z3-X3</f>
-        <v>20.4299999999998</v>
+        <v>17.23</v>
       </c>
       <c r="Z3" s="1">
-        <v>2611.19</v>
+        <v>2256.11</v>
       </c>
       <c r="AA3" s="1">
         <f>AB3-Z3</f>
-        <v>32.9899999999998</v>
+        <v>97.5799999999999</v>
       </c>
       <c r="AB3" s="1">
-        <v>2644.18</v>
+        <v>2353.69</v>
       </c>
       <c r="AC3" s="1">
         <f>AD3-AB3</f>
-        <v>45.9000000000001</v>
+        <v>58.8600000000001</v>
       </c>
       <c r="AD3" s="1">
-        <v>2690.08</v>
+        <v>2412.55</v>
       </c>
       <c r="AE3" s="11">
         <f>AF3-AD3</f>
-        <v>62.79</v>
+        <v>33.52</v>
       </c>
       <c r="AF3" s="11">
-        <v>2752.87</v>
+        <v>2446.07</v>
       </c>
       <c r="AG3" s="11">
         <f>AH3-AF3</f>
-        <v>72.2800000000002</v>
+        <v>77.4199999999996</v>
       </c>
       <c r="AH3" s="11">
-        <v>2825.15</v>
+        <v>2523.49</v>
       </c>
       <c r="AI3" s="11">
         <f>AJ3-AH3</f>
-        <v>38.1900000000001</v>
+        <v>44.5500000000002</v>
       </c>
       <c r="AJ3" s="11">
-        <v>2863.34</v>
+        <v>2568.04</v>
       </c>
       <c r="AK3" s="11">
         <f>AL3-AJ3</f>
-        <v>82.1299999999997</v>
+        <v>60.6700000000001</v>
       </c>
       <c r="AL3" s="11">
-        <v>2945.47</v>
+        <v>2628.71</v>
       </c>
       <c r="AM3" s="11">
         <f>AN3-AL3</f>
-        <v>39.5400000000004</v>
+        <v>38.8600000000001</v>
       </c>
       <c r="AN3" s="11">
-        <v>2985.01</v>
+        <v>2667.57</v>
       </c>
       <c r="AO3" s="11">
         <f>AP3-AN3</f>
-        <v>42.0499999999997</v>
+        <v>40.96</v>
       </c>
       <c r="AP3" s="11">
-        <v>3027.06</v>
+        <v>2708.53</v>
       </c>
       <c r="AQ3" s="11">
         <f>AR3-AP3</f>
-        <v>50.5799999999999</v>
+        <v>53.2099999999996</v>
       </c>
       <c r="AR3" s="11">
-        <v>3077.64</v>
+        <v>2761.74</v>
       </c>
       <c r="AS3" s="11">
         <f>AT3-AR3</f>
-        <v>42.5599999999999</v>
+        <v>44</v>
       </c>
       <c r="AT3" s="11">
-        <v>3120.2</v>
+        <v>2805.74</v>
       </c>
       <c r="AU3" s="12">
         <f>AV3-AT3</f>
-        <v>91.8800000000001</v>
+        <v>57.5</v>
       </c>
       <c r="AV3" s="12">
-        <v>3212.08</v>
+        <v>2863.24</v>
       </c>
       <c r="AW3" s="13">
         <f>AX3-AV3</f>
-        <v>74.0500000000002</v>
+        <v>54.4300000000003</v>
       </c>
       <c r="AX3" s="13">
-        <v>3286.13</v>
+        <v>2917.67</v>
       </c>
       <c r="AY3" s="13">
         <f>AZ3-AX3</f>
-        <v>43.98</v>
+        <v>56.3800000000001</v>
       </c>
       <c r="AZ3" s="13">
-        <v>3330.11</v>
+        <v>2974.05</v>
       </c>
       <c r="BA3" s="13">
         <f>BB3-AZ3</f>
-        <v>35.3499999999999</v>
+        <v>41.4399999999996</v>
       </c>
       <c r="BB3" s="13">
-        <v>3365.46</v>
+        <v>3015.49</v>
       </c>
       <c r="BC3" s="13">
         <f>BD3-BB3</f>
-        <v>38.3899999999999</v>
+        <v>42.1400000000003</v>
       </c>
       <c r="BD3" s="13">
-        <v>3403.85</v>
+        <v>3057.63</v>
       </c>
       <c r="BE3" s="12">
         <f>BF3-BD3</f>
-        <v>53.21</v>
+        <v>43.9899999999998</v>
       </c>
       <c r="BF3" s="13">
-        <v>3457.06</v>
+        <v>3101.62</v>
       </c>
       <c r="BG3" s="13">
         <f>BH3-BF3</f>
-        <v>115.36</v>
+        <v>105.04</v>
       </c>
       <c r="BH3" s="13">
-        <v>3572.42</v>
+        <v>3206.66</v>
       </c>
       <c r="BI3" s="13">
         <f>BJ3-BH3</f>
-        <v>19.0799999999999</v>
+        <v>38.7800000000002</v>
       </c>
       <c r="BJ3" s="13">
-        <v>3591.5</v>
+        <v>3245.44</v>
       </c>
       <c r="BK3" s="13">
         <f>BL3-BJ3</f>
-        <v>50.9499999999998</v>
+        <v>30.5099999999998</v>
       </c>
       <c r="BL3" s="13">
-        <v>3642.45</v>
+        <v>3275.95</v>
       </c>
       <c r="BM3" s="13">
         <f>BN3-BL3</f>
-        <v>32.1300000000001</v>
+        <v>44.8600000000001</v>
       </c>
       <c r="BN3" s="13">
-        <v>3674.58</v>
+        <v>3320.81</v>
       </c>
       <c r="BO3" s="13">
         <f>BP3-BN3</f>
-        <v>46.4099999999999</v>
+        <v>59.8400000000001</v>
       </c>
       <c r="BP3" s="13">
-        <v>3720.99</v>
+        <v>3380.65</v>
       </c>
       <c r="BQ3" s="13">
         <f>BR3-BP3</f>
-        <v>52.0300000000002</v>
+        <v>24.6300000000001</v>
       </c>
       <c r="BR3" s="13">
-        <v>3773.02</v>
+        <v>3405.28</v>
       </c>
       <c r="BS3" s="13">
         <f>BT3-BR3</f>
-        <v>27.8600000000001</v>
+        <v>93.3399999999997</v>
       </c>
       <c r="BT3" s="13">
-        <v>3800.88</v>
+        <v>3498.62</v>
       </c>
       <c r="BU3" s="13">
         <f>BV3-BT3</f>
-        <v>49.29</v>
+        <v>36.1300000000001</v>
       </c>
       <c r="BV3" s="13">
-        <v>3850.17</v>
+        <v>3534.75</v>
       </c>
       <c r="BW3" s="13">
         <f>BX3-BV3</f>
-        <v>124.53</v>
+        <v>76.7600000000002</v>
       </c>
       <c r="BX3" s="13">
-        <v>3974.7</v>
+        <v>3611.51</v>
       </c>
       <c r="BY3" s="13">
         <f>BZ3-BX3</f>
-        <v>10.3200000000002</v>
+        <v>39.77</v>
       </c>
       <c r="BZ3" s="13">
-        <v>3985.02</v>
+        <v>3651.28</v>
       </c>
       <c r="CA3" s="13">
         <f>CB3-BZ3</f>
-        <v>123.75</v>
+        <v>37.25</v>
       </c>
       <c r="CB3" s="13">
-        <v>4108.77</v>
+        <v>3688.53</v>
       </c>
       <c r="CC3" s="13">
         <f>CD3-CB3</f>
-        <v>30.1999999999998</v>
+        <v>79.0899999999997</v>
       </c>
       <c r="CD3" s="13">
-        <v>4138.97</v>
+        <v>3767.62</v>
       </c>
       <c r="CE3" s="13">
         <f>CF3-CD3</f>
-        <v>28.96</v>
+        <v>46.3600000000001</v>
       </c>
       <c r="CF3" s="13">
-        <v>4167.93</v>
+        <v>3813.98</v>
       </c>
       <c r="CG3" s="13">
         <f>CH3-CF3</f>
-        <v>87.5099999999993</v>
+        <v>88.1300000000001</v>
       </c>
       <c r="CH3" s="13">
-        <v>4255.44</v>
+        <v>3902.11</v>
       </c>
       <c r="CI3" s="13">
         <f>CJ3-CH3</f>
-        <v>49.25</v>
+        <v>53.0799999999999</v>
       </c>
       <c r="CJ3" s="13">
-        <v>4304.69</v>
+        <v>3955.19</v>
       </c>
       <c r="CK3" s="13">
         <f>CL3-CJ3</f>
-        <v>26.9800000000005</v>
+        <v>53.9200000000001</v>
       </c>
       <c r="CL3" s="13">
-        <v>4331.67</v>
+        <v>4009.11</v>
       </c>
       <c r="CM3" s="13">
         <f>CN3-CL3</f>
-        <v>20.75</v>
+        <v>50.3099999999999</v>
       </c>
       <c r="CN3" s="13">
-        <v>4352.42</v>
+        <v>4059.42</v>
       </c>
       <c r="CO3" s="13">
         <f>CP3-CN3</f>
-        <v>33.1000000000004</v>
+        <v>66.9799999999996</v>
       </c>
       <c r="CP3" s="13">
-        <v>4385.52</v>
+        <v>4126.4</v>
       </c>
       <c r="CQ3" s="13">
         <f>CR3-CP3</f>
-        <v>26.3599999999997</v>
+        <v>45.1900000000005</v>
       </c>
       <c r="CR3" s="13">
-        <v>4411.88</v>
+        <v>4171.59</v>
       </c>
       <c r="CS3" s="13">
         <f>CT3-CR3</f>
-        <v>60.2299999999996</v>
+        <v>130.22</v>
       </c>
       <c r="CT3" s="13">
-        <v>4472.11</v>
+        <v>4301.81</v>
       </c>
       <c r="CU3" s="13">
         <f>CV3-CT3</f>
-        <v>69.3200000000006</v>
+        <v>63.2299999999996</v>
       </c>
       <c r="CV3" s="13">
-        <v>4541.43</v>
+        <v>4365.04</v>
       </c>
       <c r="CW3" s="12">
         <f>CX3-CV3</f>
-        <v>175.25</v>
+        <v>53.1999999999998</v>
       </c>
       <c r="CX3" s="13">
-        <v>4716.68</v>
+        <v>4418.24</v>
       </c>
       <c r="CY3" s="13">
         <f>CZ3-CX3</f>
-        <v>17.4899999999998</v>
+        <v>74.3299999999999</v>
       </c>
       <c r="CZ3" s="13">
-        <v>4734.17</v>
+        <v>4492.57</v>
       </c>
       <c r="DA3" s="13">
         <f>DB3-CZ3</f>
-        <v>69.4399999999996</v>
+        <v>46.0799999999999</v>
       </c>
       <c r="DB3" s="13">
-        <v>4803.61</v>
+        <v>4538.65</v>
       </c>
       <c r="DC3" s="13">
         <f>DD3-DB3</f>
-        <v>67.0100000000002</v>
+        <v>50.4400000000005</v>
       </c>
       <c r="DD3" s="13">
-        <v>4870.62</v>
+        <v>4589.09</v>
       </c>
       <c r="DE3" s="13">
         <f>DF3-DD3</f>
-        <v>56.1800000000003</v>
+        <v>70.5599999999995</v>
       </c>
       <c r="DF3" s="13">
-        <v>4926.8</v>
+        <v>4659.65</v>
       </c>
       <c r="DG3" s="13">
         <f>DH3-DF3</f>
-        <v>-16.1300000000001</v>
+        <v>16.54</v>
       </c>
       <c r="DH3" s="13">
-        <v>4910.67</v>
+        <v>4676.19</v>
       </c>
       <c r="DI3" s="13">
         <f>DJ3-DH3</f>
-        <v>74.96</v>
+        <v>51.5700000000006</v>
       </c>
       <c r="DJ3" s="13">
-        <v>4985.63</v>
+        <v>4727.76</v>
       </c>
       <c r="DK3" s="13">
         <f>DL3-DJ3</f>
-        <v>89.8999999999996</v>
+        <v>39.5799999999999</v>
       </c>
       <c r="DL3" s="13">
-        <v>5075.53</v>
+        <v>4767.34</v>
       </c>
       <c r="DM3" s="13">
         <f>DN3-DL3</f>
-        <v>74.7600000000002</v>
+        <v>65.6099999999997</v>
       </c>
       <c r="DN3" s="13">
-        <v>5150.29</v>
+        <v>4832.95</v>
       </c>
       <c r="DO3" s="12">
         <f>DP3-DN3</f>
-        <v>17.6400000000003</v>
+        <v>100.79</v>
       </c>
       <c r="DP3" s="13">
-        <v>5167.93</v>
+        <v>4933.74</v>
       </c>
       <c r="DQ3" s="13">
         <f>DR3-DP3</f>
-        <v>45.4099999999999</v>
+        <v>51.6400000000003</v>
       </c>
       <c r="DR3" s="13">
-        <v>5213.34</v>
+        <v>4985.38</v>
       </c>
       <c r="DS3" s="13">
         <f>DT3-DR3</f>
-        <v>69.7299999999996</v>
+        <v>73.29</v>
       </c>
       <c r="DT3" s="13">
-        <v>5283.07</v>
+        <v>5058.67</v>
       </c>
       <c r="DU3" s="13">
         <f>DV3-DT3</f>
-        <v>49.1000000000004</v>
+        <v>132.03</v>
       </c>
       <c r="DV3" s="13">
-        <v>5332.17</v>
+        <v>5190.7</v>
       </c>
       <c r="DW3" s="13">
         <f>DX3-DV3</f>
-        <v>44.9200000000001</v>
+        <v>38.6500000000005</v>
       </c>
       <c r="DX3" s="13">
-        <v>5377.09</v>
+        <v>5229.35</v>
       </c>
       <c r="DY3" s="13">
         <f>DZ3-DX3</f>
-        <v>95.6099999999997</v>
+        <v>59.46</v>
       </c>
       <c r="DZ3" s="13">
-        <v>5472.7</v>
+        <v>5288.81</v>
       </c>
       <c r="EA3" s="13">
         <f>EB3-DZ3</f>
-        <v>75.0600000000004</v>
+        <v>26.2799999999997</v>
       </c>
       <c r="EB3" s="13">
-        <v>5547.76</v>
+        <v>5315.09</v>
       </c>
       <c r="EC3" s="13">
         <f>ED3-EB3</f>
-        <v>98.9099999999999</v>
+        <v>54.79</v>
       </c>
       <c r="ED3" s="13">
-        <v>5646.67</v>
+        <v>5369.88</v>
       </c>
       <c r="EE3" s="13">
         <f>EF3-ED3</f>
-        <v>-85.6800000000003</v>
+        <v>52.5900000000001</v>
       </c>
       <c r="EF3" s="13">
-        <v>5560.99</v>
+        <v>5422.47</v>
       </c>
       <c r="EG3" s="13">
         <f>EH3-EF3</f>
-        <v>152.59</v>
+        <v>44.5</v>
       </c>
       <c r="EH3" s="13">
-        <v>5713.58</v>
+        <v>5466.97</v>
       </c>
       <c r="EI3" s="13">
         <f>EJ3-EH3</f>
-        <v>71.1000000000004</v>
+        <v>51.71</v>
       </c>
       <c r="EJ3" s="13">
-        <v>5784.68</v>
+        <v>5518.68</v>
       </c>
       <c r="EK3" s="13">
         <f>EL3-EJ3</f>
-        <v>0</v>
+        <v>77.1700000000001</v>
       </c>
       <c r="EL3" s="13">
-        <v>5784.68</v>
+        <v>5595.85</v>
       </c>
       <c r="EM3" s="13">
         <f>EN3-EL3</f>
         <v>0</v>
       </c>
       <c r="EN3" s="13">
-        <v>5784.68</v>
+        <v>5595.85</v>
       </c>
       <c r="EO3" s="13">
         <f>EP3-EN3</f>
-        <v>0</v>
+        <v>42.1399999999994</v>
       </c>
       <c r="EP3" s="13">
-        <v>5784.68</v>
+        <v>5637.99</v>
       </c>
       <c r="EQ3" s="13">
         <f>ER3-EP3</f>
-        <v>130.08</v>
+        <v>39.9000000000005</v>
       </c>
       <c r="ER3" s="13">
-        <v>5914.76</v>
+        <v>5677.89</v>
       </c>
       <c r="ES3" s="13">
         <f>ET3-ER3</f>
-        <v>-18.8100000000004</v>
+        <v>38.4399999999996</v>
       </c>
       <c r="ET3" s="13">
-        <v>5895.95</v>
+        <v>5716.33</v>
       </c>
       <c r="EU3" s="13">
         <f>EV3-ET3</f>
-        <v>121.04</v>
+        <v>31.5900000000001</v>
       </c>
       <c r="EV3" s="13">
-        <v>6016.99</v>
+        <v>5747.92</v>
       </c>
       <c r="EW3" s="13">
         <f>EX3-EV3</f>
-        <v>19.5300000000007</v>
+        <v>20.1599999999999</v>
       </c>
       <c r="EX3" s="13">
-        <v>6036.52</v>
+        <v>5768.08</v>
       </c>
       <c r="EY3" s="13">
         <f>EZ3-EX3</f>
-        <v>-52.0100000000002</v>
+        <v>42.7600000000002</v>
       </c>
       <c r="EZ3" s="13">
-        <v>5984.51</v>
+        <v>5810.84</v>
       </c>
       <c r="FA3" s="13">
         <f>FB3-EZ3</f>
-        <v>45.0100000000002</v>
+        <v>52.1599999999999</v>
       </c>
       <c r="FB3" s="13">
-        <v>6029.52</v>
+        <v>5863</v>
       </c>
       <c r="FC3" s="13">
         <f>FD3-FB3</f>
-        <v>-65.2300000000005</v>
+        <v>64.79</v>
       </c>
       <c r="FD3" s="13">
-        <v>5964.29</v>
+        <v>5927.79</v>
       </c>
       <c r="FE3" s="13">
         <f>FF3-FD3</f>
-        <v>62.3500000000004</v>
+        <v>24.6800000000003</v>
       </c>
       <c r="FF3" s="13">
-        <v>6026.64</v>
+        <v>5952.47</v>
       </c>
       <c r="FG3" s="13">
         <f>FH3-FF3</f>
-        <v>40.9399999999996</v>
+        <v>91.2599999999993</v>
       </c>
       <c r="FH3" s="12">
-        <v>6067.58</v>
+        <v>6043.73</v>
       </c>
       <c r="FI3" s="13">
         <f>FJ3-FH3</f>
-        <v>41.9200000000001</v>
+        <v>61.6700000000001</v>
       </c>
       <c r="FJ3" s="13">
-        <v>6109.5</v>
-      </c>
-      <c r="FK3" s="12" t="s">
-        <v>105</v>
-      </c>
-      <c r="FL3" s="11">
-        <v>2255.87</v>
-      </c>
-      <c r="FM3" s="11" t="s">
+        <v>6105.4</v>
+      </c>
+      <c r="FK3" s="13">
+        <f>FL3-FJ3</f>
+        <v>72.75</v>
+      </c>
+      <c r="FL3" s="12">
+        <v>6178.15</v>
+      </c>
+      <c r="FM3" s="12" t="s">
         <v>106</v>
       </c>
       <c r="FN3" s="11">
-        <v>1211.82</v>
-      </c>
-      <c r="FO3" s="1">
-        <v>20</v>
-      </c>
-      <c r="FP3" s="1">
-        <v>1.2</v>
+        <v>2184.42</v>
+      </c>
+      <c r="FO3" s="11" t="s">
+        <v>107</v>
+      </c>
+      <c r="FP3" s="11">
+        <v>754.67</v>
       </c>
       <c r="FQ3" s="1">
-        <v>153852</v>
-      </c>
-      <c r="FR3" s="11">
-        <f>2.3635/(FJ3/FL3)</f>
-        <v>0.872698051395368</v>
-      </c>
-      <c r="FS3" s="11">
+        <v>50</v>
+      </c>
+      <c r="FR3" s="1">
+        <v>1.3</v>
+      </c>
+      <c r="FS3" s="1">
+        <v>124763</v>
+      </c>
+      <c r="FT3" s="11">
+        <f>2.3635/(FL3/FN3)</f>
+        <v>0.835667096137193</v>
+      </c>
+      <c r="FU3" s="11">
         <f>BP3-D3</f>
-        <v>1584.75</v>
-      </c>
-      <c r="FT3" s="11">
-        <f>FJ3-FB3</f>
-        <v>79.9799999999996</v>
+        <v>1654.23</v>
+      </c>
+      <c r="FV3" s="11">
+        <f>FL3-FD3</f>
+        <v>250.36</v>
       </c>
     </row>
-    <row r="4" spans="1:185">
+    <row r="4" spans="1:187">
       <c r="A4" s="1" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D4" s="1">
-        <v>1726.42</v>
+        <v>2136.24</v>
       </c>
       <c r="E4" s="1">
         <f>F4-D4</f>
-        <v>56.28</v>
+        <v>40.8200000000002</v>
       </c>
       <c r="F4" s="1">
-        <v>1782.7</v>
+        <v>2177.06</v>
       </c>
       <c r="G4" s="1">
         <f>H4-F4</f>
-        <v>70.9199999999998</v>
+        <v>62.5999999999999</v>
       </c>
       <c r="H4" s="1">
-        <v>1853.62</v>
+        <v>2239.66</v>
       </c>
       <c r="I4" s="1">
         <f>J4-H4</f>
-        <v>49.5800000000002</v>
+        <v>47.0700000000002</v>
       </c>
       <c r="J4" s="1">
-        <v>1903.2</v>
+        <v>2286.73</v>
       </c>
       <c r="K4" s="1">
         <f>L4-J4</f>
-        <v>40.4099999999999</v>
+        <v>25.52</v>
       </c>
       <c r="L4" s="1">
-        <v>1943.61</v>
+        <v>2312.25</v>
       </c>
       <c r="M4" s="1">
         <f>N4-L4</f>
-        <v>30.01</v>
+        <v>36.7800000000002</v>
       </c>
       <c r="N4" s="1">
-        <v>1973.62</v>
+        <v>2349.03</v>
       </c>
       <c r="O4" s="1">
         <f>P4-N4</f>
-        <v>83.2800000000002</v>
+        <v>-18.02</v>
       </c>
       <c r="P4" s="1">
-        <v>2056.9</v>
+        <v>2331.01</v>
       </c>
       <c r="Q4" s="1">
         <f>R4-P4</f>
-        <v>25.6399999999999</v>
+        <v>62.7599999999998</v>
       </c>
       <c r="R4" s="1">
-        <v>2082.54</v>
+        <v>2393.77</v>
       </c>
       <c r="S4" s="1">
         <f>T4-R4</f>
-        <v>66.46</v>
+        <v>55.5599999999999</v>
       </c>
       <c r="T4" s="1">
-        <v>2149</v>
+        <v>2449.33</v>
       </c>
       <c r="U4" s="1">
         <f>V4-T4</f>
-        <v>43.5599999999999</v>
+        <v>31.96</v>
       </c>
       <c r="V4" s="10">
-        <v>2192.56</v>
+        <v>2481.29</v>
       </c>
       <c r="W4" s="1">
         <f>X4-V4</f>
-        <v>46.3200000000002</v>
+        <v>109.47</v>
       </c>
       <c r="X4" s="10">
-        <v>2238.88</v>
+        <v>2590.76</v>
       </c>
       <c r="Y4" s="1">
         <f>Z4-X4</f>
-        <v>17.23</v>
+        <v>20.4299999999998</v>
       </c>
       <c r="Z4" s="1">
-        <v>2256.11</v>
+        <v>2611.19</v>
       </c>
       <c r="AA4" s="1">
         <f>AB4-Z4</f>
-        <v>97.5799999999999</v>
+        <v>32.9899999999998</v>
       </c>
       <c r="AB4" s="1">
-        <v>2353.69</v>
+        <v>2644.18</v>
       </c>
       <c r="AC4" s="1">
         <f>AD4-AB4</f>
-        <v>58.8600000000001</v>
+        <v>45.9000000000001</v>
       </c>
       <c r="AD4" s="1">
-        <v>2412.55</v>
+        <v>2690.08</v>
       </c>
       <c r="AE4" s="11">
         <f>AF4-AD4</f>
-        <v>33.52</v>
+        <v>62.79</v>
       </c>
       <c r="AF4" s="11">
-        <v>2446.07</v>
+        <v>2752.87</v>
       </c>
       <c r="AG4" s="11">
         <f>AH4-AF4</f>
-        <v>77.4199999999996</v>
+        <v>72.2800000000002</v>
       </c>
       <c r="AH4" s="11">
-        <v>2523.49</v>
+        <v>2825.15</v>
       </c>
       <c r="AI4" s="11">
         <f>AJ4-AH4</f>
-        <v>44.5500000000002</v>
+        <v>38.1900000000001</v>
       </c>
       <c r="AJ4" s="11">
-        <v>2568.04</v>
+        <v>2863.34</v>
       </c>
       <c r="AK4" s="11">
         <f>AL4-AJ4</f>
-        <v>60.6700000000001</v>
+        <v>82.1299999999997</v>
       </c>
       <c r="AL4" s="11">
-        <v>2628.71</v>
+        <v>2945.47</v>
       </c>
       <c r="AM4" s="11">
         <f>AN4-AL4</f>
-        <v>38.8600000000001</v>
+        <v>39.5400000000004</v>
       </c>
       <c r="AN4" s="11">
-        <v>2667.57</v>
+        <v>2985.01</v>
       </c>
       <c r="AO4" s="11">
         <f>AP4-AN4</f>
-        <v>40.96</v>
+        <v>42.0499999999997</v>
       </c>
       <c r="AP4" s="11">
-        <v>2708.53</v>
+        <v>3027.06</v>
       </c>
       <c r="AQ4" s="11">
         <f>AR4-AP4</f>
-        <v>53.2099999999996</v>
+        <v>50.5799999999999</v>
       </c>
       <c r="AR4" s="11">
-        <v>2761.74</v>
+        <v>3077.64</v>
       </c>
       <c r="AS4" s="11">
         <f>AT4-AR4</f>
-        <v>44</v>
+        <v>42.5599999999999</v>
       </c>
       <c r="AT4" s="11">
-        <v>2805.74</v>
+        <v>3120.2</v>
       </c>
       <c r="AU4" s="12">
         <f>AV4-AT4</f>
-        <v>57.5</v>
+        <v>91.8800000000001</v>
       </c>
       <c r="AV4" s="12">
-        <v>2863.24</v>
+        <v>3212.08</v>
       </c>
       <c r="AW4" s="13">
         <f>AX4-AV4</f>
-        <v>54.4300000000003</v>
+        <v>74.0500000000002</v>
       </c>
       <c r="AX4" s="13">
-        <v>2917.67</v>
+        <v>3286.13</v>
       </c>
       <c r="AY4" s="13">
         <f>AZ4-AX4</f>
-        <v>56.3800000000001</v>
+        <v>43.98</v>
       </c>
       <c r="AZ4" s="13">
-        <v>2974.05</v>
+        <v>3330.11</v>
       </c>
       <c r="BA4" s="13">
         <f>BB4-AZ4</f>
-        <v>41.4399999999996</v>
+        <v>35.3499999999999</v>
       </c>
       <c r="BB4" s="13">
-        <v>3015.49</v>
+        <v>3365.46</v>
       </c>
       <c r="BC4" s="13">
         <f>BD4-BB4</f>
-        <v>42.1400000000003</v>
+        <v>38.3899999999999</v>
       </c>
       <c r="BD4" s="13">
-        <v>3057.63</v>
+        <v>3403.85</v>
       </c>
       <c r="BE4" s="12">
         <f>BF4-BD4</f>
-        <v>43.9899999999998</v>
+        <v>53.21</v>
       </c>
       <c r="BF4" s="13">
-        <v>3101.62</v>
+        <v>3457.06</v>
       </c>
       <c r="BG4" s="13">
         <f>BH4-BF4</f>
-        <v>105.04</v>
+        <v>115.36</v>
       </c>
       <c r="BH4" s="13">
-        <v>3206.66</v>
+        <v>3572.42</v>
       </c>
       <c r="BI4" s="13">
         <f>BJ4-BH4</f>
-        <v>38.7800000000002</v>
+        <v>19.0799999999999</v>
       </c>
       <c r="BJ4" s="13">
-        <v>3245.44</v>
+        <v>3591.5</v>
       </c>
       <c r="BK4" s="13">
         <f>BL4-BJ4</f>
-        <v>30.5099999999998</v>
+        <v>50.9499999999998</v>
       </c>
       <c r="BL4" s="13">
-        <v>3275.95</v>
+        <v>3642.45</v>
       </c>
       <c r="BM4" s="13">
         <f>BN4-BL4</f>
-        <v>44.8600000000001</v>
+        <v>32.1300000000001</v>
       </c>
       <c r="BN4" s="13">
-        <v>3320.81</v>
+        <v>3674.58</v>
       </c>
       <c r="BO4" s="13">
         <f>BP4-BN4</f>
-        <v>59.8400000000001</v>
+        <v>46.4099999999999</v>
       </c>
       <c r="BP4" s="13">
-        <v>3380.65</v>
+        <v>3720.99</v>
       </c>
       <c r="BQ4" s="13">
         <f>BR4-BP4</f>
-        <v>24.6300000000001</v>
+        <v>52.0300000000002</v>
       </c>
       <c r="BR4" s="13">
-        <v>3405.28</v>
+        <v>3773.02</v>
       </c>
       <c r="BS4" s="13">
         <f>BT4-BR4</f>
-        <v>93.3399999999997</v>
+        <v>27.8600000000001</v>
       </c>
       <c r="BT4" s="13">
-        <v>3498.62</v>
+        <v>3800.88</v>
       </c>
       <c r="BU4" s="13">
         <f>BV4-BT4</f>
-        <v>36.1300000000001</v>
+        <v>49.29</v>
       </c>
       <c r="BV4" s="13">
-        <v>3534.75</v>
+        <v>3850.17</v>
       </c>
       <c r="BW4" s="13">
         <f>BX4-BV4</f>
-        <v>76.7600000000002</v>
+        <v>124.53</v>
       </c>
       <c r="BX4" s="13">
-        <v>3611.51</v>
+        <v>3974.7</v>
       </c>
       <c r="BY4" s="13">
         <f>BZ4-BX4</f>
-        <v>39.77</v>
+        <v>10.3200000000002</v>
       </c>
       <c r="BZ4" s="13">
-        <v>3651.28</v>
+        <v>3985.02</v>
       </c>
       <c r="CA4" s="13">
         <f>CB4-BZ4</f>
-        <v>37.25</v>
+        <v>123.75</v>
       </c>
       <c r="CB4" s="13">
-        <v>3688.53</v>
+        <v>4108.77</v>
       </c>
       <c r="CC4" s="13">
         <f>CD4-CB4</f>
-        <v>79.0899999999997</v>
+        <v>30.1999999999998</v>
       </c>
       <c r="CD4" s="13">
-        <v>3767.62</v>
+        <v>4138.97</v>
       </c>
       <c r="CE4" s="13">
         <f>CF4-CD4</f>
-        <v>46.3600000000001</v>
+        <v>28.96</v>
       </c>
       <c r="CF4" s="13">
-        <v>3813.98</v>
+        <v>4167.93</v>
       </c>
       <c r="CG4" s="13">
         <f>CH4-CF4</f>
-        <v>88.1300000000001</v>
+        <v>87.5099999999993</v>
       </c>
       <c r="CH4" s="13">
-        <v>3902.11</v>
+        <v>4255.44</v>
       </c>
       <c r="CI4" s="13">
         <f>CJ4-CH4</f>
-        <v>53.0799999999999</v>
+        <v>49.25</v>
       </c>
       <c r="CJ4" s="13">
-        <v>3955.19</v>
+        <v>4304.69</v>
       </c>
       <c r="CK4" s="13">
         <f>CL4-CJ4</f>
-        <v>53.9200000000001</v>
+        <v>26.9800000000005</v>
       </c>
       <c r="CL4" s="13">
-        <v>4009.11</v>
+        <v>4331.67</v>
       </c>
       <c r="CM4" s="13">
         <f>CN4-CL4</f>
-        <v>50.3099999999999</v>
+        <v>20.75</v>
       </c>
       <c r="CN4" s="13">
-        <v>4059.42</v>
+        <v>4352.42</v>
       </c>
       <c r="CO4" s="13">
         <f>CP4-CN4</f>
-        <v>66.9799999999996</v>
+        <v>33.1000000000004</v>
       </c>
       <c r="CP4" s="13">
-        <v>4126.4</v>
+        <v>4385.52</v>
       </c>
       <c r="CQ4" s="13">
         <f>CR4-CP4</f>
-        <v>45.1900000000005</v>
+        <v>26.3599999999997</v>
       </c>
       <c r="CR4" s="13">
-        <v>4171.59</v>
+        <v>4411.88</v>
       </c>
       <c r="CS4" s="13">
         <f>CT4-CR4</f>
-        <v>130.22</v>
+        <v>60.2299999999996</v>
       </c>
       <c r="CT4" s="13">
-        <v>4301.81</v>
+        <v>4472.11</v>
       </c>
       <c r="CU4" s="13">
         <f>CV4-CT4</f>
-        <v>63.2299999999996</v>
+        <v>69.3200000000006</v>
       </c>
       <c r="CV4" s="13">
-        <v>4365.04</v>
+        <v>4541.43</v>
       </c>
       <c r="CW4" s="12">
         <f>CX4-CV4</f>
-        <v>53.1999999999998</v>
+        <v>175.25</v>
       </c>
       <c r="CX4" s="13">
-        <v>4418.24</v>
+        <v>4716.68</v>
       </c>
       <c r="CY4" s="13">
         <f>CZ4-CX4</f>
-        <v>74.3299999999999</v>
+        <v>17.4899999999998</v>
       </c>
       <c r="CZ4" s="13">
-        <v>4492.57</v>
+        <v>4734.17</v>
       </c>
       <c r="DA4" s="13">
         <f>DB4-CZ4</f>
-        <v>46.0799999999999</v>
+        <v>69.4399999999996</v>
       </c>
       <c r="DB4" s="13">
-        <v>4538.65</v>
+        <v>4803.61</v>
       </c>
       <c r="DC4" s="13">
         <f>DD4-DB4</f>
-        <v>50.4400000000005</v>
+        <v>67.0100000000002</v>
       </c>
       <c r="DD4" s="13">
-        <v>4589.09</v>
+        <v>4870.62</v>
       </c>
       <c r="DE4" s="13">
         <f>DF4-DD4</f>
-        <v>70.5599999999995</v>
+        <v>56.1800000000003</v>
       </c>
       <c r="DF4" s="13">
-        <v>4659.65</v>
+        <v>4926.8</v>
       </c>
       <c r="DG4" s="13">
         <f>DH4-DF4</f>
-        <v>16.54</v>
+        <v>-16.1300000000001</v>
       </c>
       <c r="DH4" s="13">
-        <v>4676.19</v>
+        <v>4910.67</v>
       </c>
       <c r="DI4" s="13">
         <f>DJ4-DH4</f>
-        <v>51.5700000000006</v>
+        <v>74.96</v>
       </c>
       <c r="DJ4" s="13">
-        <v>4727.76</v>
+        <v>4985.63</v>
       </c>
       <c r="DK4" s="13">
         <f>DL4-DJ4</f>
-        <v>39.5799999999999</v>
+        <v>89.8999999999996</v>
       </c>
       <c r="DL4" s="13">
-        <v>4767.34</v>
+        <v>5075.53</v>
       </c>
       <c r="DM4" s="13">
         <f>DN4-DL4</f>
-        <v>65.6099999999997</v>
+        <v>74.7600000000002</v>
       </c>
       <c r="DN4" s="13">
-        <v>4832.95</v>
+        <v>5150.29</v>
       </c>
       <c r="DO4" s="12">
         <f>DP4-DN4</f>
-        <v>100.79</v>
+        <v>17.6400000000003</v>
       </c>
       <c r="DP4" s="13">
-        <v>4933.74</v>
+        <v>5167.93</v>
       </c>
       <c r="DQ4" s="13">
         <f>DR4-DP4</f>
-        <v>51.6400000000003</v>
+        <v>45.4099999999999</v>
       </c>
       <c r="DR4" s="13">
-        <v>4985.38</v>
+        <v>5213.34</v>
       </c>
       <c r="DS4" s="13">
         <f>DT4-DR4</f>
-        <v>73.29</v>
+        <v>69.7299999999996</v>
       </c>
       <c r="DT4" s="13">
-        <v>5058.67</v>
+        <v>5283.07</v>
       </c>
       <c r="DU4" s="13">
         <f>DV4-DT4</f>
-        <v>132.03</v>
+        <v>49.1000000000004</v>
       </c>
       <c r="DV4" s="13">
-        <v>5190.7</v>
+        <v>5332.17</v>
       </c>
       <c r="DW4" s="13">
         <f>DX4-DV4</f>
-        <v>38.6500000000005</v>
+        <v>44.9200000000001</v>
       </c>
       <c r="DX4" s="13">
-        <v>5229.35</v>
+        <v>5377.09</v>
       </c>
       <c r="DY4" s="13">
         <f>DZ4-DX4</f>
-        <v>59.46</v>
+        <v>95.6099999999997</v>
       </c>
       <c r="DZ4" s="13">
-        <v>5288.81</v>
+        <v>5472.7</v>
       </c>
       <c r="EA4" s="13">
         <f>EB4-DZ4</f>
-        <v>26.2799999999997</v>
+        <v>75.0600000000004</v>
       </c>
       <c r="EB4" s="13">
-        <v>5315.09</v>
+        <v>5547.76</v>
       </c>
       <c r="EC4" s="13">
         <f>ED4-EB4</f>
-        <v>54.79</v>
+        <v>98.9099999999999</v>
       </c>
       <c r="ED4" s="13">
-        <v>5369.88</v>
+        <v>5646.67</v>
       </c>
       <c r="EE4" s="13">
         <f>EF4-ED4</f>
-        <v>52.5900000000001</v>
+        <v>-85.6800000000003</v>
       </c>
       <c r="EF4" s="13">
-        <v>5422.47</v>
+        <v>5560.99</v>
       </c>
       <c r="EG4" s="13">
         <f>EH4-EF4</f>
-        <v>44.5</v>
+        <v>152.59</v>
       </c>
       <c r="EH4" s="13">
-        <v>5466.97</v>
+        <v>5713.58</v>
       </c>
       <c r="EI4" s="13">
         <f>EJ4-EH4</f>
-        <v>51.71</v>
+        <v>71.1000000000004</v>
       </c>
       <c r="EJ4" s="13">
-        <v>5518.68</v>
+        <v>5784.68</v>
       </c>
       <c r="EK4" s="13">
         <f>EL4-EJ4</f>
-        <v>77.1700000000001</v>
+        <v>0</v>
       </c>
       <c r="EL4" s="13">
-        <v>5595.85</v>
+        <v>5784.68</v>
       </c>
       <c r="EM4" s="13">
         <f>EN4-EL4</f>
         <v>0</v>
       </c>
       <c r="EN4" s="13">
-        <v>5595.85</v>
+        <v>5784.68</v>
       </c>
       <c r="EO4" s="13">
         <f>EP4-EN4</f>
-        <v>42.1399999999994</v>
+        <v>0</v>
       </c>
       <c r="EP4" s="13">
-        <v>5637.99</v>
+        <v>5784.68</v>
       </c>
       <c r="EQ4" s="13">
         <f>ER4-EP4</f>
-        <v>39.9000000000005</v>
+        <v>130.08</v>
       </c>
       <c r="ER4" s="13">
-        <v>5677.89</v>
+        <v>5914.76</v>
       </c>
       <c r="ES4" s="13">
         <f>ET4-ER4</f>
-        <v>38.4399999999996</v>
+        <v>-18.8100000000004</v>
       </c>
       <c r="ET4" s="13">
-        <v>5716.33</v>
+        <v>5895.95</v>
       </c>
       <c r="EU4" s="13">
         <f>EV4-ET4</f>
-        <v>31.5900000000001</v>
+        <v>121.04</v>
       </c>
       <c r="EV4" s="13">
-        <v>5747.92</v>
+        <v>6016.99</v>
       </c>
       <c r="EW4" s="13">
         <f>EX4-EV4</f>
-        <v>20.1599999999999</v>
+        <v>19.5300000000007</v>
       </c>
       <c r="EX4" s="13">
-        <v>5768.08</v>
+        <v>6036.52</v>
       </c>
       <c r="EY4" s="13">
         <f>EZ4-EX4</f>
-        <v>42.7600000000002</v>
+        <v>-52.0100000000002</v>
       </c>
       <c r="EZ4" s="13">
-        <v>5810.84</v>
+        <v>5984.51</v>
       </c>
       <c r="FA4" s="13">
         <f>FB4-EZ4</f>
-        <v>52.1599999999999</v>
+        <v>45.0100000000002</v>
       </c>
       <c r="FB4" s="13">
-        <v>5863</v>
+        <v>6029.52</v>
       </c>
       <c r="FC4" s="13">
         <f>FD4-FB4</f>
-        <v>64.79</v>
+        <v>-65.2300000000005</v>
       </c>
       <c r="FD4" s="13">
-        <v>5927.79</v>
+        <v>5964.29</v>
       </c>
       <c r="FE4" s="13">
         <f>FF4-FD4</f>
-        <v>24.6800000000003</v>
+        <v>62.3500000000004</v>
       </c>
       <c r="FF4" s="13">
-        <v>5952.47</v>
+        <v>6026.64</v>
       </c>
       <c r="FG4" s="13">
         <f>FH4-FF4</f>
-        <v>91.2599999999993</v>
+        <v>40.9399999999996</v>
       </c>
       <c r="FH4" s="12">
-        <v>6043.73</v>
+        <v>6067.58</v>
       </c>
       <c r="FI4" s="13">
         <f>FJ4-FH4</f>
-        <v>61.6700000000001</v>
+        <v>41.9200000000001</v>
       </c>
       <c r="FJ4" s="13">
-        <v>6105.4</v>
-      </c>
-      <c r="FK4" s="12" t="s">
-        <v>109</v>
-      </c>
-      <c r="FL4" s="11">
-        <v>2159.32</v>
-      </c>
-      <c r="FM4" s="11" t="s">
+        <v>6109.5</v>
+      </c>
+      <c r="FK4" s="13">
+        <f>FL4-FJ4</f>
+        <v>31.3800000000001</v>
+      </c>
+      <c r="FL4" s="12">
+        <v>6140.88</v>
+      </c>
+      <c r="FM4" s="12" t="s">
         <v>110</v>
       </c>
       <c r="FN4" s="11">
-        <v>754.67</v>
-      </c>
-      <c r="FO4" s="1">
-        <v>50</v>
-      </c>
-      <c r="FP4" s="1">
-        <v>1.3</v>
+        <v>2256.07</v>
+      </c>
+      <c r="FO4" s="11" t="s">
+        <v>111</v>
+      </c>
+      <c r="FP4" s="11">
+        <v>1211.82</v>
       </c>
       <c r="FQ4" s="1">
-        <v>124763</v>
-      </c>
-      <c r="FR4" s="11">
-        <f>2.3635/(FJ4/FL4)</f>
-        <v>0.835908019130606</v>
-      </c>
-      <c r="FS4" s="11">
+        <v>20</v>
+      </c>
+      <c r="FR4" s="1">
+        <v>1.2</v>
+      </c>
+      <c r="FS4" s="1">
+        <v>153852</v>
+      </c>
+      <c r="FT4" s="11">
+        <f>2.3635/(FL4/FN4)</f>
+        <v>0.868315525624992</v>
+      </c>
+      <c r="FU4" s="11">
         <f>BP4-D4</f>
-        <v>1654.23</v>
-      </c>
-      <c r="FT4" s="11">
-        <f>FJ4-FB4</f>
-        <v>242.4</v>
+        <v>1584.75</v>
+      </c>
+      <c r="FV4" s="11">
+        <f>FL4-FD4</f>
+        <v>176.59</v>
       </c>
     </row>
-    <row r="5" spans="1:185">
+    <row r="5" spans="1:187">
       <c r="A5" s="2" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="D5" s="2">
         <v>1425.22</v>
@@ -4791,52 +4824,59 @@
       <c r="FJ5" s="17">
         <v>5125.69</v>
       </c>
-      <c r="FK5" s="16" t="s">
-        <v>112</v>
-      </c>
-      <c r="FL5" s="15">
-        <v>1357.57</v>
-      </c>
-      <c r="FM5" s="15" t="s">
-        <v>112</v>
+      <c r="FK5" s="17">
+        <f>FL5-FJ5</f>
+        <v>15.25</v>
+      </c>
+      <c r="FL5" s="16">
+        <v>5140.94</v>
+      </c>
+      <c r="FM5" s="16" t="s">
+        <v>113</v>
       </c>
       <c r="FN5" s="15">
+        <v>1368.72</v>
+      </c>
+      <c r="FO5" s="15" t="s">
+        <v>113</v>
+      </c>
+      <c r="FP5" s="15">
         <v>748.71</v>
       </c>
-      <c r="FO5" s="2">
+      <c r="FQ5" s="2">
         <v>20</v>
       </c>
-      <c r="FP5" s="2">
+      <c r="FR5" s="2">
         <v>1.1</v>
       </c>
-      <c r="FQ5" s="2">
+      <c r="FS5" s="2">
         <v>106867</v>
       </c>
-      <c r="FR5" s="15">
-        <f>2.3635/(FJ5/FL5)</f>
-        <v>0.625987270982053</v>
-      </c>
-      <c r="FS5" s="15">
+      <c r="FT5" s="15">
+        <f>2.3635/(FL5/FN5)</f>
+        <v>0.629256462825865</v>
+      </c>
+      <c r="FU5" s="15">
         <f>BP5-D5</f>
         <v>1715.51</v>
       </c>
-      <c r="FT5" s="15">
-        <f>FJ5-FB5</f>
-        <v>64.75</v>
-      </c>
-      <c r="GC5">
+      <c r="FV5" s="15">
+        <f>FL5-FD5</f>
+        <v>68.4499999999998</v>
+      </c>
+      <c r="GE5">
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:185">
+    <row r="6" spans="1:187">
       <c r="A6" s="2" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="D6" s="2">
         <v>1349.35</v>
@@ -5408,49 +5448,56 @@
       <c r="FJ6" s="17">
         <v>4964.73</v>
       </c>
-      <c r="FK6" s="16" t="s">
-        <v>114</v>
-      </c>
-      <c r="FL6" s="15">
-        <v>1045.9</v>
-      </c>
-      <c r="FM6" s="15" t="s">
-        <v>112</v>
+      <c r="FK6" s="17">
+        <f>FL6-FJ6</f>
+        <v>14.2200000000003</v>
+      </c>
+      <c r="FL6" s="16">
+        <v>4978.95</v>
+      </c>
+      <c r="FM6" s="16" t="s">
+        <v>115</v>
       </c>
       <c r="FN6" s="15">
+        <v>1626.92</v>
+      </c>
+      <c r="FO6" s="15" t="s">
+        <v>113</v>
+      </c>
+      <c r="FP6" s="15">
         <v>645.48</v>
       </c>
-      <c r="FO6" s="2">
+      <c r="FQ6" s="2">
         <v>20</v>
       </c>
-      <c r="FP6" s="2">
+      <c r="FR6" s="2">
         <v>3.2</v>
       </c>
-      <c r="FQ6" s="2">
+      <c r="FS6" s="2">
         <v>109106</v>
       </c>
-      <c r="FR6" s="15">
-        <f>2.3635/(FJ6/FL6)</f>
-        <v>0.497909181365351</v>
-      </c>
-      <c r="FS6" s="15">
+      <c r="FT6" s="15">
+        <f>2.3635/(FL6/FN6)</f>
+        <v>0.772296452063186</v>
+      </c>
+      <c r="FU6" s="15">
         <f>BP6-D6</f>
         <v>1368.34</v>
       </c>
-      <c r="FT6" s="15">
-        <f>FJ6-FB6</f>
-        <v>73.9599999999991</v>
+      <c r="FV6" s="15">
+        <f>FL6-FD6</f>
+        <v>68.0199999999995</v>
       </c>
     </row>
-    <row r="7" spans="1:185">
+    <row r="7" spans="1:187">
       <c r="A7" s="3" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="D7" s="3">
         <v>848.93</v>
@@ -6022,49 +6069,56 @@
       <c r="FJ7" s="21">
         <v>2800.28</v>
       </c>
-      <c r="FK7" s="20" t="s">
-        <v>109</v>
-      </c>
-      <c r="FL7" s="19">
-        <v>1219.67</v>
-      </c>
-      <c r="FM7" s="19" t="s">
-        <v>110</v>
+      <c r="FK7" s="21">
+        <f>FL7-FJ7</f>
+        <v>1.42999999999984</v>
+      </c>
+      <c r="FL7" s="20">
+        <v>2801.71</v>
+      </c>
+      <c r="FM7" s="20" t="s">
+        <v>106</v>
       </c>
       <c r="FN7" s="19">
+        <v>1244.17</v>
+      </c>
+      <c r="FO7" s="19" t="s">
+        <v>107</v>
+      </c>
+      <c r="FP7" s="19">
         <v>556.77</v>
       </c>
-      <c r="FO7" s="3">
+      <c r="FQ7" s="3">
         <v>30</v>
       </c>
-      <c r="FP7" s="3">
+      <c r="FR7" s="3">
         <v>3.2</v>
       </c>
-      <c r="FQ7" s="3">
+      <c r="FS7" s="3">
         <v>78989</v>
       </c>
-      <c r="FR7" s="19">
-        <f>2.3635/(FJ7/FL7)</f>
-        <v>1.02942921600697</v>
-      </c>
-      <c r="FS7" s="19">
+      <c r="FT7" s="19">
+        <f>2.3635/(FL7/FN7)</f>
+        <v>1.04957179543921</v>
+      </c>
+      <c r="FU7" s="19">
         <f>BP7-D7</f>
         <v>967.13</v>
       </c>
-      <c r="FT7" s="19">
-        <f>FJ7-FB7</f>
-        <v>29.8900000000003</v>
+      <c r="FV7" s="19">
+        <f>FL7-FD7</f>
+        <v>28.4400000000001</v>
       </c>
     </row>
-    <row r="8" spans="1:185">
+    <row r="8" spans="1:187">
       <c r="A8" s="5" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="D8" s="5">
         <v>4105.48</v>
@@ -6636,49 +6690,56 @@
       <c r="FJ8" s="24">
         <v>12768.67</v>
       </c>
-      <c r="FK8" s="23" t="s">
-        <v>119</v>
-      </c>
-      <c r="FL8" s="9">
-        <v>3168.42</v>
-      </c>
-      <c r="FM8" s="9" t="s">
+      <c r="FK8" s="24">
+        <f>FL8-FJ8</f>
+        <v>20.6599999999999</v>
+      </c>
+      <c r="FL8" s="23">
+        <v>12789.33</v>
+      </c>
+      <c r="FM8" s="23" t="s">
         <v>120</v>
       </c>
       <c r="FN8" s="9">
+        <v>3162.42</v>
+      </c>
+      <c r="FO8" s="9" t="s">
+        <v>121</v>
+      </c>
+      <c r="FP8" s="9">
         <v>1267.77</v>
       </c>
-      <c r="FO8" s="5">
+      <c r="FQ8" s="5">
         <v>400</v>
       </c>
-      <c r="FP8" s="5">
+      <c r="FR8" s="5">
         <v>1.2</v>
       </c>
-      <c r="FQ8" s="5">
+      <c r="FS8" s="5">
         <v>186759</v>
       </c>
-      <c r="FR8" s="9">
-        <f>2.3635/(FJ8/FL8)</f>
-        <v>0.586479302072965</v>
-      </c>
-      <c r="FS8" s="9">
+      <c r="FT8" s="9">
+        <f>2.3635/(FL8/FN8)</f>
+        <v>0.584423083148218</v>
+      </c>
+      <c r="FU8" s="9">
         <f>BP8-D8</f>
         <v>2684.95</v>
       </c>
-      <c r="FT8" s="9">
-        <f>FJ8-FB8</f>
-        <v>654.969999999999</v>
+      <c r="FV8" s="9">
+        <f>FL8-FD8</f>
+        <v>630.780000000001</v>
       </c>
     </row>
-    <row r="9" spans="1:185">
+    <row r="9" spans="1:187">
       <c r="A9" s="8" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C9" s="8" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="D9" s="8"/>
       <c r="E9" s="8"/>
@@ -7150,43 +7211,50 @@
       <c r="FJ9" s="28">
         <v>3869.14</v>
       </c>
-      <c r="FK9" s="27" t="s">
-        <v>123</v>
-      </c>
-      <c r="FL9" s="26">
-        <v>915.62</v>
-      </c>
-      <c r="FM9" s="26" t="s">
-        <v>112</v>
+      <c r="FK9" s="28">
+        <f>FL9-FJ9</f>
+        <v>22.5</v>
+      </c>
+      <c r="FL9" s="27">
+        <v>3891.64</v>
+      </c>
+      <c r="FM9" s="27" t="s">
+        <v>124</v>
       </c>
       <c r="FN9" s="26">
+        <v>916.62</v>
+      </c>
+      <c r="FO9" s="26" t="s">
+        <v>113</v>
+      </c>
+      <c r="FP9" s="26">
         <v>490.62</v>
       </c>
-      <c r="FO9" s="8"/>
-      <c r="FP9" s="8"/>
       <c r="FQ9" s="8"/>
-      <c r="FR9" s="26">
-        <f>2.3635/(FJ9/FL9)</f>
-        <v>0.559314956295197</v>
-      </c>
-      <c r="FS9" s="26">
+      <c r="FR9" s="8"/>
+      <c r="FS9" s="8"/>
+      <c r="FT9" s="26">
+        <f>2.3635/(FL9/FN9)</f>
+        <v>0.556688534910732</v>
+      </c>
+      <c r="FU9" s="26">
         <f>BP9-D9</f>
         <v>2634.73</v>
       </c>
-      <c r="FT9" s="26">
-        <f>FJ9-FB9</f>
-        <v>107.09</v>
+      <c r="FV9" s="26">
+        <f>FL9-FD9</f>
+        <v>109.51</v>
       </c>
     </row>
-    <row r="10" spans="1:185">
+    <row r="10" spans="1:187">
       <c r="A10" s="5" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="D10" s="5">
         <v>2714.1</v>
@@ -7758,49 +7826,56 @@
       <c r="FJ10" s="24">
         <v>10051.79</v>
       </c>
-      <c r="FK10" s="23" t="s">
-        <v>126</v>
-      </c>
-      <c r="FL10" s="9">
-        <v>2738.92</v>
-      </c>
-      <c r="FM10" s="9" t="s">
+      <c r="FK10" s="24">
+        <f>FL10-FJ10</f>
+        <v>42.1999999999989</v>
+      </c>
+      <c r="FL10" s="23">
+        <v>10093.99</v>
+      </c>
+      <c r="FM10" s="23" t="s">
         <v>127</v>
       </c>
       <c r="FN10" s="9">
+        <v>2764.72</v>
+      </c>
+      <c r="FO10" s="9" t="s">
+        <v>128</v>
+      </c>
+      <c r="FP10" s="9">
         <v>1327.12</v>
       </c>
-      <c r="FO10" s="5">
+      <c r="FQ10" s="5">
         <v>500</v>
       </c>
-      <c r="FP10" s="5">
+      <c r="FR10" s="5">
         <v>8.6</v>
       </c>
-      <c r="FQ10" s="5">
+      <c r="FS10" s="5">
         <v>191519</v>
       </c>
-      <c r="FR10" s="9">
-        <f>2.3635/(FJ10/FL10)</f>
-        <v>0.644008422380491</v>
-      </c>
-      <c r="FS10" s="9">
+      <c r="FT10" s="9">
+        <f>2.3635/(FL10/FN10)</f>
+        <v>0.64735706296519</v>
+      </c>
+      <c r="FU10" s="9">
         <f>BP10-D10</f>
         <v>3022.78</v>
       </c>
-      <c r="FT10" s="9">
-        <f>FJ10-FB10</f>
-        <v>478.26</v>
+      <c r="FV10" s="9">
+        <f>FL10-FD10</f>
+        <v>416.129999999999</v>
       </c>
     </row>
-    <row r="11" spans="1:185">
+    <row r="11" spans="1:187">
       <c r="A11" s="1" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="D11" s="1">
         <v>1350.52</v>
@@ -8372,49 +8447,56 @@
       <c r="FJ11" s="13">
         <v>6836.58</v>
       </c>
-      <c r="FK11" s="12" t="s">
-        <v>109</v>
-      </c>
-      <c r="FL11" s="11">
-        <v>2183.87</v>
-      </c>
-      <c r="FM11" s="11" t="s">
-        <v>110</v>
+      <c r="FK11" s="13">
+        <f>FL11-FJ11</f>
+        <v>38.6499999999996</v>
+      </c>
+      <c r="FL11" s="12">
+        <v>6875.23</v>
+      </c>
+      <c r="FM11" s="12" t="s">
+        <v>106</v>
       </c>
       <c r="FN11" s="11">
+        <v>2167.47</v>
+      </c>
+      <c r="FO11" s="11" t="s">
+        <v>107</v>
+      </c>
+      <c r="FP11" s="11">
         <v>896.02</v>
       </c>
-      <c r="FO11" s="1">
+      <c r="FQ11" s="1">
         <v>65</v>
       </c>
-      <c r="FP11" s="1">
+      <c r="FR11" s="1">
         <v>1.4</v>
       </c>
-      <c r="FQ11" s="1">
+      <c r="FS11" s="1">
         <v>127603</v>
       </c>
-      <c r="FR11" s="11">
-        <f>2.3635/(FJ11/FL11)</f>
-        <v>0.754993980177223</v>
-      </c>
-      <c r="FS11" s="11">
+      <c r="FT11" s="11">
+        <f>2.3635/(FL11/FN11)</f>
+        <v>0.745111850076288</v>
+      </c>
+      <c r="FU11" s="11">
         <f>BP11-D11</f>
         <v>2104.56</v>
       </c>
-      <c r="FT11" s="11">
-        <f>FJ11-FB11</f>
-        <v>298.36</v>
+      <c r="FV11" s="11">
+        <f>FL11-FD11</f>
+        <v>184.179999999999</v>
       </c>
     </row>
-    <row r="12" spans="1:185">
+    <row r="12" spans="1:187">
       <c r="A12" s="2" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="D12" s="2">
         <v>1156.57</v>
@@ -8986,49 +9068,56 @@
       <c r="FJ12" s="17">
         <v>5203.49</v>
       </c>
-      <c r="FK12" s="16" t="s">
-        <v>131</v>
-      </c>
-      <c r="FL12" s="15">
-        <v>1638.08</v>
-      </c>
-      <c r="FM12" s="15" t="s">
-        <v>101</v>
+      <c r="FK12" s="17">
+        <f>FL12-FJ12</f>
+        <v>49.8600000000006</v>
+      </c>
+      <c r="FL12" s="16">
+        <v>5253.35</v>
+      </c>
+      <c r="FM12" s="16" t="s">
+        <v>132</v>
       </c>
       <c r="FN12" s="15">
+        <v>1652.58</v>
+      </c>
+      <c r="FO12" s="15" t="s">
+        <v>102</v>
+      </c>
+      <c r="FP12" s="15">
         <v>614.12</v>
       </c>
-      <c r="FO12" s="2">
+      <c r="FQ12" s="2">
         <v>25</v>
       </c>
-      <c r="FP12" s="2">
+      <c r="FR12" s="2">
         <v>3</v>
       </c>
-      <c r="FQ12" s="2">
+      <c r="FS12" s="2">
         <v>100457</v>
       </c>
-      <c r="FR12" s="15">
-        <f>2.3635/(FJ12/FL12)</f>
-        <v>0.744039496568649</v>
-      </c>
-      <c r="FS12" s="15">
+      <c r="FT12" s="15">
+        <f>2.3635/(FL12/FN12)</f>
+        <v>0.743501352470328</v>
+      </c>
+      <c r="FU12" s="15">
         <f>BP12-D12</f>
         <v>1572.99</v>
       </c>
-      <c r="FT12" s="15">
-        <f>FJ12-FB12</f>
-        <v>213.5</v>
+      <c r="FV12" s="15">
+        <f>FL12-FD12</f>
+        <v>237.79</v>
       </c>
     </row>
-    <row r="13" spans="1:185">
+    <row r="13" spans="1:187">
       <c r="A13" s="2" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="D13" s="2">
         <v>907.94</v>
@@ -9600,49 +9689,56 @@
       <c r="FJ13" s="17">
         <v>4648.5</v>
       </c>
-      <c r="FK13" s="16" t="s">
-        <v>133</v>
-      </c>
-      <c r="FL13" s="15">
-        <v>1360.38</v>
-      </c>
-      <c r="FM13" s="15" t="s">
-        <v>133</v>
+      <c r="FK13" s="17">
+        <f>FL13-FJ13</f>
+        <v>50.0799999999999</v>
+      </c>
+      <c r="FL13" s="16">
+        <v>4698.58</v>
+      </c>
+      <c r="FM13" s="16" t="s">
+        <v>134</v>
       </c>
       <c r="FN13" s="15">
+        <v>1586.92</v>
+      </c>
+      <c r="FO13" s="15" t="s">
+        <v>135</v>
+      </c>
+      <c r="FP13" s="15">
         <v>628.67</v>
       </c>
-      <c r="FO13" s="2">
+      <c r="FQ13" s="2">
         <v>35</v>
       </c>
-      <c r="FP13" s="2">
+      <c r="FR13" s="2">
         <v>8.2</v>
       </c>
-      <c r="FQ13" s="2">
+      <c r="FS13" s="2">
         <v>65285</v>
       </c>
-      <c r="FR13" s="15">
-        <f>2.3635/(FJ13/FL13)</f>
-        <v>0.691676482736367</v>
-      </c>
-      <c r="FS13" s="15">
+      <c r="FT13" s="15">
+        <f>2.3635/(FL13/FN13)</f>
+        <v>0.798259350697445</v>
+      </c>
+      <c r="FU13" s="15">
         <f>BP13-D13</f>
         <v>1361.61</v>
       </c>
-      <c r="FT13" s="15">
-        <f>FJ13-FB13</f>
-        <v>177.52</v>
+      <c r="FV13" s="15">
+        <f>FL13-FD13</f>
+        <v>190.63</v>
       </c>
     </row>
-    <row r="14" spans="1:185">
+    <row r="14" spans="1:187">
       <c r="A14" s="8" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="C14" s="8" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="D14" s="8"/>
       <c r="E14" s="8"/>
@@ -9939,36 +10035,43 @@
       <c r="FJ14" s="28">
         <v>3276.86</v>
       </c>
-      <c r="FK14" s="27" t="s">
-        <v>101</v>
-      </c>
-      <c r="FL14" s="26">
+      <c r="FK14" s="28">
+        <f>FL14-FJ14</f>
+        <v>0</v>
+      </c>
+      <c r="FL14" s="27">
+        <v>3276.86</v>
+      </c>
+      <c r="FM14" s="27" t="s">
+        <v>102</v>
+      </c>
+      <c r="FN14" s="26">
         <v>636.58</v>
       </c>
-      <c r="FM14" s="26"/>
-      <c r="FN14" s="26"/>
-      <c r="FO14" s="8"/>
-      <c r="FP14" s="8"/>
+      <c r="FO14" s="26"/>
+      <c r="FP14" s="26"/>
       <c r="FQ14" s="8"/>
-      <c r="FR14" s="26">
-        <f>2.3635/(FJ14/FL14)</f>
+      <c r="FR14" s="8"/>
+      <c r="FS14" s="8"/>
+      <c r="FT14" s="26">
+        <f>2.3635/(FL14/FN14)</f>
         <v>0.459145898817771</v>
       </c>
-      <c r="FS14" s="26"/>
-      <c r="FT14" s="26">
-        <f>FJ14-FB14</f>
-        <v>78.6900000000001</v>
+      <c r="FU14" s="26"/>
+      <c r="FV14" s="26">
+        <f>FL14-FD14</f>
+        <v>53.8700000000003</v>
       </c>
     </row>
-    <row r="15" spans="1:185">
+    <row r="15" spans="1:187">
       <c r="A15" s="3" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="D15" s="3">
         <v>363.88</v>
@@ -10540,49 +10643,56 @@
       <c r="FJ15" s="21">
         <v>2569.53</v>
       </c>
-      <c r="FK15" s="20" t="s">
-        <v>123</v>
-      </c>
-      <c r="FL15" s="19">
-        <v>815.06</v>
-      </c>
-      <c r="FM15" s="19" t="s">
-        <v>123</v>
+      <c r="FK15" s="21">
+        <f>FL15-FJ15</f>
+        <v>28.2599999999998</v>
+      </c>
+      <c r="FL15" s="20">
+        <v>2597.79</v>
+      </c>
+      <c r="FM15" s="20" t="s">
+        <v>124</v>
       </c>
       <c r="FN15" s="19">
+        <v>779.27</v>
+      </c>
+      <c r="FO15" s="19" t="s">
+        <v>124</v>
+      </c>
+      <c r="FP15" s="19">
         <v>368.34</v>
       </c>
-      <c r="FO15" s="3">
+      <c r="FQ15" s="3">
         <v>0</v>
       </c>
-      <c r="FP15" s="3">
+      <c r="FR15" s="3">
         <v>1</v>
       </c>
-      <c r="FQ15" s="3">
+      <c r="FS15" s="3">
         <v>47256</v>
       </c>
-      <c r="FR15" s="19">
-        <f>2.3635/(FJ15/FL15)</f>
-        <v>0.74970687635482</v>
-      </c>
-      <c r="FS15" s="19">
+      <c r="FT15" s="19">
+        <f>2.3635/(FL15/FN15)</f>
+        <v>0.708989042609295</v>
+      </c>
+      <c r="FU15" s="19">
         <f>BP15-D15</f>
         <v>790.52</v>
       </c>
-      <c r="FT15" s="19">
-        <f>FJ15-FB15</f>
-        <v>248.87</v>
+      <c r="FV15" s="19">
+        <f>FL15-FD15</f>
+        <v>174.95</v>
       </c>
     </row>
-    <row r="16" spans="1:185">
+    <row r="16" spans="1:187">
       <c r="A16" s="3" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B16" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="C16" s="3" t="s">
         <v>137</v>
-      </c>
-      <c r="C16" s="3" t="s">
-        <v>135</v>
       </c>
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
@@ -11054,43 +11164,50 @@
       <c r="FJ16" s="21">
         <v>2012.17</v>
       </c>
-      <c r="FK16" s="20" t="s">
-        <v>138</v>
-      </c>
-      <c r="FL16" s="19">
-        <v>507.09</v>
-      </c>
-      <c r="FM16" s="19" t="s">
-        <v>139</v>
+      <c r="FK16" s="21">
+        <f>FL16-FJ16</f>
+        <v>32.3</v>
+      </c>
+      <c r="FL16" s="20">
+        <v>2044.47</v>
+      </c>
+      <c r="FM16" s="20" t="s">
+        <v>140</v>
       </c>
       <c r="FN16" s="19">
+        <v>521.46</v>
+      </c>
+      <c r="FO16" s="19" t="s">
+        <v>141</v>
+      </c>
+      <c r="FP16" s="19">
         <v>148.34</v>
       </c>
-      <c r="FO16" s="3"/>
-      <c r="FP16" s="3"/>
       <c r="FQ16" s="3"/>
-      <c r="FR16" s="19">
-        <f>2.3635/(FJ16/FL16)</f>
-        <v>0.595629203794908</v>
-      </c>
-      <c r="FS16" s="19">
+      <c r="FR16" s="3"/>
+      <c r="FS16" s="3"/>
+      <c r="FT16" s="19">
+        <f>2.3635/(FL16/FN16)</f>
+        <v>0.602831398846645</v>
+      </c>
+      <c r="FU16" s="19">
         <f>BP16-D16</f>
         <v>897.4</v>
       </c>
-      <c r="FT16" s="19">
-        <f>FJ16-FB16</f>
-        <v>112.67</v>
+      <c r="FV16" s="19">
+        <f>FL16-FD16</f>
+        <v>128.21</v>
       </c>
     </row>
-    <row r="17" spans="1:176">
+    <row r="17" spans="1:178">
       <c r="A17" s="5" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="D17" s="5">
         <v>2533.85</v>
@@ -11662,49 +11779,56 @@
       <c r="FJ17" s="24">
         <v>10255.05</v>
       </c>
-      <c r="FK17" s="23" t="s">
-        <v>142</v>
-      </c>
-      <c r="FL17" s="9">
+      <c r="FK17" s="24">
+        <f>FL17-FJ17</f>
+        <v>62.8000000000011</v>
+      </c>
+      <c r="FL17" s="23">
+        <v>10317.85</v>
+      </c>
+      <c r="FM17" s="23" t="s">
+        <v>144</v>
+      </c>
+      <c r="FN17" s="9">
         <v>2488.3</v>
       </c>
-      <c r="FM17" s="9" t="s">
-        <v>109</v>
-      </c>
-      <c r="FN17" s="9">
+      <c r="FO17" s="9" t="s">
+        <v>106</v>
+      </c>
+      <c r="FP17" s="9">
         <v>1010.07</v>
       </c>
-      <c r="FO17" s="5">
+      <c r="FQ17" s="5">
         <v>200</v>
       </c>
-      <c r="FP17" s="5">
+      <c r="FR17" s="5">
         <v>1.6</v>
       </c>
-      <c r="FQ17" s="5">
+      <c r="FS17" s="5">
         <v>172501</v>
       </c>
-      <c r="FR17" s="9">
-        <f>2.3635/(FJ17/FL17)</f>
-        <v>0.573483020560602</v>
-      </c>
-      <c r="FS17" s="9">
+      <c r="FT17" s="9">
+        <f>2.3635/(FL17/FN17)</f>
+        <v>0.569992493591204</v>
+      </c>
+      <c r="FU17" s="9">
         <f>BP17-D17</f>
         <v>2277.14</v>
       </c>
-      <c r="FT17" s="9">
-        <f>FJ17-FB17</f>
-        <v>531.75</v>
+      <c r="FV17" s="9">
+        <f>FL17-FD17</f>
+        <v>414.460000000001</v>
       </c>
     </row>
-    <row r="18" spans="1:176">
+    <row r="18" spans="1:178">
       <c r="A18" s="3" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="D18" s="3">
         <v>552.79</v>
@@ -12276,49 +12400,56 @@
       <c r="FJ18" s="21">
         <v>1060.27</v>
       </c>
-      <c r="FK18" s="20" t="s">
-        <v>112</v>
-      </c>
-      <c r="FL18" s="19">
-        <v>348.29</v>
-      </c>
-      <c r="FM18" s="19" t="s">
-        <v>123</v>
+      <c r="FK18" s="21">
+        <f>FL18-FJ18</f>
+        <v>4.33999999999992</v>
+      </c>
+      <c r="FL18" s="20">
+        <v>1064.61</v>
+      </c>
+      <c r="FM18" s="20" t="s">
+        <v>113</v>
       </c>
       <c r="FN18" s="19">
+        <v>348.49</v>
+      </c>
+      <c r="FO18" s="19" t="s">
+        <v>124</v>
+      </c>
+      <c r="FP18" s="19">
         <v>171.75</v>
       </c>
-      <c r="FO18" s="3">
+      <c r="FQ18" s="3">
         <v>0</v>
       </c>
-      <c r="FP18" s="3">
+      <c r="FR18" s="3">
         <v>0.5</v>
       </c>
-      <c r="FQ18" s="3">
+      <c r="FS18" s="3">
         <v>49654</v>
       </c>
-      <c r="FR18" s="19">
-        <f>2.3635/(FJ18/FL18)</f>
-        <v>0.776390367547889</v>
-      </c>
-      <c r="FS18" s="19">
+      <c r="FT18" s="19">
+        <f>2.3635/(FL18/FN18)</f>
+        <v>0.773669339006773</v>
+      </c>
+      <c r="FU18" s="19">
         <f>BP18-D18</f>
         <v>175.03</v>
       </c>
-      <c r="FT18" s="19">
-        <f>FJ18-FB18</f>
-        <v>63.9499999999999</v>
+      <c r="FV18" s="19">
+        <f>FL18-FD18</f>
+        <v>62.8799999999999</v>
       </c>
     </row>
-    <row r="19" spans="1:176">
+    <row r="19" spans="1:178">
       <c r="A19" s="8" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="B19" s="8" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="C19" s="8" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="D19" s="8">
         <v>953.78</v>
@@ -12890,49 +13021,56 @@
       <c r="FJ19" s="28">
         <v>4454.87</v>
       </c>
-      <c r="FK19" s="27" t="s">
-        <v>109</v>
-      </c>
-      <c r="FL19" s="26">
-        <v>1926.37</v>
-      </c>
-      <c r="FM19" s="26" t="s">
-        <v>110</v>
+      <c r="FK19" s="28">
+        <f>FL19-FJ19</f>
+        <v>26.1400000000003</v>
+      </c>
+      <c r="FL19" s="27">
+        <v>4481.01</v>
+      </c>
+      <c r="FM19" s="27" t="s">
+        <v>106</v>
       </c>
       <c r="FN19" s="26">
+        <v>1951.27</v>
+      </c>
+      <c r="FO19" s="26" t="s">
+        <v>107</v>
+      </c>
+      <c r="FP19" s="26">
         <v>758.25</v>
       </c>
-      <c r="FO19" s="8">
+      <c r="FQ19" s="8">
         <v>30</v>
       </c>
-      <c r="FP19" s="8">
+      <c r="FR19" s="8">
         <v>1</v>
       </c>
-      <c r="FQ19" s="8">
+      <c r="FS19" s="8">
         <v>105419</v>
       </c>
-      <c r="FR19" s="26">
-        <f>2.3635/(FJ19/FL19)</f>
-        <v>1.02202207808533</v>
-      </c>
-      <c r="FS19" s="26">
+      <c r="FT19" s="26">
+        <f>2.3635/(FL19/FN19)</f>
+        <v>1.02919356238884</v>
+      </c>
+      <c r="FU19" s="26">
         <f>BP19-D19</f>
         <v>1446.26</v>
       </c>
-      <c r="FT19" s="26">
-        <f>FJ19-FB19</f>
-        <v>136.27</v>
+      <c r="FV19" s="26">
+        <f>FL19-FD19</f>
+        <v>131.780000000001</v>
       </c>
     </row>
-    <row r="20" spans="1:176">
+    <row r="20" spans="1:178">
       <c r="A20" s="1" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="D20" s="1">
         <v>1735.94</v>
@@ -13504,49 +13642,56 @@
       <c r="FJ20" s="13">
         <v>6865</v>
       </c>
-      <c r="FK20" s="12" t="s">
-        <v>119</v>
-      </c>
-      <c r="FL20" s="11">
-        <v>2093.92</v>
-      </c>
-      <c r="FM20" s="11" t="s">
-        <v>148</v>
+      <c r="FK20" s="13">
+        <f>FL20-FJ20</f>
+        <v>25.5</v>
+      </c>
+      <c r="FL20" s="13">
+        <v>6890.5</v>
+      </c>
+      <c r="FM20" s="12" t="s">
+        <v>120</v>
       </c>
       <c r="FN20" s="11">
+        <v>2101.32</v>
+      </c>
+      <c r="FO20" s="11" t="s">
+        <v>150</v>
+      </c>
+      <c r="FP20" s="11">
         <v>824.67</v>
       </c>
-      <c r="FO20" s="1">
+      <c r="FQ20" s="1">
         <v>80</v>
       </c>
-      <c r="FP20" s="1">
+      <c r="FR20" s="1">
         <v>7.2</v>
       </c>
-      <c r="FQ20" s="1">
+      <c r="FS20" s="1">
         <v>150192</v>
       </c>
-      <c r="FR20" s="11">
-        <f>2.3635/(FJ20/FL20)</f>
-        <v>0.720900206846322</v>
-      </c>
-      <c r="FS20" s="11">
+      <c r="FT20" s="11">
+        <f>2.3635/(FL20/FN20)</f>
+        <v>0.720770600101589</v>
+      </c>
+      <c r="FU20" s="11">
         <f>BP20-D20</f>
         <v>1944.52</v>
       </c>
-      <c r="FT20" s="11">
-        <f>FJ20-FB20</f>
-        <v>337.11</v>
+      <c r="FV20" s="11">
+        <f>FL20-FD20</f>
+        <v>214.79</v>
       </c>
     </row>
-    <row r="21" spans="1:176">
+    <row r="21" spans="1:178">
       <c r="A21" s="2" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="D21" s="2">
         <v>1446.65</v>
@@ -14118,49 +14263,56 @@
       <c r="FJ21" s="17">
         <v>5705.77</v>
       </c>
-      <c r="FK21" s="16" t="s">
-        <v>109</v>
-      </c>
-      <c r="FL21" s="15">
-        <v>2414.12</v>
-      </c>
-      <c r="FM21" s="15" t="s">
-        <v>110</v>
+      <c r="FK21" s="17">
+        <f>FL21-FJ21</f>
+        <v>74.25</v>
+      </c>
+      <c r="FL21" s="16">
+        <v>5780.02</v>
+      </c>
+      <c r="FM21" s="16" t="s">
+        <v>106</v>
       </c>
       <c r="FN21" s="15">
+        <v>2437.12</v>
+      </c>
+      <c r="FO21" s="15" t="s">
+        <v>107</v>
+      </c>
+      <c r="FP21" s="15">
         <v>1048.57</v>
       </c>
-      <c r="FO21" s="2">
+      <c r="FQ21" s="2">
         <v>65</v>
       </c>
-      <c r="FP21" s="2">
+      <c r="FR21" s="2">
         <v>1.4</v>
       </c>
-      <c r="FQ21" s="2">
+      <c r="FS21" s="2">
         <v>109333</v>
       </c>
-      <c r="FR21" s="15">
-        <f>2.3635/(FJ21/FL21)</f>
-        <v>1.0000004591843</v>
-      </c>
-      <c r="FS21" s="15">
+      <c r="FT21" s="15">
+        <f>2.3635/(FL21/FN21)</f>
+        <v>0.996559375227075</v>
+      </c>
+      <c r="FU21" s="15">
         <f>BP21-D21</f>
         <v>1685.99</v>
       </c>
-      <c r="FT21" s="15">
-        <f>FJ21-FB21</f>
-        <v>265.950000000001</v>
+      <c r="FV21" s="15">
+        <f>FL21-FD21</f>
+        <v>297.830000000001</v>
       </c>
     </row>
-    <row r="22" spans="1:176">
+    <row r="22" spans="1:178">
       <c r="A22" s="8" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="B22" s="8" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="C22" s="8" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="D22" s="8"/>
       <c r="E22" s="8"/>
@@ -14632,43 +14784,50 @@
       <c r="FJ22" s="28">
         <v>4390.47</v>
       </c>
-      <c r="FK22" s="27" t="s">
-        <v>152</v>
-      </c>
-      <c r="FL22" s="26">
-        <v>1198.92</v>
-      </c>
-      <c r="FM22" s="26" t="s">
-        <v>138</v>
+      <c r="FK22" s="28">
+        <f>FL22-FJ22</f>
+        <v>24.4799999999996</v>
+      </c>
+      <c r="FL22" s="27">
+        <v>4414.95</v>
+      </c>
+      <c r="FM22" s="27" t="s">
+        <v>154</v>
       </c>
       <c r="FN22" s="26">
+        <v>1207.12</v>
+      </c>
+      <c r="FO22" s="26" t="s">
+        <v>140</v>
+      </c>
+      <c r="FP22" s="26">
         <v>304.12</v>
       </c>
-      <c r="FO22" s="8"/>
-      <c r="FP22" s="8"/>
       <c r="FQ22" s="8"/>
-      <c r="FR22" s="26">
-        <f>2.3635/(FJ22/FL22)</f>
-        <v>0.645408673786633</v>
-      </c>
-      <c r="FS22" s="26">
+      <c r="FR22" s="8"/>
+      <c r="FS22" s="8"/>
+      <c r="FT22" s="26">
+        <f>2.3635/(FL22/FN22)</f>
+        <v>0.646219803168779</v>
+      </c>
+      <c r="FU22" s="26">
         <f>BP22-D22</f>
         <v>1776.78</v>
       </c>
-      <c r="FT22" s="26">
-        <f>FJ22-FB22</f>
-        <v>268.17</v>
+      <c r="FV22" s="26">
+        <f>FL22-FD22</f>
+        <v>156.75</v>
       </c>
     </row>
-    <row r="23" spans="1:176">
+    <row r="23" spans="1:178">
       <c r="A23" s="8" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="B23" s="8" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="C23" s="8" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="D23" s="8">
         <v>950.09</v>
@@ -15240,49 +15399,56 @@
       <c r="FJ23" s="28">
         <v>4172.38</v>
       </c>
-      <c r="FK23" s="27" t="s">
-        <v>139</v>
-      </c>
-      <c r="FL23" s="26">
-        <v>1715.56</v>
-      </c>
-      <c r="FM23" s="26" t="s">
-        <v>138</v>
+      <c r="FK23" s="28">
+        <f>FL23-FJ23</f>
+        <v>81.3800000000001</v>
+      </c>
+      <c r="FL23" s="27">
+        <v>4253.76</v>
+      </c>
+      <c r="FM23" s="27" t="s">
+        <v>141</v>
       </c>
       <c r="FN23" s="26">
+        <v>1748.76</v>
+      </c>
+      <c r="FO23" s="26" t="s">
+        <v>140</v>
+      </c>
+      <c r="FP23" s="26">
         <v>704.28</v>
       </c>
-      <c r="FO23" s="8">
+      <c r="FQ23" s="8">
         <v>10</v>
       </c>
-      <c r="FP23" s="8">
+      <c r="FR23" s="8">
         <v>2.2</v>
       </c>
-      <c r="FQ23" s="8">
+      <c r="FS23" s="8">
         <v>86194</v>
       </c>
-      <c r="FR23" s="26">
-        <f>2.3635/(FJ23/FL23)</f>
-        <v>0.971801719881698</v>
-      </c>
-      <c r="FS23" s="26">
+      <c r="FT23" s="26">
+        <f>2.3635/(FL23/FN23)</f>
+        <v>0.97165666610246</v>
+      </c>
+      <c r="FU23" s="26">
         <f>BP23-D23</f>
         <v>1143.19</v>
       </c>
-      <c r="FT23" s="26">
-        <f>FJ23-FB23</f>
-        <v>137.29</v>
+      <c r="FV23" s="26">
+        <f>FL23-FD23</f>
+        <v>188.84</v>
       </c>
     </row>
-    <row r="24" spans="1:176">
+    <row r="24" spans="1:178">
       <c r="A24" s="8" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="B24" s="8" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="C24" s="8" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="D24" s="8"/>
       <c r="E24" s="8"/>
@@ -15754,40 +15920,47 @@
       <c r="FJ24" s="28">
         <v>3795.38</v>
       </c>
-      <c r="FK24" s="27" t="s">
-        <v>114</v>
-      </c>
-      <c r="FL24" s="26">
-        <v>587.61</v>
-      </c>
-      <c r="FM24" s="26" t="s">
-        <v>112</v>
+      <c r="FK24" s="28">
+        <f>FL24-FJ24</f>
+        <v>63.5299999999997</v>
+      </c>
+      <c r="FL24" s="27">
+        <v>3858.91</v>
+      </c>
+      <c r="FM24" s="27" t="s">
+        <v>134</v>
       </c>
       <c r="FN24" s="26">
+        <v>585.61</v>
+      </c>
+      <c r="FO24" s="26" t="s">
+        <v>113</v>
+      </c>
+      <c r="FP24" s="26">
         <v>303.44</v>
       </c>
-      <c r="FO24" s="8"/>
-      <c r="FP24" s="8"/>
       <c r="FQ24" s="8"/>
-      <c r="FR24" s="26">
-        <f>2.3635/(FJ24/FL24)</f>
-        <v>0.365922841718089</v>
-      </c>
-      <c r="FS24" s="26">
+      <c r="FR24" s="8"/>
+      <c r="FS24" s="8"/>
+      <c r="FT24" s="26">
+        <f>2.3635/(FL24/FN24)</f>
+        <v>0.358673624158117</v>
+      </c>
+      <c r="FU24" s="26">
         <f>BP24-D24</f>
         <v>1817.1</v>
       </c>
-      <c r="FT24" s="26">
-        <f>FJ24-FB24</f>
-        <v>209.16</v>
+      <c r="FV24" s="26">
+        <f>FL24-FD24</f>
+        <v>255.51</v>
       </c>
     </row>
-    <row r="27" spans="1:176">
+    <row r="27" spans="1:178">
       <c r="A27" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="B27" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="C27" s="29"/>
       <c r="D27" s="29"/>
@@ -15955,13 +16128,15 @@
       <c r="FJ27" s="29"/>
       <c r="FK27" s="29"/>
       <c r="FL27" s="29"/>
+      <c r="FM27" s="29"/>
+      <c r="FN27" s="29"/>
     </row>
-    <row r="28" spans="1:176">
+    <row r="28" spans="1:178">
       <c r="A28" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="B28" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="P28" s="29"/>
       <c r="Q28" s="29"/>
@@ -16119,21 +16294,23 @@
       <c r="FM28" s="29"/>
       <c r="FN28" s="29"/>
       <c r="FO28" s="29"/>
+      <c r="FP28" s="29"/>
+      <c r="FQ28" s="29"/>
     </row>
-    <row r="29" spans="1:176">
+    <row r="29" spans="1:178">
       <c r="A29" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="B29" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
     </row>
-    <row r="30" spans="1:176">
+    <row r="30" spans="1:178">
       <c r="A30" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B30" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="C30" s="29"/>
       <c r="D30" s="29"/>
@@ -16300,57 +16477,59 @@
       <c r="FI30" s="29"/>
       <c r="FJ30" s="29"/>
       <c r="FK30" s="29"/>
+      <c r="FL30" s="29"/>
+      <c r="FM30" s="29"/>
     </row>
-    <row r="31" spans="1:176">
+    <row r="31" spans="1:178">
       <c r="A31" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="B31" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
     </row>
-    <row r="32" spans="1:176">
+    <row r="32" spans="1:178">
       <c r="A32" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B32" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B33" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34" t="s">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="B34" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="B35" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="B36" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
     </row>
   </sheetData>
-  <sortState ref="A2:FT24">
+  <sortState ref="A2:FV24">
     <sortCondition ref="A2"/>
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -16388,157 +16567,157 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="C1" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="D1" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="E1" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="F1" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="G1" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="H1" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="I1" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="J1" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="K1" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="L1" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="M1" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="N1" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="O1" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="P1" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="Q1" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="R1" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="S1" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="T1" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="U1" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="V1" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="W1" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="X1" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="Y1" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="Z1" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="AA1" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="AB1" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="AC1" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="AD1" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="AE1" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="AF1" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="AG1" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="AH1" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="AI1" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="AJ1" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="AK1" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="AL1" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="AM1" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="AN1" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="AO1" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="AP1" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="AQ1" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="AR1" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="AS1" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="AT1" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="AU1" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="AV1" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="AW1" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="AX1" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="AY1" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="AZ1" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
     </row>
     <row r="2" spans="1:54">
@@ -17839,7 +18018,7 @@
     </row>
     <row r="14" spans="1:54">
       <c r="A14" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="B14">
         <f>SUM(B2:B9)</f>
@@ -18049,7 +18228,7 @@
     <row r="18" ht="10" customHeight="1"/>
     <row r="19" spans="1:52">
       <c r="A19" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
     </row>
     <row r="20" spans="1:52">
@@ -19294,10 +19473,10 @@
     </row>
     <row r="29" spans="1:52">
       <c r="A29" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="AZ29" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
     </row>
     <row r="30" spans="1:52">
@@ -21030,7 +21209,7 @@
   <pageSetup paperSize="9" orientation="portrait"/>
   <headerFooter/>
   <ignoredErrors>
-    <ignoredError sqref="C31:L38 M31:M39 N31:AY38" formulaRange="1"/>
+    <ignoredError sqref="N31:AY38 M31:M39 C31:L38" formulaRange="1"/>
   </ignoredErrors>
 </worksheet>
 </file>